--- a/results/excel/Mundial_2026_Predicciones.xlsx
+++ b/results/excel/Mundial_2026_Predicciones.xlsx
@@ -5834,16 +5834,16 @@
         <v>1771</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.4628</v>
+        <v>0.459</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2934</v>
+        <v>0.3006</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1602</v>
+        <v>0.1642</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.08360000000000001</v>
+        <v>0.07619999999999993</v>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
@@ -5862,16 +5862,16 @@
         <v>1746</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.5018</v>
+        <v>0.4804</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>0.2836</v>
+        <v>0.294</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.1476</v>
+        <v>0.1494</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>0.06699999999999995</v>
+        <v>0.07620000000000007</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -5890,16 +5890,16 @@
         <v>1734</v>
       </c>
       <c r="X5" s="19" t="n">
-        <v>0.2756</v>
+        <v>0.2898</v>
       </c>
       <c r="Y5" s="19" t="n">
-        <v>0.2764</v>
+        <v>0.2746</v>
       </c>
       <c r="Z5" s="19" t="n">
-        <v>0.2284</v>
+        <v>0.2244</v>
       </c>
       <c r="AA5" s="19" t="n">
-        <v>0.2196</v>
+        <v>0.2111999999999999</v>
       </c>
       <c r="AB5" s="17" t="inlineStr">
         <is>
@@ -5918,16 +5918,16 @@
         <v>1838</v>
       </c>
       <c r="AH5" s="19" t="n">
-        <v>0.4552</v>
+        <v>0.456</v>
       </c>
       <c r="AI5" s="19" t="n">
-        <v>0.3454</v>
+        <v>0.3498</v>
       </c>
       <c r="AJ5" s="19" t="n">
-        <v>0.1522</v>
+        <v>0.1472</v>
       </c>
       <c r="AK5" s="19" t="n">
-        <v>0.04719999999999996</v>
+        <v>0.04700000000000004</v>
       </c>
       <c r="AL5" s="17" t="inlineStr">
         <is>
@@ -5948,16 +5948,16 @@
         <v>1725</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>0.3288</v>
+        <v>0.3272</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0.3304</v>
+        <v>0.3258</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0.2112</v>
+        <v>0.2242</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0.1296</v>
+        <v>0.1228000000000001</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
@@ -5976,16 +5976,16 @@
         <v>1685</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>0.306</v>
+        <v>0.328</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>0.3514</v>
+        <v>0.3368</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>0.2152</v>
+        <v>0.2184</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>0.1274</v>
+        <v>0.1167999999999999</v>
       </c>
       <c r="R6" s="20" t="inlineStr">
         <is>
@@ -6007,13 +6007,13 @@
         <v>0.2738</v>
       </c>
       <c r="Y6" s="22" t="n">
-        <v>0.2634</v>
+        <v>0.2534</v>
       </c>
       <c r="Z6" s="22" t="n">
-        <v>0.2434</v>
+        <v>0.2504</v>
       </c>
       <c r="AA6" s="22" t="n">
-        <v>0.2193999999999999</v>
+        <v>0.2223999999999999</v>
       </c>
       <c r="AB6" s="20" t="inlineStr">
         <is>
@@ -6032,16 +6032,16 @@
         <v>1828</v>
       </c>
       <c r="AH6" s="22" t="n">
-        <v>0.419</v>
+        <v>0.4282</v>
       </c>
       <c r="AI6" s="22" t="n">
-        <v>0.3724</v>
+        <v>0.371</v>
       </c>
       <c r="AJ6" s="22" t="n">
-        <v>0.1622</v>
+        <v>0.1556</v>
       </c>
       <c r="AK6" s="22" t="n">
-        <v>0.04639999999999994</v>
+        <v>0.04519999999999999</v>
       </c>
       <c r="AL6" s="20" t="inlineStr">
         <is>
@@ -6062,16 +6062,16 @@
         <v>1605</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.126</v>
+        <v>0.1364</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>0.225</v>
+        <v>0.2238</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.3236</v>
+        <v>0.3202</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.3254</v>
+        <v>0.3196000000000001</v>
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
@@ -6090,16 +6090,16 @@
         <v>1562</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.1086</v>
+        <v>0.1138</v>
       </c>
       <c r="O7" s="25" t="n">
-        <v>0.215</v>
+        <v>0.2168</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>0.3398</v>
+        <v>0.3476</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>0.3366</v>
+        <v>0.3218</v>
       </c>
       <c r="R7" s="26" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         <v>1729</v>
       </c>
       <c r="X7" s="25" t="n">
-        <v>0.2648</v>
+        <v>0.2592</v>
       </c>
       <c r="Y7" s="25" t="n">
-        <v>0.2606</v>
+        <v>0.2634</v>
       </c>
       <c r="Z7" s="25" t="n">
-        <v>0.2534</v>
+        <v>0.251</v>
       </c>
       <c r="AA7" s="25" t="n">
-        <v>0.2212000000000001</v>
+        <v>0.2264</v>
       </c>
       <c r="AB7" s="26" t="inlineStr">
         <is>
@@ -6146,16 +6146,16 @@
         <v>1632</v>
       </c>
       <c r="AH7" s="25" t="n">
-        <v>0.0982</v>
+        <v>0.0906</v>
       </c>
       <c r="AI7" s="25" t="n">
-        <v>0.1984</v>
+        <v>0.2076</v>
       </c>
       <c r="AJ7" s="25" t="n">
-        <v>0.4318</v>
+        <v>0.4404</v>
       </c>
       <c r="AK7" s="25" t="n">
-        <v>0.2716</v>
+        <v>0.2614</v>
       </c>
       <c r="AL7" s="26" t="inlineStr">
         <is>
@@ -6176,16 +6176,16 @@
         <v>1549</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.0824</v>
+        <v>0.0774</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.1512</v>
+        <v>0.1498</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.305</v>
+        <v>0.2914</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.4614</v>
+        <v>0.4813999999999999</v>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
@@ -6204,16 +6204,16 @@
         <v>1513</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>0.15</v>
+        <v>0.1524</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.2974</v>
+        <v>0.2846</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>0.469</v>
+        <v>0.4852</v>
       </c>
       <c r="R8" s="30" t="inlineStr">
         <is>
@@ -6232,16 +6232,16 @@
         <v>1676</v>
       </c>
       <c r="X8" s="29" t="n">
-        <v>0.1858</v>
+        <v>0.1772</v>
       </c>
       <c r="Y8" s="29" t="n">
-        <v>0.1996</v>
+        <v>0.2086</v>
       </c>
       <c r="Z8" s="29" t="n">
-        <v>0.2748</v>
+        <v>0.2742</v>
       </c>
       <c r="AA8" s="29" t="n">
-        <v>0.3398</v>
+        <v>0.34</v>
       </c>
       <c r="AB8" s="30" t="inlineStr">
         <is>
@@ -6260,16 +6260,16 @@
         <v>1499</v>
       </c>
       <c r="AH8" s="29" t="n">
-        <v>0.0276</v>
+        <v>0.0252</v>
       </c>
       <c r="AI8" s="29" t="n">
-        <v>0.0838</v>
+        <v>0.0716</v>
       </c>
       <c r="AJ8" s="29" t="n">
-        <v>0.2538</v>
+        <v>0.2568</v>
       </c>
       <c r="AK8" s="29" t="n">
-        <v>0.6348</v>
+        <v>0.6464000000000001</v>
       </c>
       <c r="AL8" s="30" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         <v>1819</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.494</v>
+        <v>0.4894</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.3144</v>
+        <v>0.3084</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.1536</v>
+        <v>0.16</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.03800000000000001</v>
+        <v>0.04219999999999993</v>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -6502,16 +6502,16 @@
         <v>1830</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>0.4664</v>
+        <v>0.4808</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>0.3146</v>
+        <v>0.3028</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>0.1474</v>
+        <v>0.153</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>0.07160000000000008</v>
+        <v>0.06339999999999998</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -6530,16 +6530,16 @@
         <v>1791</v>
       </c>
       <c r="X13" s="19" t="n">
-        <v>0.4434</v>
+        <v>0.4508</v>
       </c>
       <c r="Y13" s="19" t="n">
-        <v>0.3028</v>
+        <v>0.3068</v>
       </c>
       <c r="Z13" s="19" t="n">
-        <v>0.1806</v>
+        <v>0.1716</v>
       </c>
       <c r="AA13" s="19" t="n">
-        <v>0.07319999999999996</v>
+        <v>0.0708</v>
       </c>
       <c r="AB13" s="17" t="inlineStr">
         <is>
@@ -6558,16 +6558,16 @@
         <v>1961</v>
       </c>
       <c r="AH13" s="19" t="n">
-        <v>0.7066</v>
+        <v>0.7238</v>
       </c>
       <c r="AI13" s="19" t="n">
-        <v>0.2256</v>
+        <v>0.2144</v>
       </c>
       <c r="AJ13" s="19" t="n">
-        <v>0.0572</v>
+        <v>0.0524</v>
       </c>
       <c r="AK13" s="19" t="n">
-        <v>0.0106</v>
+        <v>0.009399999999999992</v>
       </c>
       <c r="AL13" s="17" t="inlineStr">
         <is>
@@ -6588,16 +6588,16 @@
         <v>1756</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0.3292</v>
+        <v>0.323</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0.359</v>
+        <v>0.3582</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.2308</v>
+        <v>0.2436</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.08100000000000007</v>
+        <v>0.07520000000000002</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         <v>1792</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.3662</v>
+        <v>0.358</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>0.339</v>
+        <v>0.347</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.1896</v>
+        <v>0.198</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>0.1051999999999999</v>
+        <v>0.09700000000000003</v>
       </c>
       <c r="R14" s="20" t="inlineStr">
         <is>
@@ -6644,16 +6644,16 @@
         <v>1740</v>
       </c>
       <c r="X14" s="22" t="n">
-        <v>0.3266</v>
+        <v>0.3082</v>
       </c>
       <c r="Y14" s="22" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="Z14" s="22" t="n">
-        <v>0.2416</v>
+        <v>0.244</v>
       </c>
       <c r="AA14" s="22" t="n">
-        <v>0.1088</v>
+        <v>0.1268</v>
       </c>
       <c r="AB14" s="20" t="inlineStr">
         <is>
@@ -6672,16 +6672,16 @@
         <v>1767</v>
       </c>
       <c r="AH14" s="22" t="n">
-        <v>0.2306</v>
+        <v>0.2142</v>
       </c>
       <c r="AI14" s="22" t="n">
-        <v>0.4768</v>
+        <v>0.4886</v>
       </c>
       <c r="AJ14" s="22" t="n">
-        <v>0.2168</v>
+        <v>0.2114</v>
       </c>
       <c r="AK14" s="22" t="n">
-        <v>0.07579999999999998</v>
+        <v>0.08580000000000007</v>
       </c>
       <c r="AL14" s="20" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>1647</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.1502</v>
+        <v>0.1618</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.2562</v>
+        <v>0.2606</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.3976</v>
+        <v>0.3932</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>0.196</v>
+        <v>0.1844000000000001</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -6723,23 +6723,23 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="M15" s="23" t="n">
-        <v>1610</v>
+        <v>1615</v>
       </c>
       <c r="N15" s="25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="O15" s="25" t="n">
-        <v>0.1674</v>
+        <v>0.1862</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>0.3236</v>
+        <v>0.3262</v>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>0.423</v>
+        <v>0.4048</v>
       </c>
       <c r="R15" s="26" t="inlineStr">
         <is>
@@ -6758,16 +6758,16 @@
         <v>1669</v>
       </c>
       <c r="X15" s="25" t="n">
-        <v>0.1776</v>
+        <v>0.1868</v>
       </c>
       <c r="Y15" s="25" t="n">
-        <v>0.2656</v>
+        <v>0.2582</v>
       </c>
       <c r="Z15" s="25" t="n">
-        <v>0.3332</v>
+        <v>0.3368</v>
       </c>
       <c r="AA15" s="25" t="n">
-        <v>0.2236</v>
+        <v>0.2182000000000001</v>
       </c>
       <c r="AB15" s="26" t="inlineStr">
         <is>
@@ -6786,16 +6786,16 @@
         <v>1575</v>
       </c>
       <c r="AH15" s="25" t="n">
-        <v>0.041</v>
+        <v>0.0404</v>
       </c>
       <c r="AI15" s="25" t="n">
-        <v>0.179</v>
+        <v>0.1802</v>
       </c>
       <c r="AJ15" s="25" t="n">
-        <v>0.4122</v>
+        <v>0.4034</v>
       </c>
       <c r="AK15" s="25" t="n">
-        <v>0.3678</v>
+        <v>0.376</v>
       </c>
       <c r="AL15" s="26" t="inlineStr">
         <is>
@@ -6816,16 +6816,16 @@
         <v>1461</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.0266</v>
+        <v>0.0258</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>0.0704</v>
+        <v>0.0728</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>0.218</v>
+        <v>0.2032</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6981999999999999</v>
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
@@ -6837,23 +6837,23 @@
       </c>
       <c r="L16" s="28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.0814</v>
+        <v>0.0784</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.179</v>
+        <v>0.164</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>0.3394</v>
+        <v>0.3228</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>0.4002000000000001</v>
+        <v>0.4348</v>
       </c>
       <c r="R16" s="30" t="inlineStr">
         <is>
@@ -6872,16 +6872,16 @@
         <v>1532</v>
       </c>
       <c r="X16" s="29" t="n">
-        <v>0.0524</v>
+        <v>0.0542</v>
       </c>
       <c r="Y16" s="29" t="n">
-        <v>0.1086</v>
+        <v>0.114</v>
       </c>
       <c r="Z16" s="29" t="n">
-        <v>0.2446</v>
+        <v>0.2476</v>
       </c>
       <c r="AA16" s="29" t="n">
-        <v>0.5943999999999999</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="AB16" s="30" t="inlineStr">
         <is>
@@ -6900,16 +6900,16 @@
         <v>1517</v>
       </c>
       <c r="AH16" s="29" t="n">
-        <v>0.0218</v>
+        <v>0.0216</v>
       </c>
       <c r="AI16" s="29" t="n">
-        <v>0.1186</v>
+        <v>0.1168</v>
       </c>
       <c r="AJ16" s="29" t="n">
-        <v>0.3138</v>
+        <v>0.3328</v>
       </c>
       <c r="AK16" s="29" t="n">
-        <v>0.5457999999999998</v>
+        <v>0.5288</v>
       </c>
       <c r="AL16" s="30" t="inlineStr">
         <is>
@@ -7114,16 +7114,16 @@
         <v>1931</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.6378</v>
+        <v>0.6276</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.2402</v>
+        <v>0.2318</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.0868</v>
+        <v>0.1032</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.03519999999999997</v>
+        <v>0.03739999999999995</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -7142,16 +7142,16 @@
         <v>1940</v>
       </c>
       <c r="N21" s="19" t="n">
-        <v>0.7116</v>
+        <v>0.7128</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>0.1892</v>
+        <v>0.1916</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0726</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>0.02379999999999999</v>
+        <v>0.02300000000000002</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -7170,16 +7170,16 @@
         <v>1832</v>
       </c>
       <c r="X21" s="19" t="n">
-        <v>0.4658</v>
+        <v>0.469</v>
       </c>
       <c r="Y21" s="19" t="n">
-        <v>0.3106</v>
+        <v>0.3074</v>
       </c>
       <c r="Z21" s="19" t="n">
-        <v>0.159</v>
+        <v>0.1518</v>
       </c>
       <c r="AA21" s="19" t="n">
-        <v>0.06460000000000002</v>
+        <v>0.07180000000000003</v>
       </c>
       <c r="AB21" s="17" t="inlineStr">
         <is>
@@ -7198,16 +7198,16 @@
         <v>1887</v>
       </c>
       <c r="AH21" s="19" t="n">
-        <v>0.5586</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AI21" s="19" t="n">
-        <v>0.282</v>
+        <v>0.2878</v>
       </c>
       <c r="AJ21" s="19" t="n">
-        <v>0.1294</v>
+        <v>0.1226</v>
       </c>
       <c r="AK21" s="19" t="n">
-        <v>0.03000000000000005</v>
+        <v>0.03159999999999995</v>
       </c>
       <c r="AL21" s="17" t="inlineStr">
         <is>
@@ -7228,16 +7228,16 @@
         <v>1769</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0.2142</v>
+        <v>0.2106</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0.368</v>
+        <v>0.3704</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>0.2618</v>
+        <v>0.257</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0.1560000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -7256,16 +7256,16 @@
         <v>1688</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>0.1274</v>
+        <v>0.1222</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>0.3336</v>
+        <v>0.3324</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.3094</v>
+        <v>0.305</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0.2296</v>
+        <v>0.2404000000000001</v>
       </c>
       <c r="R22" s="20" t="inlineStr">
         <is>
@@ -7284,16 +7284,16 @@
         <v>1794</v>
       </c>
       <c r="X22" s="22" t="n">
-        <v>0.3502</v>
+        <v>0.3492</v>
       </c>
       <c r="Y22" s="22" t="n">
-        <v>0.3456</v>
+        <v>0.3332</v>
       </c>
       <c r="Z22" s="22" t="n">
-        <v>0.2014</v>
+        <v>0.21</v>
       </c>
       <c r="AA22" s="22" t="n">
-        <v>0.1027999999999999</v>
+        <v>0.1076000000000001</v>
       </c>
       <c r="AB22" s="20" t="inlineStr">
         <is>
@@ -7312,16 +7312,16 @@
         <v>1794</v>
       </c>
       <c r="AH22" s="22" t="n">
-        <v>0.3122</v>
+        <v>0.2936</v>
       </c>
       <c r="AI22" s="22" t="n">
-        <v>0.3852</v>
+        <v>0.381</v>
       </c>
       <c r="AJ22" s="22" t="n">
-        <v>0.2294</v>
+        <v>0.2394</v>
       </c>
       <c r="AK22" s="22" t="n">
-        <v>0.07319999999999999</v>
+        <v>0.08599999999999991</v>
       </c>
       <c r="AL22" s="20" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         <v>1688</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.1016</v>
+        <v>0.1084</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0.2416</v>
+        <v>0.2448</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>0.3556</v>
+        <v>0.3482</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>0.3011999999999999</v>
+        <v>0.2985999999999999</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -7370,16 +7370,16 @@
         <v>1681</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>0.1128</v>
+        <v>0.1168</v>
       </c>
       <c r="O23" s="25" t="n">
-        <v>0.3098</v>
+        <v>0.3096</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.3294</v>
+        <v>0.3242</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>0.2479999999999999</v>
+        <v>0.2494</v>
       </c>
       <c r="R23" s="26" t="inlineStr">
         <is>
@@ -7398,16 +7398,16 @@
         <v>1652</v>
       </c>
       <c r="X23" s="25" t="n">
-        <v>0.1086</v>
+        <v>0.1074</v>
       </c>
       <c r="Y23" s="25" t="n">
-        <v>0.1972</v>
+        <v>0.2038</v>
       </c>
       <c r="Z23" s="25" t="n">
-        <v>0.3558</v>
+        <v>0.353</v>
       </c>
       <c r="AA23" s="25" t="n">
-        <v>0.3383999999999999</v>
+        <v>0.3358000000000001</v>
       </c>
       <c r="AB23" s="26" t="inlineStr">
         <is>
@@ -7426,16 +7426,16 @@
         <v>1671</v>
       </c>
       <c r="AH23" s="25" t="n">
-        <v>0.1086</v>
+        <v>0.1264</v>
       </c>
       <c r="AI23" s="25" t="n">
-        <v>0.2556</v>
+        <v>0.2474</v>
       </c>
       <c r="AJ23" s="25" t="n">
-        <v>0.4234</v>
+        <v>0.4104</v>
       </c>
       <c r="AK23" s="25" t="n">
-        <v>0.2123999999999999</v>
+        <v>0.2157999999999999</v>
       </c>
       <c r="AL23" s="26" t="inlineStr">
         <is>
@@ -7456,16 +7456,16 @@
         <v>1613</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>0.0464</v>
+        <v>0.0534</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>0.1502</v>
+        <v>0.153</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0.2958</v>
+        <v>0.2916</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.502</v>
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
@@ -7487,13 +7487,13 @@
         <v>0.0482</v>
       </c>
       <c r="O24" s="29" t="n">
-        <v>0.1674</v>
+        <v>0.1664</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.2858</v>
+        <v>0.2982</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>0.4986</v>
+        <v>0.4872</v>
       </c>
       <c r="R24" s="30" t="inlineStr">
         <is>
@@ -7512,16 +7512,16 @@
         <v>1607</v>
       </c>
       <c r="X24" s="29" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="Y24" s="29" t="n">
-        <v>0.1466</v>
+        <v>0.1556</v>
       </c>
       <c r="Z24" s="29" t="n">
-        <v>0.2838</v>
+        <v>0.2852</v>
       </c>
       <c r="AA24" s="29" t="n">
-        <v>0.4942</v>
+        <v>0.4848</v>
       </c>
       <c r="AB24" s="30" t="inlineStr">
         <is>
@@ -7540,16 +7540,16 @@
         <v>1500</v>
       </c>
       <c r="AH24" s="29" t="n">
-        <v>0.0206</v>
+        <v>0.022</v>
       </c>
       <c r="AI24" s="29" t="n">
-        <v>0.0772</v>
+        <v>0.0838</v>
       </c>
       <c r="AJ24" s="29" t="n">
-        <v>0.2178</v>
+        <v>0.2276</v>
       </c>
       <c r="AK24" s="29" t="n">
-        <v>0.6844</v>
+        <v>0.6666</v>
       </c>
       <c r="AL24" s="30" t="inlineStr">
         <is>
@@ -7718,11 +7718,11 @@
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D5" s="34" t="n">
-        <v>0.515</v>
+        <v>0.521</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="F5" s="35" t="n">
-        <v>0.299</v>
+        <v>0.297</v>
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
@@ -7755,15 +7755,15 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.5379999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
       <c r="G6" s="36" t="inlineStr">
         <is>
@@ -8048,11 +8048,11 @@
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D15" s="34" t="n">
-        <v>0.433</v>
+        <v>0.427</v>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
@@ -8060,11 +8060,11 @@
         </is>
       </c>
       <c r="F15" s="35" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="G15" s="36" t="inlineStr">
         <is>
-          <t>→ United States</t>
+          <t>→ Turkey</t>
         </is>
       </c>
     </row>
@@ -8085,15 +8085,15 @@
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.611</v>
+        <v>0.624</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F16" s="35" t="n">
-        <v>0.258</v>
+        <v>0.253</v>
       </c>
       <c r="G16" s="36" t="inlineStr">
         <is>
@@ -8379,11 +8379,11 @@
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="D26" s="34" t="n">
-        <v>0.531</v>
+        <v>0.5379999999999999</v>
       </c>
       <c r="E26" s="39" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="F26" s="35" t="n">
-        <v>0.292</v>
+        <v>0.29</v>
       </c>
       <c r="G26" s="40" t="inlineStr">
         <is>

--- a/results/excel/Mundial_2026_Predicciones.xlsx
+++ b/results/excel/Mundial_2026_Predicciones.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fase Eliminatoria" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prob. Campeonato" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validación Modelo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -158,7 +159,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001B5E20"/>
+      <color rgb="00B71C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B71C1C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -168,18 +175,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00555555"/>
+      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00B71C1C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B71C1C"/>
+      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
@@ -191,8 +192,19 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -304,6 +316,16 @@
         <fgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -331,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -539,10 +561,10 @@
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -551,19 +573,19 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -595,6 +617,54 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1097,13 +1167,13 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.7033</v>
+        <v>0.6179</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1928</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.1967</v>
+        <v>0.1893</v>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
@@ -1111,10 +1181,10 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1831</v>
+        <v>1816</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1629</v>
+        <v>1641</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1681</v>
@@ -1123,10 +1193,10 @@
         <v>1430</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1771</v>
+        <v>1762</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1549</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="5">
@@ -1151,13 +1221,13 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.5588</v>
+        <v>0.5688</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.1605</v>
+        <v>0.2055</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.2808</v>
+        <v>0.2257</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
@@ -1165,10 +1235,10 @@
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1815</v>
+        <v>1840</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1675</v>
+        <v>1631</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>1589</v>
@@ -1177,10 +1247,10 @@
         <v>1501</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>1725</v>
+        <v>1739</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>1605</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1">
@@ -1221,13 +1291,13 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.6512</v>
+        <v>0.6253</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1075</v>
+        <v>0.1909</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.2413</v>
+        <v>0.1838</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -1235,10 +1305,10 @@
         </is>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1597</v>
+        <v>1534</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>1556</v>
@@ -1247,10 +1317,10 @@
         <v>1386</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>1513</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1">
@@ -1291,13 +1361,13 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.4539</v>
+        <v>0.492</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.2216</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0.3244</v>
+        <v>0.2253</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0.2827</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -1305,10 +1375,10 @@
         </is>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1790</v>
+        <v>1726</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>1673</v>
@@ -1320,7 +1390,7 @@
         <v>1734</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>1676</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="10" ht="6" customHeight="1">
@@ -1361,13 +1431,13 @@
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.2314</v>
+        <v>0.2064</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1988</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.6686</v>
+        <v>0.5948</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
@@ -1375,10 +1445,10 @@
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1633</v>
+        <v>1615</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1811</v>
+        <v>1792</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>1455</v>
@@ -1387,10 +1457,10 @@
         <v>1649</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1562</v>
+        <v>1551</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>1746</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="12" ht="6" customHeight="1">
@@ -1431,24 +1501,24 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.3749</v>
+        <v>0.3439</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.2704</v>
+        <v>0.2479</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.3547</v>
+        <v>0.4082</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>→ Brazil</t>
+          <t>→ Morocco</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1889</v>
+        <v>1862</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1876</v>
+        <v>1915</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>1761</v>
@@ -1457,10 +1527,10 @@
         <v>1756</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1838</v>
+        <v>1821</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>1828</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="14">
@@ -1485,13 +1555,13 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.2704</v>
+        <v>0.2772</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1466</v>
+        <v>0.2233</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.583</v>
+        <v>0.4995</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
@@ -1499,10 +1569,10 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1637</v>
+        <v>1653</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1722</v>
+        <v>1686</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>1292</v>
@@ -1511,10 +1581,10 @@
         <v>1498</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1632</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1">
@@ -1555,24 +1625,24 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.3594</v>
+        <v>0.423</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.2789</v>
+        <v>0.2438</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.3617</v>
+        <v>0.3332</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>→ Turkey</t>
+          <t>→ Australia</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1828</v>
+        <v>1858</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1818</v>
+        <v>1777</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1581</v>
@@ -1581,10 +1651,10 @@
         <v>1599</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1729</v>
+        <v>1747</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1730</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="17" ht="6" customHeight="1">
@@ -1625,13 +1695,13 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.7985</v>
+        <v>0.7174</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1655</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.1015</v>
+        <v>0.1171</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -1639,10 +1709,10 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1879</v>
+        <v>1856</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1572</v>
+        <v>1621</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>1730</v>
@@ -1651,10 +1721,10 @@
         <v>1295</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1819</v>
+        <v>1806</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1461</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="19">
@@ -1678,14 +1748,14 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
-        <v>0.2888</v>
+      <c r="E19" s="7" t="n">
+        <v>0.3086</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.1713</v>
+        <v>0.2346</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.54</v>
+        <v>0.4568</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -1693,10 +1763,10 @@
         </is>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1723</v>
+        <v>1747</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1863</v>
+        <v>1819</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>1533</v>
@@ -1705,10 +1775,10 @@
         <v>1595</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1647</v>
+        <v>1662</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>1756</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="20" ht="6" customHeight="1">
@@ -1749,13 +1819,13 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.4199</v>
+        <v>0.3767</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.2422</v>
+        <v>0.2571</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.3379</v>
+        <v>0.3663</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -1763,10 +1833,10 @@
         </is>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1878</v>
+        <v>1862</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1880</v>
+        <v>1919</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>1758</v>
@@ -1775,10 +1845,10 @@
         <v>1660</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>1830</v>
+        <v>1820</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>1792</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="22">
@@ -1803,24 +1873,24 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.3676</v>
+        <v>0.3287</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.2751</v>
+        <v>0.2421</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.3573</v>
+        <v>0.4292</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>→ Sweden</t>
+          <t>→ Tunisia</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1681</v>
+        <v>1621</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1694</v>
+        <v>1720</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>1515</v>
@@ -1829,10 +1899,10 @@
         <v>1483</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1615</v>
+        <v>1579</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1610</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="23" ht="6" customHeight="1">
@@ -1873,10 +1943,10 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.5643</v>
+        <v>0.4978</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.1573</v>
+        <v>0.2238</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>0.2784</v>
@@ -1887,10 +1957,10 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1829</v>
+        <v>1804</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1739</v>
+        <v>1750</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>1735</v>
@@ -1899,10 +1969,10 @@
         <v>1563</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1669</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="25">
@@ -1927,13 +1997,13 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.6912</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1916</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.2088</v>
+        <v>0.1859</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -1941,10 +2011,10 @@
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1823</v>
+        <v>1851</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1698</v>
+        <v>1723</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>1615</v>
@@ -1953,10 +2023,10 @@
         <v>1282</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>1740</v>
+        <v>1756</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>1532</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="26" ht="6" customHeight="1">
@@ -1997,13 +2067,13 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.801</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.1</v>
+        <v>0.138</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0.0648</v>
+        <v>0.0609</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
@@ -2011,10 +2081,10 @@
         </is>
       </c>
       <c r="I27" s="10" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>1876</v>
@@ -2023,10 +2093,10 @@
         <v>1366</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>1517</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="28">
@@ -2051,13 +2121,13 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.2232</v>
+        <v>0.2201</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2036</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.6768</v>
+        <v>0.5764</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
@@ -2065,10 +2135,10 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1830</v>
+        <v>1793</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>1421</v>
@@ -2077,10 +2147,10 @@
         <v>1673</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1767</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="29" ht="6" customHeight="1">
@@ -2121,13 +2191,13 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.6334</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.1177</v>
+        <v>0.2103</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>0.2489</v>
+        <v>0.2398</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
@@ -2135,10 +2205,10 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1967</v>
+        <v>1953</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1822</v>
+        <v>1838</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>1877</v>
@@ -2147,10 +2217,10 @@
         <v>1689</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1769</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="31">
@@ -2175,13 +2245,13 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.3125</v>
+        <v>0.301</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.2043</v>
+        <v>0.2318</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4832</v>
+        <v>0.4672</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
@@ -2189,10 +2259,10 @@
         </is>
       </c>
       <c r="I31" s="10" t="n">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>1447</v>
@@ -2201,10 +2271,10 @@
         <v>1551</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>1688</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1">
@@ -2245,13 +2315,13 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.7289</v>
+        <v>0.6308</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1894</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.1711</v>
+        <v>0.1798</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
@@ -2259,10 +2329,10 @@
         </is>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1983</v>
+        <v>1958</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1771</v>
+        <v>1802</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>1875</v>
@@ -2271,10 +2341,10 @@
         <v>1564</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>1940</v>
+        <v>1925</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>1688</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="34">
@@ -2298,14 +2368,14 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
-        <v>0.5233</v>
+      <c r="E34" s="7" t="n">
+        <v>0.4413</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.1809</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>0.2958</v>
+        <v>0.2388</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0.32</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
@@ -2313,10 +2383,10 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1739</v>
+        <v>1709</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1709</v>
+        <v>1751</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>1593</v>
@@ -2325,10 +2395,10 @@
         <v>1391</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1681</v>
+        <v>1663</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1582</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="35" ht="6" customHeight="1">
@@ -2369,13 +2439,13 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.7067</v>
+        <v>0.6044</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1963</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>0.1933</v>
+        <v>0.1993</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -2383,10 +2453,10 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1878</v>
+        <v>1846</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1693</v>
+        <v>1715</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>1764</v>
@@ -2395,10 +2465,10 @@
         <v>1478</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1832</v>
+        <v>1813</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>1607</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="37">
@@ -2423,13 +2493,13 @@
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.2644</v>
+        <v>0.2701</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.1385</v>
+        <v>0.2209</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.597</v>
+        <v>0.509</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -2437,10 +2507,10 @@
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1777</v>
+        <v>1808</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1861</v>
+        <v>1839</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>1465</v>
@@ -2449,10 +2519,10 @@
         <v>1693</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>1652</v>
+        <v>1671</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>1794</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="38" ht="6" customHeight="1">
@@ -2493,13 +2563,13 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.5132</v>
+        <v>0.511</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.1867</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2204</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>0.2687</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
@@ -2507,10 +2577,10 @@
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1846</v>
+        <v>1819</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>1826</v>
@@ -2519,10 +2589,10 @@
         <v>1717</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>1794</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="40">
@@ -2547,13 +2617,13 @@
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.2419</v>
+        <v>0.2221</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.1083</v>
+        <v>0.2042</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.6498</v>
+        <v>0.5737</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
@@ -2561,10 +2631,10 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>1346</v>
@@ -2573,10 +2643,10 @@
         <v>1541</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1671</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="41" ht="6" customHeight="1">
@@ -2617,13 +2687,13 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.4497</v>
+        <v>0.399</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.2242</v>
+        <v>0.2505</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.3261</v>
+        <v>0.3504</v>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
@@ -2631,10 +2701,10 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1675</v>
+        <v>1631</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1629</v>
+        <v>1641</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>1501</v>
@@ -2643,10 +2713,10 @@
         <v>1430</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>1605</v>
+        <v>1579</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1549</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="43">
@@ -2671,13 +2741,13 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.3988</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.2341</v>
+        <v>0.2506</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.3326</v>
+        <v>0.3506</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -2685,10 +2755,10 @@
         </is>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1831</v>
+        <v>1816</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1815</v>
+        <v>1840</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>1681</v>
@@ -2697,10 +2767,10 @@
         <v>1589</v>
       </c>
       <c r="M43" s="10" t="n">
-        <v>1771</v>
+        <v>1762</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>1725</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="44" ht="6" customHeight="1">
@@ -2741,13 +2811,13 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.7139</v>
+        <v>0.6713</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1786</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0.1861</v>
+        <v>0.1502</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -2755,10 +2825,10 @@
         </is>
       </c>
       <c r="I45" s="10" t="n">
-        <v>1811</v>
+        <v>1792</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1597</v>
+        <v>1534</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>1649</v>
@@ -2767,10 +2837,10 @@
         <v>1386</v>
       </c>
       <c r="M45" s="10" t="n">
-        <v>1746</v>
+        <v>1735</v>
       </c>
       <c r="N45" s="10" t="n">
-        <v>1513</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="46">
@@ -2795,13 +2865,13 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0.5653</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.1567</v>
+        <v>0.2127</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0.278</v>
+        <v>0.2466</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
@@ -2809,10 +2879,10 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1633</v>
+        <v>1615</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>1556</v>
@@ -2821,10 +2891,10 @@
         <v>1455</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1562</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="47" ht="6" customHeight="1">
@@ -2865,13 +2935,13 @@
         </is>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.2202</v>
+        <v>0.1636</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1836</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.6798</v>
+        <v>0.6528</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
@@ -2879,10 +2949,10 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1722</v>
+        <v>1686</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1876</v>
+        <v>1915</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>1498</v>
@@ -2891,10 +2961,10 @@
         <v>1756</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>1632</v>
+        <v>1611</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1828</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="49">
@@ -2919,13 +2989,13 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0.788</v>
+        <v>0.7159</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1659</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>0.112</v>
+        <v>0.1182</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
@@ -2933,10 +3003,10 @@
         </is>
       </c>
       <c r="I49" s="10" t="n">
-        <v>1889</v>
+        <v>1862</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1637</v>
+        <v>1653</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>1761</v>
@@ -2945,10 +3015,10 @@
         <v>1292</v>
       </c>
       <c r="M49" s="10" t="n">
-        <v>1838</v>
+        <v>1821</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>1499</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="50" ht="6" customHeight="1">
@@ -2989,24 +3059,24 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.3676</v>
+        <v>0.3582</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.2751</v>
+        <v>0.2537</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.3573</v>
+        <v>0.3881</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>→ United States</t>
+          <t>→ Australia</t>
         </is>
       </c>
       <c r="I51" s="10" t="n">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>1828</v>
+        <v>1858</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>1673</v>
@@ -3018,7 +3088,7 @@
         <v>1734</v>
       </c>
       <c r="N51" s="10" t="n">
-        <v>1729</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="52">
@@ -3042,14 +3112,14 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n">
-        <v>0.4476</v>
+      <c r="E52" s="6" t="n">
+        <v>0.4576</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.2254</v>
+        <v>0.2343</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0.327</v>
+        <v>0.308</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
@@ -3057,10 +3127,10 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1818</v>
+        <v>1777</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>1790</v>
+        <v>1726</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>1599</v>
@@ -3069,10 +3139,10 @@
         <v>1504</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>1730</v>
+        <v>1706</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>1676</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="53" ht="6" customHeight="1">
@@ -3113,13 +3183,13 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.6509</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.1077</v>
+        <v>0.2103</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>0.2414</v>
+        <v>0.2398</v>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
@@ -3127,10 +3197,10 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1879</v>
+        <v>1856</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1723</v>
+        <v>1747</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>1730</v>
@@ -3139,10 +3209,10 @@
         <v>1533</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1819</v>
+        <v>1806</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1647</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="55">
@@ -3167,13 +3237,13 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0.7605</v>
+        <v>0.6513</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.1</v>
+        <v>0.184</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.1395</v>
+        <v>0.1647</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
@@ -3181,10 +3251,10 @@
         </is>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1863</v>
+        <v>1819</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>1572</v>
+        <v>1621</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>1595</v>
@@ -3193,10 +3263,10 @@
         <v>1295</v>
       </c>
       <c r="M55" s="10" t="n">
-        <v>1756</v>
+        <v>1730</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>1461</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="56" ht="6" customHeight="1">
@@ -3237,13 +3307,13 @@
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0.6977</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1833</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.2023</v>
+        <v>0.163</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
@@ -3251,10 +3321,10 @@
         </is>
       </c>
       <c r="I57" s="10" t="n">
-        <v>1878</v>
+        <v>1862</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>1681</v>
+        <v>1621</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>1758</v>
@@ -3263,10 +3333,10 @@
         <v>1515</v>
       </c>
       <c r="M57" s="10" t="n">
-        <v>1830</v>
+        <v>1820</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>1615</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="58">
@@ -3291,13 +3361,13 @@
         </is>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.2335</v>
+        <v>0.2014</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.1</v>
+        <v>0.197</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.6665</v>
+        <v>0.6016</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
@@ -3305,10 +3375,10 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1694</v>
+        <v>1720</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1880</v>
+        <v>1919</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>1483</v>
@@ -3317,10 +3387,10 @@
         <v>1660</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>1610</v>
+        <v>1625</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1792</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="59" ht="6" customHeight="1">
@@ -3361,13 +3431,13 @@
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0.4424</v>
+        <v>0.3954</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.2285</v>
+        <v>0.2516</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.329</v>
+        <v>0.353</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
@@ -3375,10 +3445,10 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1829</v>
+        <v>1804</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1823</v>
+        <v>1851</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>1735</v>
@@ -3387,10 +3457,10 @@
         <v>1615</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1740</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="61">
@@ -3415,13 +3485,13 @@
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.268</v>
+        <v>0.2533</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.1434</v>
+        <v>0.215</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.5886</v>
+        <v>0.5316</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
@@ -3429,10 +3499,10 @@
         </is>
       </c>
       <c r="I61" s="10" t="n">
-        <v>1698</v>
+        <v>1723</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>1739</v>
+        <v>1750</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>1282</v>
@@ -3441,10 +3511,10 @@
         <v>1563</v>
       </c>
       <c r="M61" s="10" t="n">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="N61" s="10" t="n">
-        <v>1669</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="62" ht="6" customHeight="1">
@@ -3485,13 +3555,13 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0.8123</v>
+        <v>0.7641</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1509</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>0.0877</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
@@ -3499,10 +3569,10 @@
         </is>
       </c>
       <c r="I63" s="10" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>1876</v>
@@ -3511,10 +3581,10 @@
         <v>1421</v>
       </c>
       <c r="M63" s="10" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>1575</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="64">
@@ -3539,13 +3609,13 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>0.7276</v>
+        <v>0.6458</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1854</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>0.1724</v>
+        <v>0.1687</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
@@ -3553,10 +3623,10 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1830</v>
+        <v>1793</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>1673</v>
@@ -3565,10 +3635,10 @@
         <v>1366</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>1767</v>
+        <v>1745</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1517</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="65" ht="6" customHeight="1">
@@ -3609,13 +3679,13 @@
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.7761</v>
+        <v>0.7115</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1672</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>0.1239</v>
+        <v>0.1213</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
@@ -3623,10 +3693,10 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>1967</v>
+        <v>1953</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1877</v>
@@ -3635,10 +3705,10 @@
         <v>1447</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="67">
@@ -3662,14 +3732,14 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n">
-        <v>0.309</v>
+      <c r="E67" s="8" t="n">
+        <v>0.2915</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.1993</v>
+        <v>0.2284</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>0.4918</v>
+        <v>0.4802</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
@@ -3677,10 +3747,10 @@
         </is>
       </c>
       <c r="I67" s="10" t="n">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>1822</v>
+        <v>1838</v>
       </c>
       <c r="K67" s="10" t="n">
         <v>1551</v>
@@ -3689,10 +3759,10 @@
         <v>1689</v>
       </c>
       <c r="M67" s="10" t="n">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="N67" s="10" t="n">
-        <v>1769</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="68" ht="6" customHeight="1">
@@ -3733,13 +3803,13 @@
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.7346</v>
+        <v>0.6731</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1781</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0.1654</v>
+        <v>0.1489</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
@@ -3747,10 +3817,10 @@
         </is>
       </c>
       <c r="I69" s="10" t="n">
-        <v>1983</v>
+        <v>1958</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>1739</v>
+        <v>1709</v>
       </c>
       <c r="K69" s="10" t="n">
         <v>1875</v>
@@ -3759,10 +3829,10 @@
         <v>1593</v>
       </c>
       <c r="M69" s="10" t="n">
-        <v>1940</v>
+        <v>1925</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>1681</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="70">
@@ -3787,13 +3857,13 @@
         </is>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0.2906</v>
+        <v>0.2794</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.1737</v>
+        <v>0.2241</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>0.5357</v>
+        <v>0.4964</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
@@ -3801,10 +3871,10 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1709</v>
+        <v>1751</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1771</v>
+        <v>1802</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>1391</v>
@@ -3813,10 +3883,10 @@
         <v>1564</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>1582</v>
+        <v>1607</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1688</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="71" ht="6" customHeight="1">
@@ -3857,13 +3927,13 @@
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>0.6642</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2108</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>0.2357</v>
+        <v>0.2412</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
@@ -3871,10 +3941,10 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1878</v>
+        <v>1846</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>1777</v>
+        <v>1808</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>1764</v>
@@ -3883,10 +3953,10 @@
         <v>1465</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>1832</v>
+        <v>1813</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>1652</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="73">
@@ -3911,13 +3981,13 @@
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.5685</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2056</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.2291</v>
+        <v>0.226</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
@@ -3925,10 +3995,10 @@
         </is>
       </c>
       <c r="I73" s="10" t="n">
-        <v>1861</v>
+        <v>1839</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>1693</v>
+        <v>1715</v>
       </c>
       <c r="K73" s="10" t="n">
         <v>1693</v>
@@ -3937,10 +4007,10 @@
         <v>1478</v>
       </c>
       <c r="M73" s="10" t="n">
-        <v>1794</v>
+        <v>1781</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>1607</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="74" ht="6" customHeight="1">
@@ -3981,13 +4051,13 @@
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>0.8128</v>
+        <v>0.7641</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1509</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.0872</v>
+        <v>0.0849</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
@@ -3995,10 +4065,10 @@
         </is>
       </c>
       <c r="I75" s="10" t="n">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="K75" s="10" t="n">
         <v>1826</v>
@@ -4007,10 +4077,10 @@
         <v>1346</v>
       </c>
       <c r="M75" s="10" t="n">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="N75" s="10" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="76">
@@ -4035,13 +4105,13 @@
         </is>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.2783</v>
+        <v>0.2746</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>0.1571</v>
+        <v>0.2224</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>0.5646</v>
+        <v>0.5029</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
@@ -4049,10 +4119,10 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>1846</v>
+        <v>1819</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>1541</v>
@@ -4061,10 +4131,10 @@
         <v>1717</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>1794</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="77" ht="6" customHeight="1">
@@ -4105,13 +4175,13 @@
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>0.639</v>
+        <v>0.5938</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>0.1145</v>
+        <v>0.199</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>0.2465</v>
+        <v>0.2071</v>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
@@ -4119,10 +4189,10 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1831</v>
+        <v>1816</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1675</v>
+        <v>1631</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>1681</v>
@@ -4131,10 +4201,10 @@
         <v>1501</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>1771</v>
+        <v>1762</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>1605</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="79">
@@ -4159,13 +4229,13 @@
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.2391</v>
+        <v>0.207</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>0.1046</v>
+        <v>0.199</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>0.6563</v>
+        <v>0.594</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
@@ -4173,10 +4243,10 @@
         </is>
       </c>
       <c r="I79" s="10" t="n">
-        <v>1629</v>
+        <v>1641</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>1815</v>
+        <v>1840</v>
       </c>
       <c r="K79" s="10" t="n">
         <v>1430</v>
@@ -4185,10 +4255,10 @@
         <v>1589</v>
       </c>
       <c r="M79" s="10" t="n">
-        <v>1549</v>
+        <v>1556</v>
       </c>
       <c r="N79" s="10" t="n">
-        <v>1725</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="80" ht="6" customHeight="1">
@@ -4229,13 +4299,13 @@
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0.3226</v>
+        <v>0.3277</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G81" s="6" t="n">
-        <v>0.4585</v>
+        <v>0.2417</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>0.4306</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
@@ -4243,10 +4313,10 @@
         </is>
       </c>
       <c r="I81" s="10" t="n">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>1811</v>
+        <v>1792</v>
       </c>
       <c r="K81" s="10" t="n">
         <v>1556</v>
@@ -4255,10 +4325,10 @@
         <v>1649</v>
       </c>
       <c r="M81" s="10" t="n">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="N81" s="10" t="n">
-        <v>1746</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="82">
@@ -4283,13 +4353,13 @@
         </is>
       </c>
       <c r="E82" s="7" t="n">
-        <v>0.3305</v>
+        <v>0.3011</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>0.4387</v>
+        <v>0.2318</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>0.467</v>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
@@ -4297,10 +4367,10 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>1597</v>
+        <v>1534</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>1633</v>
+        <v>1615</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>1386</v>
@@ -4309,10 +4379,10 @@
         <v>1455</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>1513</v>
+        <v>1475</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>1562</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="83" ht="6" customHeight="1">
@@ -4353,13 +4423,13 @@
         </is>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0.2111</v>
+        <v>0.1854</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1914</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>0.6889</v>
+        <v>0.6232</v>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
@@ -4367,10 +4437,10 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>1722</v>
+        <v>1686</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1889</v>
+        <v>1862</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>1498</v>
@@ -4379,10 +4449,10 @@
         <v>1761</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>1632</v>
+        <v>1611</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1838</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="85">
@@ -4407,13 +4477,13 @@
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>0.7825</v>
+        <v>0.7381</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1592</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.1175</v>
+        <v>0.1027</v>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
@@ -4421,10 +4491,10 @@
         </is>
       </c>
       <c r="I85" s="10" t="n">
-        <v>1876</v>
+        <v>1915</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>1637</v>
+        <v>1653</v>
       </c>
       <c r="K85" s="10" t="n">
         <v>1756</v>
@@ -4433,10 +4503,10 @@
         <v>1292</v>
       </c>
       <c r="M85" s="10" t="n">
-        <v>1828</v>
+        <v>1851</v>
       </c>
       <c r="N85" s="10" t="n">
-        <v>1499</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="86" ht="6" customHeight="1">
@@ -4477,13 +4547,13 @@
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>0.3658</v>
+        <v>0.4053</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>0.2762</v>
+        <v>0.2488</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0.3579</v>
+        <v>0.346</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
@@ -4491,10 +4561,10 @@
         </is>
       </c>
       <c r="I87" s="10" t="n">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>1818</v>
+        <v>1777</v>
       </c>
       <c r="K87" s="10" t="n">
         <v>1673</v>
@@ -4506,7 +4576,7 @@
         <v>1734</v>
       </c>
       <c r="N87" s="10" t="n">
-        <v>1730</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="88">
@@ -4530,14 +4600,14 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="E88" s="7" t="n">
-        <v>0.3277</v>
+      <c r="E88" s="8" t="n">
+        <v>0.27</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>0.2265</v>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>0.4458</v>
+        <v>0.2208</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>0.5092</v>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
@@ -4545,10 +4615,10 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1790</v>
+        <v>1726</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>1828</v>
+        <v>1858</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>1504</v>
@@ -4557,10 +4627,10 @@
         <v>1581</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>1676</v>
+        <v>1637</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>1729</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="89" ht="6" customHeight="1">
@@ -4601,13 +4671,13 @@
         </is>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0.2298</v>
+        <v>0.2172</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2026</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>0.6702</v>
+        <v>0.5802</v>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
@@ -4615,10 +4685,10 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>1572</v>
+        <v>1621</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>1723</v>
+        <v>1747</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>1295</v>
@@ -4627,10 +4697,10 @@
         <v>1533</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>1647</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="91">
@@ -4655,13 +4725,13 @@
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>0.3209</v>
+        <v>0.3013</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0.2164</v>
+        <v>0.2319</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>0.4627</v>
+        <v>0.4668</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
@@ -4669,10 +4739,10 @@
         </is>
       </c>
       <c r="I91" s="10" t="n">
-        <v>1863</v>
+        <v>1819</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>1879</v>
+        <v>1856</v>
       </c>
       <c r="K91" s="10" t="n">
         <v>1595</v>
@@ -4681,10 +4751,10 @@
         <v>1730</v>
       </c>
       <c r="M91" s="10" t="n">
-        <v>1756</v>
+        <v>1730</v>
       </c>
       <c r="N91" s="10" t="n">
-        <v>1819</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="92" ht="6" customHeight="1">
@@ -4725,13 +4795,13 @@
         </is>
       </c>
       <c r="E93" s="6" t="n">
-        <v>0.6596</v>
+        <v>0.649</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.1027</v>
+        <v>0.1846</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>0.2377</v>
+        <v>0.1664</v>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
@@ -4739,10 +4809,10 @@
         </is>
       </c>
       <c r="I93" s="10" t="n">
-        <v>1880</v>
+        <v>1919</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>1681</v>
+        <v>1621</v>
       </c>
       <c r="K93" s="10" t="n">
         <v>1660</v>
@@ -4751,10 +4821,10 @@
         <v>1515</v>
       </c>
       <c r="M93" s="10" t="n">
-        <v>1792</v>
+        <v>1815</v>
       </c>
       <c r="N93" s="10" t="n">
-        <v>1615</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="94">
@@ -4779,13 +4849,13 @@
         </is>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0.1979</v>
+        <v>0.1975</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1957</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.6068</v>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
@@ -4793,10 +4863,10 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>1694</v>
+        <v>1720</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>1878</v>
+        <v>1862</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>1483</v>
@@ -4805,10 +4875,10 @@
         <v>1758</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>1610</v>
+        <v>1625</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>1830</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="95" ht="6" customHeight="1">
@@ -4848,14 +4918,14 @@
           <t>Iran</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n">
-        <v>0.3156</v>
+      <c r="E96" s="8" t="n">
+        <v>0.2965</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0.2087</v>
+        <v>0.2302</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>0.4757</v>
+        <v>0.4733</v>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
@@ -4863,10 +4933,10 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1739</v>
+        <v>1750</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>1823</v>
+        <v>1851</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>1563</v>
@@ -4875,10 +4945,10 @@
         <v>1615</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>1669</v>
+        <v>1675</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>1740</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="97">
@@ -4903,13 +4973,13 @@
         </is>
       </c>
       <c r="E97" s="8" t="n">
-        <v>0.1651</v>
+        <v>0.1712</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1863</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>0.7349</v>
+        <v>0.6424</v>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
@@ -4917,10 +4987,10 @@
         </is>
       </c>
       <c r="I97" s="10" t="n">
-        <v>1698</v>
+        <v>1723</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>1829</v>
+        <v>1804</v>
       </c>
       <c r="K97" s="10" t="n">
         <v>1282</v>
@@ -4929,10 +4999,10 @@
         <v>1735</v>
       </c>
       <c r="M97" s="10" t="n">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="N97" s="10" t="n">
-        <v>1791</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="98" ht="6" customHeight="1">
@@ -4973,13 +5043,13 @@
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>0.325</v>
+        <v>0.3107</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.2226</v>
+        <v>0.2353</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>0.4524</v>
+        <v>0.454</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
@@ -4987,10 +5057,10 @@
         </is>
       </c>
       <c r="I99" s="10" t="n">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="K99" s="10" t="n">
         <v>1366</v>
@@ -4999,10 +5069,10 @@
         <v>1421</v>
       </c>
       <c r="M99" s="10" t="n">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="N99" s="10" t="n">
-        <v>1575</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="100">
@@ -5027,13 +5097,13 @@
         </is>
       </c>
       <c r="E100" s="8" t="n">
-        <v>0.222</v>
+        <v>0.1826</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1904</v>
       </c>
       <c r="G100" s="6" t="n">
-        <v>0.678</v>
+        <v>0.627</v>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
@@ -5041,10 +5111,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1830</v>
+        <v>1793</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>1673</v>
@@ -5053,10 +5123,10 @@
         <v>1876</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>1767</v>
+        <v>1745</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="101" ht="6" customHeight="1">
@@ -5097,13 +5167,13 @@
         </is>
       </c>
       <c r="E102" s="8" t="n">
-        <v>0.1782</v>
+        <v>0.1704</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>0.1</v>
+        <v>0.186</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>0.7218</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
@@ -5111,10 +5181,10 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>1967</v>
+        <v>1953</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>1551</v>
@@ -5123,10 +5193,10 @@
         <v>1877</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>1931</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="103">
@@ -5151,13 +5221,13 @@
         </is>
       </c>
       <c r="E103" s="6" t="n">
-        <v>0.6232</v>
+        <v>0.5717</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>0.1236</v>
+        <v>0.2047</v>
       </c>
       <c r="G103" s="8" t="n">
-        <v>0.2532</v>
+        <v>0.2235</v>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
@@ -5165,10 +5235,10 @@
         </is>
       </c>
       <c r="I103" s="10" t="n">
-        <v>1822</v>
+        <v>1838</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="K103" s="10" t="n">
         <v>1689</v>
@@ -5177,10 +5247,10 @@
         <v>1447</v>
       </c>
       <c r="M103" s="10" t="n">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="N103" s="10" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="104" ht="6" customHeight="1">
@@ -5221,13 +5291,13 @@
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0.3711</v>
+        <v>0.4262</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.2728</v>
+        <v>0.2429</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.3561</v>
+        <v>0.3309</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
@@ -5235,10 +5305,10 @@
         </is>
       </c>
       <c r="I105" s="10" t="n">
-        <v>1771</v>
+        <v>1802</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>1739</v>
+        <v>1709</v>
       </c>
       <c r="K105" s="10" t="n">
         <v>1564</v>
@@ -5247,10 +5317,10 @@
         <v>1593</v>
       </c>
       <c r="M105" s="10" t="n">
-        <v>1688</v>
+        <v>1707</v>
       </c>
       <c r="N105" s="10" t="n">
-        <v>1681</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="106">
@@ -5275,13 +5345,13 @@
         </is>
       </c>
       <c r="E106" s="8" t="n">
-        <v>0.1016</v>
+        <v>0.1154</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1648</v>
       </c>
       <c r="G106" s="6" t="n">
-        <v>0.7984</v>
+        <v>0.7198</v>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
@@ -5289,10 +5359,10 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1709</v>
+        <v>1751</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>1983</v>
+        <v>1958</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>1391</v>
@@ -5301,10 +5371,10 @@
         <v>1875</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>1582</v>
+        <v>1607</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>1940</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="107" ht="6" customHeight="1">
@@ -5345,13 +5415,13 @@
         </is>
       </c>
       <c r="E108" s="7" t="n">
-        <v>0.3374</v>
+        <v>0.3414</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>0.2415</v>
+        <v>0.247</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>0.4211</v>
+        <v>0.4116</v>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
@@ -5359,10 +5429,10 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>1861</v>
+        <v>1839</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>1878</v>
+        <v>1846</v>
       </c>
       <c r="K108" s="4" t="n">
         <v>1693</v>
@@ -5371,10 +5441,10 @@
         <v>1764</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>1794</v>
+        <v>1781</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>1832</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="109">
@@ -5399,13 +5469,13 @@
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>0.3331</v>
+        <v>0.3252</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>0.2348</v>
+        <v>0.2407</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.4321</v>
+        <v>0.4341</v>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
@@ -5413,10 +5483,10 @@
         </is>
       </c>
       <c r="I109" s="10" t="n">
-        <v>1693</v>
+        <v>1715</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>1777</v>
+        <v>1808</v>
       </c>
       <c r="K109" s="10" t="n">
         <v>1478</v>
@@ -5425,10 +5495,10 @@
         <v>1465</v>
       </c>
       <c r="M109" s="10" t="n">
-        <v>1607</v>
+        <v>1620</v>
       </c>
       <c r="N109" s="10" t="n">
-        <v>1652</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="110" ht="6" customHeight="1">
@@ -5469,13 +5539,13 @@
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>0.2013</v>
+        <v>0.1808</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1898</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>0.6987</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
@@ -5483,10 +5553,10 @@
         </is>
       </c>
       <c r="I111" s="10" t="n">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="K111" s="10" t="n">
         <v>1541</v>
@@ -5495,10 +5565,10 @@
         <v>1826</v>
       </c>
       <c r="M111" s="10" t="n">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="N111" s="10" t="n">
-        <v>1887</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="112">
@@ -5523,13 +5593,13 @@
         </is>
       </c>
       <c r="E112" s="6" t="n">
-        <v>0.7605</v>
+        <v>0.6801</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>0.1</v>
+        <v>0.1761</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>0.1395</v>
+        <v>0.1438</v>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
@@ -5537,10 +5607,10 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>1846</v>
+        <v>1819</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>1717</v>
@@ -5549,10 +5619,10 @@
         <v>1346</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>1794</v>
+        <v>1778</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="113" ht="8" customHeight="1"/>
@@ -5831,19 +5901,19 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>1771</v>
+        <v>1762</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.459</v>
+        <v>0.4552</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.3006</v>
+        <v>0.295</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1642</v>
+        <v>0.1664</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.07619999999999993</v>
+        <v>0.08339999999999997</v>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
@@ -5859,19 +5929,19 @@
         </is>
       </c>
       <c r="M5" s="17" t="n">
-        <v>1746</v>
+        <v>1735</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.4804</v>
+        <v>0.4888</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>0.294</v>
+        <v>0.3072</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.1494</v>
+        <v>0.141</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>0.07620000000000007</v>
+        <v>0.06300000000000003</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -5883,23 +5953,23 @@
       </c>
       <c r="V5" s="18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="W5" s="17" t="n">
-        <v>1734</v>
+        <v>1747</v>
       </c>
       <c r="X5" s="19" t="n">
-        <v>0.2898</v>
+        <v>0.3258</v>
       </c>
       <c r="Y5" s="19" t="n">
-        <v>0.2746</v>
+        <v>0.2806</v>
       </c>
       <c r="Z5" s="19" t="n">
-        <v>0.2244</v>
+        <v>0.2328</v>
       </c>
       <c r="AA5" s="19" t="n">
-        <v>0.2111999999999999</v>
+        <v>0.1608</v>
       </c>
       <c r="AB5" s="17" t="inlineStr">
         <is>
@@ -5911,23 +5981,23 @@
       </c>
       <c r="AF5" s="18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="AG5" s="17" t="n">
-        <v>1838</v>
+        <v>1851</v>
       </c>
       <c r="AH5" s="19" t="n">
-        <v>0.456</v>
+        <v>0.5342</v>
       </c>
       <c r="AI5" s="19" t="n">
-        <v>0.3498</v>
+        <v>0.3072</v>
       </c>
       <c r="AJ5" s="19" t="n">
-        <v>0.1472</v>
+        <v>0.1276</v>
       </c>
       <c r="AK5" s="19" t="n">
-        <v>0.04700000000000004</v>
+        <v>0.03100000000000003</v>
       </c>
       <c r="AL5" s="17" t="inlineStr">
         <is>
@@ -5945,19 +6015,19 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>1725</v>
+        <v>1739</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>0.3272</v>
+        <v>0.3562</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0.3258</v>
+        <v>0.3322</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0.2242</v>
+        <v>0.1938</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0.1228000000000001</v>
+        <v>0.1177999999999999</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
@@ -5973,19 +6043,19 @@
         </is>
       </c>
       <c r="M6" s="20" t="n">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>0.328</v>
+        <v>0.3488</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>0.3368</v>
+        <v>0.3536</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>0.2184</v>
+        <v>0.2006</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>0.1167999999999999</v>
+        <v>0.09699999999999998</v>
       </c>
       <c r="R6" s="20" t="inlineStr">
         <is>
@@ -5997,23 +6067,23 @@
       </c>
       <c r="V6" s="21" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="W6" s="20" t="n">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="X6" s="22" t="n">
-        <v>0.2738</v>
+        <v>0.2832</v>
       </c>
       <c r="Y6" s="22" t="n">
-        <v>0.2534</v>
+        <v>0.272</v>
       </c>
       <c r="Z6" s="22" t="n">
-        <v>0.2504</v>
+        <v>0.2454</v>
       </c>
       <c r="AA6" s="22" t="n">
-        <v>0.2223999999999999</v>
+        <v>0.1994</v>
       </c>
       <c r="AB6" s="20" t="inlineStr">
         <is>
@@ -6025,23 +6095,23 @@
       </c>
       <c r="AF6" s="21" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="AG6" s="20" t="n">
-        <v>1828</v>
+        <v>1821</v>
       </c>
       <c r="AH6" s="22" t="n">
-        <v>0.4282</v>
+        <v>0.3544</v>
       </c>
       <c r="AI6" s="22" t="n">
-        <v>0.371</v>
+        <v>0.4116</v>
       </c>
       <c r="AJ6" s="22" t="n">
-        <v>0.1556</v>
+        <v>0.171</v>
       </c>
       <c r="AK6" s="22" t="n">
-        <v>0.04519999999999999</v>
+        <v>0.06299999999999992</v>
       </c>
       <c r="AL6" s="20" t="inlineStr">
         <is>
@@ -6059,19 +6129,19 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>1605</v>
+        <v>1579</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.1364</v>
+        <v>0.1086</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>0.2238</v>
+        <v>0.211</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.3202</v>
+        <v>0.3224</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.3196000000000001</v>
+        <v>0.358</v>
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
@@ -6087,19 +6157,19 @@
         </is>
       </c>
       <c r="M7" s="23" t="n">
-        <v>1562</v>
+        <v>1551</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.1138</v>
+        <v>0.0958</v>
       </c>
       <c r="O7" s="25" t="n">
-        <v>0.2168</v>
+        <v>0.1948</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>0.3476</v>
+        <v>0.348</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>0.3218</v>
+        <v>0.3614000000000001</v>
       </c>
       <c r="R7" s="26" t="inlineStr">
         <is>
@@ -6111,23 +6181,23 @@
       </c>
       <c r="V7" s="24" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="W7" s="23" t="n">
-        <v>1729</v>
+        <v>1706</v>
       </c>
       <c r="X7" s="25" t="n">
-        <v>0.2592</v>
+        <v>0.272</v>
       </c>
       <c r="Y7" s="25" t="n">
-        <v>0.2634</v>
+        <v>0.2744</v>
       </c>
       <c r="Z7" s="25" t="n">
-        <v>0.251</v>
+        <v>0.2522</v>
       </c>
       <c r="AA7" s="25" t="n">
-        <v>0.2264</v>
+        <v>0.2014</v>
       </c>
       <c r="AB7" s="26" t="inlineStr">
         <is>
@@ -6143,19 +6213,19 @@
         </is>
       </c>
       <c r="AG7" s="23" t="n">
-        <v>1632</v>
+        <v>1611</v>
       </c>
       <c r="AH7" s="25" t="n">
-        <v>0.0906</v>
+        <v>0.079</v>
       </c>
       <c r="AI7" s="25" t="n">
-        <v>0.2076</v>
+        <v>0.1758</v>
       </c>
       <c r="AJ7" s="25" t="n">
-        <v>0.4404</v>
+        <v>0.404</v>
       </c>
       <c r="AK7" s="25" t="n">
-        <v>0.2614</v>
+        <v>0.3412000000000001</v>
       </c>
       <c r="AL7" s="26" t="inlineStr">
         <is>
@@ -6173,19 +6243,19 @@
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>1549</v>
+        <v>1556</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.0774</v>
+        <v>0.08</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.1498</v>
+        <v>0.1618</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.2914</v>
+        <v>0.3174</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.4813999999999999</v>
+        <v>0.4408</v>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
@@ -6201,19 +6271,19 @@
         </is>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1513</v>
+        <v>1475</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>0.1524</v>
+        <v>0.1444</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.2846</v>
+        <v>0.3104</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>0.4852</v>
+        <v>0.4786</v>
       </c>
       <c r="R8" s="30" t="inlineStr">
         <is>
@@ -6229,19 +6299,19 @@
         </is>
       </c>
       <c r="W8" s="27" t="n">
-        <v>1676</v>
+        <v>1637</v>
       </c>
       <c r="X8" s="29" t="n">
-        <v>0.1772</v>
+        <v>0.119</v>
       </c>
       <c r="Y8" s="29" t="n">
-        <v>0.2086</v>
+        <v>0.173</v>
       </c>
       <c r="Z8" s="29" t="n">
-        <v>0.2742</v>
+        <v>0.2696</v>
       </c>
       <c r="AA8" s="29" t="n">
-        <v>0.34</v>
+        <v>0.4384</v>
       </c>
       <c r="AB8" s="30" t="inlineStr">
         <is>
@@ -6257,19 +6327,19 @@
         </is>
       </c>
       <c r="AG8" s="27" t="n">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="AH8" s="29" t="n">
-        <v>0.0252</v>
+        <v>0.0324</v>
       </c>
       <c r="AI8" s="29" t="n">
-        <v>0.0716</v>
+        <v>0.1054</v>
       </c>
       <c r="AJ8" s="29" t="n">
-        <v>0.2568</v>
+        <v>0.2974</v>
       </c>
       <c r="AK8" s="29" t="n">
-        <v>0.6464000000000001</v>
+        <v>0.5648000000000001</v>
       </c>
       <c r="AL8" s="30" t="inlineStr">
         <is>
@@ -6471,19 +6541,19 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1819</v>
+        <v>1806</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.4894</v>
+        <v>0.5806</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.3084</v>
+        <v>0.2548</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.16</v>
+        <v>0.1232</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.04219999999999993</v>
+        <v>0.04139999999999996</v>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -6499,19 +6569,19 @@
         </is>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1830</v>
+        <v>1820</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>0.4808</v>
+        <v>0.4398</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>0.3028</v>
+        <v>0.3424</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>0.153</v>
+        <v>0.157</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>0.06339999999999998</v>
+        <v>0.06080000000000005</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -6527,19 +6597,19 @@
         </is>
       </c>
       <c r="W13" s="17" t="n">
-        <v>1791</v>
+        <v>1776</v>
       </c>
       <c r="X13" s="19" t="n">
-        <v>0.4508</v>
+        <v>0.4516</v>
       </c>
       <c r="Y13" s="19" t="n">
-        <v>0.3068</v>
+        <v>0.2904</v>
       </c>
       <c r="Z13" s="19" t="n">
-        <v>0.1716</v>
+        <v>0.187</v>
       </c>
       <c r="AA13" s="19" t="n">
-        <v>0.0708</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="AB13" s="17" t="inlineStr">
         <is>
@@ -6555,19 +6625,19 @@
         </is>
       </c>
       <c r="AG13" s="17" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="AH13" s="19" t="n">
-        <v>0.7238</v>
+        <v>0.7786</v>
       </c>
       <c r="AI13" s="19" t="n">
-        <v>0.2144</v>
+        <v>0.1714</v>
       </c>
       <c r="AJ13" s="19" t="n">
-        <v>0.0524</v>
+        <v>0.0392</v>
       </c>
       <c r="AK13" s="19" t="n">
-        <v>0.009399999999999992</v>
+        <v>0.01080000000000005</v>
       </c>
       <c r="AL13" s="17" t="inlineStr">
         <is>
@@ -6585,19 +6655,19 @@
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>1756</v>
+        <v>1730</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0.323</v>
+        <v>0.212</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0.3582</v>
+        <v>0.3334</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.2436</v>
+        <v>0.313</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.07520000000000002</v>
+        <v>0.1416000000000001</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
@@ -6613,19 +6683,19 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>1792</v>
+        <v>1815</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.358</v>
+        <v>0.4358</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>0.347</v>
+        <v>0.3562</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.198</v>
+        <v>0.1498</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>0.09700000000000003</v>
+        <v>0.05820000000000003</v>
       </c>
       <c r="R14" s="20" t="inlineStr">
         <is>
@@ -6641,19 +6711,19 @@
         </is>
       </c>
       <c r="W14" s="20" t="n">
-        <v>1740</v>
+        <v>1756</v>
       </c>
       <c r="X14" s="22" t="n">
-        <v>0.3082</v>
+        <v>0.3182</v>
       </c>
       <c r="Y14" s="22" t="n">
-        <v>0.321</v>
+        <v>0.3302</v>
       </c>
       <c r="Z14" s="22" t="n">
-        <v>0.244</v>
+        <v>0.2362</v>
       </c>
       <c r="AA14" s="22" t="n">
-        <v>0.1268</v>
+        <v>0.1154</v>
       </c>
       <c r="AB14" s="20" t="inlineStr">
         <is>
@@ -6669,19 +6739,19 @@
         </is>
       </c>
       <c r="AG14" s="20" t="n">
-        <v>1767</v>
+        <v>1745</v>
       </c>
       <c r="AH14" s="22" t="n">
-        <v>0.2142</v>
+        <v>0.1622</v>
       </c>
       <c r="AI14" s="22" t="n">
-        <v>0.4886</v>
+        <v>0.4998</v>
       </c>
       <c r="AJ14" s="22" t="n">
-        <v>0.2114</v>
+        <v>0.2414</v>
       </c>
       <c r="AK14" s="22" t="n">
-        <v>0.08580000000000007</v>
+        <v>0.09659999999999996</v>
       </c>
       <c r="AL14" s="20" t="inlineStr">
         <is>
@@ -6699,19 +6769,19 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>1647</v>
+        <v>1662</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.1618</v>
+        <v>0.178</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.2606</v>
+        <v>0.324</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.3932</v>
+        <v>0.3428</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>0.1844000000000001</v>
+        <v>0.1552000000000001</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -6723,23 +6793,23 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="M15" s="23" t="n">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="N15" s="25" t="n">
-        <v>0.0828</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="O15" s="25" t="n">
-        <v>0.1862</v>
+        <v>0.1726</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>0.3262</v>
+        <v>0.3948</v>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>0.4048</v>
+        <v>0.3568000000000001</v>
       </c>
       <c r="R15" s="26" t="inlineStr">
         <is>
@@ -6755,19 +6825,19 @@
         </is>
       </c>
       <c r="W15" s="23" t="n">
-        <v>1669</v>
+        <v>1675</v>
       </c>
       <c r="X15" s="25" t="n">
-        <v>0.1868</v>
+        <v>0.1874</v>
       </c>
       <c r="Y15" s="25" t="n">
-        <v>0.2582</v>
+        <v>0.2598</v>
       </c>
       <c r="Z15" s="25" t="n">
-        <v>0.3368</v>
+        <v>0.3316</v>
       </c>
       <c r="AA15" s="25" t="n">
-        <v>0.2182000000000001</v>
+        <v>0.2212</v>
       </c>
       <c r="AB15" s="26" t="inlineStr">
         <is>
@@ -6783,19 +6853,19 @@
         </is>
       </c>
       <c r="AG15" s="23" t="n">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="AH15" s="25" t="n">
-        <v>0.0404</v>
+        <v>0.0364</v>
       </c>
       <c r="AI15" s="25" t="n">
-        <v>0.1802</v>
+        <v>0.193</v>
       </c>
       <c r="AJ15" s="25" t="n">
-        <v>0.4034</v>
+        <v>0.3892</v>
       </c>
       <c r="AK15" s="25" t="n">
-        <v>0.376</v>
+        <v>0.3814</v>
       </c>
       <c r="AL15" s="26" t="inlineStr">
         <is>
@@ -6813,19 +6883,19 @@
         </is>
       </c>
       <c r="C16" s="27" t="n">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.0258</v>
+        <v>0.0294</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>0.0728</v>
+        <v>0.0878</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>0.2032</v>
+        <v>0.221</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.6981999999999999</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
@@ -6837,23 +6907,23 @@
       </c>
       <c r="L16" s="28" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1610</v>
+        <v>1579</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.0784</v>
+        <v>0.0486</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.164</v>
+        <v>0.1288</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>0.3228</v>
+        <v>0.2984</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>0.4348</v>
+        <v>0.5242</v>
       </c>
       <c r="R16" s="30" t="inlineStr">
         <is>
@@ -6869,19 +6939,19 @@
         </is>
       </c>
       <c r="W16" s="27" t="n">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="X16" s="29" t="n">
-        <v>0.0542</v>
+        <v>0.0428</v>
       </c>
       <c r="Y16" s="29" t="n">
-        <v>0.114</v>
+        <v>0.1196</v>
       </c>
       <c r="Z16" s="29" t="n">
-        <v>0.2476</v>
+        <v>0.2452</v>
       </c>
       <c r="AA16" s="29" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5924</v>
       </c>
       <c r="AB16" s="30" t="inlineStr">
         <is>
@@ -6897,19 +6967,19 @@
         </is>
       </c>
       <c r="AG16" s="27" t="n">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="AH16" s="29" t="n">
-        <v>0.0216</v>
+        <v>0.0228</v>
       </c>
       <c r="AI16" s="29" t="n">
-        <v>0.1168</v>
+        <v>0.1358</v>
       </c>
       <c r="AJ16" s="29" t="n">
-        <v>0.3328</v>
+        <v>0.3302</v>
       </c>
       <c r="AK16" s="29" t="n">
-        <v>0.5288</v>
+        <v>0.5111999999999999</v>
       </c>
       <c r="AL16" s="30" t="inlineStr">
         <is>
@@ -7111,19 +7181,19 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.6276</v>
+        <v>0.588</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.2318</v>
+        <v>0.2676</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.1032</v>
+        <v>0.1088</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.03739999999999995</v>
+        <v>0.03560000000000003</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -7139,19 +7209,19 @@
         </is>
       </c>
       <c r="M21" s="17" t="n">
-        <v>1940</v>
+        <v>1925</v>
       </c>
       <c r="N21" s="19" t="n">
-        <v>0.7128</v>
+        <v>0.681</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>0.1916</v>
+        <v>0.2132</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>0.0726</v>
+        <v>0.081</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>0.02300000000000002</v>
+        <v>0.02479999999999995</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -7167,19 +7237,19 @@
         </is>
       </c>
       <c r="W21" s="17" t="n">
-        <v>1832</v>
+        <v>1813</v>
       </c>
       <c r="X21" s="19" t="n">
-        <v>0.469</v>
+        <v>0.4714</v>
       </c>
       <c r="Y21" s="19" t="n">
-        <v>0.3074</v>
+        <v>0.2778</v>
       </c>
       <c r="Z21" s="19" t="n">
-        <v>0.1518</v>
+        <v>0.158</v>
       </c>
       <c r="AA21" s="19" t="n">
-        <v>0.07180000000000003</v>
+        <v>0.09279999999999997</v>
       </c>
       <c r="AB21" s="17" t="inlineStr">
         <is>
@@ -7195,19 +7265,19 @@
         </is>
       </c>
       <c r="AG21" s="17" t="n">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="AH21" s="19" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AI21" s="19" t="n">
-        <v>0.2878</v>
+        <v>0.2884</v>
       </c>
       <c r="AJ21" s="19" t="n">
-        <v>0.1226</v>
+        <v>0.1264</v>
       </c>
       <c r="AK21" s="19" t="n">
-        <v>0.03159999999999995</v>
+        <v>0.02819999999999995</v>
       </c>
       <c r="AL21" s="17" t="inlineStr">
         <is>
@@ -7225,19 +7295,19 @@
         </is>
       </c>
       <c r="C22" s="20" t="n">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0.2106</v>
+        <v>0.256</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0.3704</v>
+        <v>0.3654</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>0.257</v>
+        <v>0.2492</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0.162</v>
+        <v>0.1294</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -7253,19 +7323,19 @@
         </is>
       </c>
       <c r="M22" s="20" t="n">
-        <v>1688</v>
+        <v>1707</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>0.1222</v>
+        <v>0.1536</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>0.3324</v>
+        <v>0.3404</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.305</v>
+        <v>0.2988</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0.2404000000000001</v>
+        <v>0.2072</v>
       </c>
       <c r="R22" s="20" t="inlineStr">
         <is>
@@ -7281,19 +7351,19 @@
         </is>
       </c>
       <c r="W22" s="20" t="n">
-        <v>1794</v>
+        <v>1781</v>
       </c>
       <c r="X22" s="22" t="n">
-        <v>0.3492</v>
+        <v>0.3</v>
       </c>
       <c r="Y22" s="22" t="n">
-        <v>0.3332</v>
+        <v>0.3236</v>
       </c>
       <c r="Z22" s="22" t="n">
-        <v>0.21</v>
+        <v>0.224</v>
       </c>
       <c r="AA22" s="22" t="n">
-        <v>0.1076000000000001</v>
+        <v>0.1524</v>
       </c>
       <c r="AB22" s="20" t="inlineStr">
         <is>
@@ -7309,19 +7379,19 @@
         </is>
       </c>
       <c r="AG22" s="20" t="n">
-        <v>1794</v>
+        <v>1778</v>
       </c>
       <c r="AH22" s="22" t="n">
-        <v>0.2936</v>
+        <v>0.298</v>
       </c>
       <c r="AI22" s="22" t="n">
-        <v>0.381</v>
+        <v>0.3812</v>
       </c>
       <c r="AJ22" s="22" t="n">
-        <v>0.2394</v>
+        <v>0.2392</v>
       </c>
       <c r="AK22" s="22" t="n">
-        <v>0.08599999999999991</v>
+        <v>0.08159999999999998</v>
       </c>
       <c r="AL22" s="20" t="inlineStr">
         <is>
@@ -7339,19 +7409,19 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.1084</v>
+        <v>0.1062</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0.2448</v>
+        <v>0.2262</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>0.3482</v>
+        <v>0.3658</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>0.2985999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -7367,19 +7437,19 @@
         </is>
       </c>
       <c r="M23" s="23" t="n">
-        <v>1681</v>
+        <v>1663</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>0.1168</v>
+        <v>0.1122</v>
       </c>
       <c r="O23" s="25" t="n">
-        <v>0.3096</v>
+        <v>0.2822</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.3242</v>
+        <v>0.3406</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>0.2494</v>
+        <v>0.265</v>
       </c>
       <c r="R23" s="26" t="inlineStr">
         <is>
@@ -7395,19 +7465,19 @@
         </is>
       </c>
       <c r="W23" s="23" t="n">
-        <v>1652</v>
+        <v>1671</v>
       </c>
       <c r="X23" s="25" t="n">
-        <v>0.1074</v>
+        <v>0.132</v>
       </c>
       <c r="Y23" s="25" t="n">
-        <v>0.2038</v>
+        <v>0.2282</v>
       </c>
       <c r="Z23" s="25" t="n">
-        <v>0.353</v>
+        <v>0.3198</v>
       </c>
       <c r="AA23" s="25" t="n">
-        <v>0.3358000000000001</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="AB23" s="26" t="inlineStr">
         <is>
@@ -7423,19 +7493,19 @@
         </is>
       </c>
       <c r="AG23" s="23" t="n">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="AH23" s="25" t="n">
-        <v>0.1264</v>
+        <v>0.1244</v>
       </c>
       <c r="AI23" s="25" t="n">
-        <v>0.2474</v>
+        <v>0.2574</v>
       </c>
       <c r="AJ23" s="25" t="n">
-        <v>0.4104</v>
+        <v>0.412</v>
       </c>
       <c r="AK23" s="25" t="n">
-        <v>0.2157999999999999</v>
+        <v>0.2062000000000001</v>
       </c>
       <c r="AL23" s="26" t="inlineStr">
         <is>
@@ -7453,19 +7523,19 @@
         </is>
       </c>
       <c r="C24" s="27" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>0.0534</v>
+        <v>0.0498</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>0.153</v>
+        <v>0.1408</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0.2916</v>
+        <v>0.2762</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>0.502</v>
+        <v>0.5332</v>
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
@@ -7481,19 +7551,19 @@
         </is>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1582</v>
+        <v>1607</v>
       </c>
       <c r="N24" s="29" t="n">
-        <v>0.0482</v>
+        <v>0.0532</v>
       </c>
       <c r="O24" s="29" t="n">
-        <v>0.1664</v>
+        <v>0.1642</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.2982</v>
+        <v>0.2796</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>0.4872</v>
+        <v>0.5029999999999999</v>
       </c>
       <c r="R24" s="30" t="inlineStr">
         <is>
@@ -7509,19 +7579,19 @@
         </is>
       </c>
       <c r="W24" s="27" t="n">
-        <v>1607</v>
+        <v>1620</v>
       </c>
       <c r="X24" s="29" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="Y24" s="29" t="n">
-        <v>0.1556</v>
+        <v>0.1704</v>
       </c>
       <c r="Z24" s="29" t="n">
-        <v>0.2852</v>
+        <v>0.2982</v>
       </c>
       <c r="AA24" s="29" t="n">
-        <v>0.4848</v>
+        <v>0.4348</v>
       </c>
       <c r="AB24" s="30" t="inlineStr">
         <is>
@@ -7537,19 +7607,19 @@
         </is>
       </c>
       <c r="AG24" s="27" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="AH24" s="29" t="n">
-        <v>0.022</v>
+        <v>0.0206</v>
       </c>
       <c r="AI24" s="29" t="n">
-        <v>0.0838</v>
+        <v>0.073</v>
       </c>
       <c r="AJ24" s="29" t="n">
-        <v>0.2276</v>
+        <v>0.2224</v>
       </c>
       <c r="AK24" s="29" t="n">
-        <v>0.6666</v>
+        <v>0.6840000000000002</v>
       </c>
       <c r="AL24" s="30" t="inlineStr">
         <is>
@@ -7656,7 +7726,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="E3" s="33" t="inlineStr">
         <is>
@@ -7664,7 +7734,7 @@
         </is>
       </c>
       <c r="F3" s="35" t="n">
-        <v>0.306</v>
+        <v>0.303</v>
       </c>
       <c r="G3" s="36" t="inlineStr">
         <is>
@@ -7689,7 +7759,7 @@
         </is>
       </c>
       <c r="D4" s="34" t="n">
-        <v>0.394</v>
+        <v>0.376</v>
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
@@ -7697,11 +7767,11 @@
         </is>
       </c>
       <c r="F4" s="35" t="n">
-        <v>0.348</v>
+        <v>0.366</v>
       </c>
       <c r="G4" s="36" t="inlineStr">
         <is>
-          <t>→ Switzerland</t>
+          <t>→ South Korea</t>
         </is>
       </c>
     </row>
@@ -7718,23 +7788,23 @@
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D5" s="34" t="n">
-        <v>0.521</v>
+        <v>0.464</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F5" s="35" t="n">
-        <v>0.297</v>
+        <v>0.303</v>
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
-          <t>→ Morocco</t>
+          <t>→ Brazil</t>
         </is>
       </c>
     </row>
@@ -7751,23 +7821,23 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.54</v>
+        <v>0.551</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.289</v>
+        <v>0.239</v>
       </c>
       <c r="G6" s="36" t="inlineStr">
         <is>
-          <t>→ Brazil</t>
+          <t>→ Morocco</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7858,7 @@
         </is>
       </c>
       <c r="D7" s="34" t="n">
-        <v>0.403</v>
+        <v>0.382</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
@@ -7796,11 +7866,11 @@
         </is>
       </c>
       <c r="F7" s="35" t="n">
-        <v>0.344</v>
+        <v>0.362</v>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>→ Germany</t>
+          <t>→ Japan</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7891,7 @@
         </is>
       </c>
       <c r="D8" s="34" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
@@ -7829,7 +7899,7 @@
         </is>
       </c>
       <c r="F8" s="35" t="n">
-        <v>0.314</v>
+        <v>0.288</v>
       </c>
       <c r="G8" s="36" t="inlineStr">
         <is>
@@ -7854,7 +7924,7 @@
         </is>
       </c>
       <c r="D9" s="34" t="n">
-        <v>0.398</v>
+        <v>0.41</v>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
@@ -7862,7 +7932,7 @@
         </is>
       </c>
       <c r="F9" s="35" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="G9" s="36" t="inlineStr">
         <is>
@@ -7887,7 +7957,7 @@
         </is>
       </c>
       <c r="D10" s="34" t="n">
-        <v>0.703</v>
+        <v>0.615</v>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
@@ -7895,7 +7965,7 @@
         </is>
       </c>
       <c r="F10" s="35" t="n">
-        <v>0.197</v>
+        <v>0.191</v>
       </c>
       <c r="G10" s="36" t="inlineStr">
         <is>
@@ -7920,7 +7990,7 @@
         </is>
       </c>
       <c r="D11" s="34" t="n">
-        <v>0.722</v>
+        <v>0.629</v>
       </c>
       <c r="E11" s="33" t="inlineStr">
         <is>
@@ -7928,7 +7998,7 @@
         </is>
       </c>
       <c r="F11" s="35" t="n">
-        <v>0.178</v>
+        <v>0.181</v>
       </c>
       <c r="G11" s="36" t="inlineStr">
         <is>
@@ -7953,7 +8023,7 @@
         </is>
       </c>
       <c r="D12" s="34" t="n">
-        <v>0.648</v>
+        <v>0.552</v>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
@@ -7961,7 +8031,7 @@
         </is>
       </c>
       <c r="F12" s="35" t="n">
-        <v>0.242</v>
+        <v>0.238</v>
       </c>
       <c r="G12" s="36" t="inlineStr">
         <is>
@@ -7986,7 +8056,7 @@
         </is>
       </c>
       <c r="D13" s="34" t="n">
-        <v>0.42</v>
+        <v>0.415</v>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
@@ -7994,7 +8064,7 @@
         </is>
       </c>
       <c r="F13" s="35" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="G13" s="36" t="inlineStr">
         <is>
@@ -8019,7 +8089,7 @@
         </is>
       </c>
       <c r="D14" s="34" t="n">
-        <v>0.514</v>
+        <v>0.508</v>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
@@ -8027,7 +8097,7 @@
         </is>
       </c>
       <c r="F14" s="35" t="n">
-        <v>0.3</v>
+        <v>0.271</v>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
@@ -8048,23 +8118,23 @@
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="D15" s="34" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
       <c r="F15" s="35" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="G15" s="36" t="inlineStr">
         <is>
-          <t>→ Turkey</t>
+          <t>→ Australia</t>
         </is>
       </c>
     </row>
@@ -8081,23 +8151,23 @@
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.624</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F16" s="35" t="n">
-        <v>0.253</v>
+        <v>0.227</v>
       </c>
       <c r="G16" s="36" t="inlineStr">
         <is>
-          <t>→ Brazil</t>
+          <t>→ Morocco</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8188,15 @@
         </is>
       </c>
       <c r="D17" s="34" t="n">
-        <v>0.552</v>
+        <v>0.498</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F17" s="35" t="n">
-        <v>0.284</v>
+        <v>0.278</v>
       </c>
       <c r="G17" s="36" t="inlineStr">
         <is>
@@ -8151,7 +8221,7 @@
         </is>
       </c>
       <c r="D18" s="34" t="n">
-        <v>0.757</v>
+        <v>0.6940000000000001</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
@@ -8159,7 +8229,7 @@
         </is>
       </c>
       <c r="F18" s="35" t="n">
-        <v>0.143</v>
+        <v>0.134</v>
       </c>
       <c r="G18" s="36" t="inlineStr">
         <is>
@@ -8189,11 +8259,11 @@
       </c>
       <c r="E20" s="39" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F20" s="35" t="n">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="G20" s="40" t="inlineStr">
         <is>
@@ -8214,23 +8284,23 @@
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="D21" s="34" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E21" s="39" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
       <c r="F21" s="35" t="n">
-        <v>0.355</v>
+        <v>0.344</v>
       </c>
       <c r="G21" s="40" t="inlineStr">
         <is>
-          <t>→ Brazil</t>
+          <t>→ Morocco</t>
         </is>
       </c>
     </row>
@@ -8247,11 +8317,11 @@
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D22" s="34" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="E22" s="39" t="inlineStr">
         <is>
@@ -8259,7 +8329,7 @@
         </is>
       </c>
       <c r="F22" s="35" t="n">
-        <v>0.354</v>
+        <v>0.366</v>
       </c>
       <c r="G22" s="40" t="inlineStr">
         <is>
@@ -8284,7 +8354,7 @@
         </is>
       </c>
       <c r="D23" s="34" t="n">
-        <v>0.647</v>
+        <v>0.594</v>
       </c>
       <c r="E23" s="39" t="inlineStr">
         <is>
@@ -8292,7 +8362,7 @@
         </is>
       </c>
       <c r="F23" s="35" t="n">
-        <v>0.243</v>
+        <v>0.207</v>
       </c>
       <c r="G23" s="40" t="inlineStr">
         <is>
@@ -8325,7 +8395,7 @@
         </is>
       </c>
       <c r="F24" s="35" t="n">
-        <v>0.355</v>
+        <v>0.369</v>
       </c>
       <c r="G24" s="40" t="inlineStr">
         <is>
@@ -8350,7 +8420,7 @@
         </is>
       </c>
       <c r="D25" s="34" t="n">
-        <v>0.449</v>
+        <v>0.468</v>
       </c>
       <c r="E25" s="39" t="inlineStr">
         <is>
@@ -8358,7 +8428,7 @@
         </is>
       </c>
       <c r="F25" s="35" t="n">
-        <v>0.326</v>
+        <v>0.301</v>
       </c>
       <c r="G25" s="40" t="inlineStr">
         <is>
@@ -8379,23 +8449,23 @@
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D26" s="34" t="n">
-        <v>0.5379999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="E26" s="39" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F26" s="35" t="n">
-        <v>0.29</v>
+        <v>0.276</v>
       </c>
       <c r="G26" s="40" t="inlineStr">
         <is>
-          <t>→ Brazil</t>
+          <t>→ Morocco</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8486,7 @@
         </is>
       </c>
       <c r="D27" s="34" t="n">
-        <v>0.647</v>
+        <v>0.594</v>
       </c>
       <c r="E27" s="39" t="inlineStr">
         <is>
@@ -8424,7 +8494,7 @@
         </is>
       </c>
       <c r="F27" s="35" t="n">
-        <v>0.243</v>
+        <v>0.207</v>
       </c>
       <c r="G27" s="40" t="inlineStr">
         <is>
@@ -8450,19 +8520,19 @@
         </is>
       </c>
       <c r="D29" s="34" t="n">
-        <v>0.468</v>
+        <v>0.483</v>
       </c>
       <c r="E29" s="43" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F29" s="35" t="n">
-        <v>0.319</v>
+        <v>0.289</v>
       </c>
       <c r="G29" s="44" t="inlineStr">
         <is>
-          <t>→ Brazil</t>
+          <t>→ Morocco</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8553,7 @@
         </is>
       </c>
       <c r="D30" s="34" t="n">
-        <v>0.58</v>
+        <v>0.544</v>
       </c>
       <c r="E30" s="43" t="inlineStr">
         <is>
@@ -8491,7 +8561,7 @@
         </is>
       </c>
       <c r="F30" s="35" t="n">
-        <v>0.272</v>
+        <v>0.244</v>
       </c>
       <c r="G30" s="44" t="inlineStr">
         <is>
@@ -8516,7 +8586,7 @@
         </is>
       </c>
       <c r="D31" s="34" t="n">
-        <v>0.444</v>
+        <v>0.415</v>
       </c>
       <c r="E31" s="43" t="inlineStr">
         <is>
@@ -8524,7 +8594,7 @@
         </is>
       </c>
       <c r="F31" s="35" t="n">
-        <v>0.328</v>
+        <v>0.339</v>
       </c>
       <c r="G31" s="44" t="inlineStr">
         <is>
@@ -8545,11 +8615,11 @@
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D32" s="34" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="E32" s="43" t="inlineStr">
         <is>
@@ -8557,7 +8627,7 @@
         </is>
       </c>
       <c r="F32" s="35" t="n">
-        <v>0.278</v>
+        <v>0.272</v>
       </c>
       <c r="G32" s="44" t="inlineStr">
         <is>
@@ -8579,11 +8649,11 @@
       </c>
       <c r="C34" s="47" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D34" s="34" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="E34" s="47" t="inlineStr">
         <is>
@@ -8591,7 +8661,7 @@
         </is>
       </c>
       <c r="F34" s="35" t="n">
-        <v>0.278</v>
+        <v>0.272</v>
       </c>
       <c r="G34" s="48" t="inlineStr">
         <is>
@@ -8616,7 +8686,7 @@
         </is>
       </c>
       <c r="D35" s="34" t="n">
-        <v>0.394</v>
+        <v>0.414</v>
       </c>
       <c r="E35" s="47" t="inlineStr">
         <is>
@@ -8624,7 +8694,7 @@
         </is>
       </c>
       <c r="F35" s="35" t="n">
-        <v>0.348</v>
+        <v>0.34</v>
       </c>
       <c r="G35" s="48" t="inlineStr">
         <is>
@@ -8650,7 +8720,7 @@
         </is>
       </c>
       <c r="D37" s="51" t="n">
-        <v>0.36</v>
+        <v>0.371</v>
       </c>
       <c r="E37" s="50" t="inlineStr">
         <is>
@@ -8658,7 +8728,7 @@
         </is>
       </c>
       <c r="F37" s="51" t="n">
-        <v>0.36</v>
+        <v>0.371</v>
       </c>
       <c r="G37" s="50" t="inlineStr">
         <is>
@@ -8751,19 +8821,19 @@
         </is>
       </c>
       <c r="D3" s="55" t="n">
-        <v>0.3126</v>
+        <v>0.2269</v>
       </c>
       <c r="E3" s="55" t="n">
-        <v>0.3123</v>
+        <v>0.2261</v>
       </c>
       <c r="F3" s="56" t="inlineStr">
         <is>
-          <t>→ 0.0%</t>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G3" s="57" t="inlineStr">
         <is>
-          <t>██████████████████████████████████████████████</t>
+          <t>█████████████████████████████████░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8782,19 +8852,19 @@
         </is>
       </c>
       <c r="D4" s="61" t="n">
-        <v>0.1059</v>
+        <v>0.1176</v>
       </c>
       <c r="E4" s="61" t="n">
-        <v>0.1148</v>
+        <v>0.1388</v>
       </c>
       <c r="F4" s="62" t="inlineStr">
         <is>
-          <t>↑ 0.9%</t>
+          <t>↑ 2.1%</t>
         </is>
       </c>
       <c r="G4" s="63" t="inlineStr">
         <is>
-          <t>█████████████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████████████████████░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8813,19 +8883,19 @@
         </is>
       </c>
       <c r="D5" s="67" t="n">
-        <v>0.08789999999999999</v>
+        <v>0.1129</v>
       </c>
       <c r="E5" s="67" t="n">
-        <v>0.1038</v>
+        <v>0.1352</v>
       </c>
       <c r="F5" s="68" t="inlineStr">
         <is>
-          <t>↑ 1.6%</t>
+          <t>↑ 2.2%</t>
         </is>
       </c>
       <c r="G5" s="69" t="inlineStr">
         <is>
-          <t>███████████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████████████████████░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8905,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -8844,19 +8914,19 @@
         </is>
       </c>
       <c r="D6" s="70" t="n">
-        <v>0.0553</v>
+        <v>0.0863</v>
       </c>
       <c r="E6" s="70" t="n">
-        <v>0.0646</v>
+        <v>0.0805</v>
       </c>
       <c r="F6" s="71" t="inlineStr">
         <is>
-          <t>↑ 0.9%</t>
+          <t>↓ 0.6%</t>
         </is>
       </c>
       <c r="G6" s="72" t="inlineStr">
         <is>
-          <t>█████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8875,10 +8945,10 @@
         </is>
       </c>
       <c r="D7" s="73" t="n">
-        <v>0.0548</v>
+        <v>0.0699</v>
       </c>
       <c r="E7" s="73" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="F7" s="74" t="inlineStr">
         <is>
@@ -8887,7 +8957,7 @@
       </c>
       <c r="G7" s="75" t="inlineStr">
         <is>
-          <t>█████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8897,28 +8967,28 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D8" s="70" t="n">
-        <v>0.0437</v>
+        <v>0.031</v>
       </c>
       <c r="E8" s="70" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="F8" s="71" t="inlineStr">
-        <is>
-          <t>↑ 1.1%</t>
+        <v>0.0406</v>
+      </c>
+      <c r="F8" s="76" t="inlineStr">
+        <is>
+          <t>↑ 1.0%</t>
         </is>
       </c>
       <c r="G8" s="72" t="inlineStr">
         <is>
-          <t>████████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8998,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -8937,14 +9007,14 @@
         </is>
       </c>
       <c r="D9" s="73" t="n">
-        <v>0.0292</v>
+        <v>0.0741</v>
       </c>
       <c r="E9" s="73" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>↑ 0.6%</t>
+        <v>0.0396</v>
+      </c>
+      <c r="F9" s="77" t="inlineStr">
+        <is>
+          <t>↓ 3.5%</t>
         </is>
       </c>
       <c r="G9" s="75" t="inlineStr">
@@ -8968,19 +9038,19 @@
         </is>
       </c>
       <c r="D10" s="70" t="n">
-        <v>0.0315</v>
+        <v>0.0329</v>
       </c>
       <c r="E10" s="70" t="n">
-        <v>0.03</v>
+        <v>0.0377</v>
       </c>
       <c r="F10" s="76" t="inlineStr">
         <is>
-          <t>→ 0.1%</t>
+          <t>↑ 0.5%</t>
         </is>
       </c>
       <c r="G10" s="72" t="inlineStr">
         <is>
-          <t>████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8990,28 +9060,28 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D11" s="73" t="n">
-        <v>0.0243</v>
+        <v>0.0203</v>
       </c>
       <c r="E11" s="73" t="n">
-        <v>0.0261</v>
-      </c>
-      <c r="F11" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.2%</t>
+        <v>0.0288</v>
+      </c>
+      <c r="F11" s="74" t="inlineStr">
+        <is>
+          <t>↑ 0.9%</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
         <is>
-          <t>███░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9021,23 +9091,23 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D12" s="70" t="n">
-        <v>0.0161</v>
+        <v>0.0188</v>
       </c>
       <c r="E12" s="70" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F12" s="71" t="inlineStr">
-        <is>
-          <t>↑ 1.0%</t>
+        <v>0.0257</v>
+      </c>
+      <c r="F12" s="76" t="inlineStr">
+        <is>
+          <t>↑ 0.7%</t>
         </is>
       </c>
       <c r="G12" s="72" t="inlineStr">
@@ -9052,23 +9122,23 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D13" s="73" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="E13" s="73" t="n">
-        <v>0.0203</v>
-      </c>
-      <c r="F13" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0215</v>
+      </c>
+      <c r="F13" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G13" s="75" t="inlineStr">
@@ -9083,28 +9153,28 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo L</t>
         </is>
       </c>
       <c r="D14" s="70" t="n">
-        <v>0.0302</v>
+        <v>0.0167</v>
       </c>
       <c r="E14" s="70" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="F14" s="78" t="inlineStr">
-        <is>
-          <t>↓ 1.2%</t>
+        <v>0.021</v>
+      </c>
+      <c r="F14" s="76" t="inlineStr">
+        <is>
+          <t>↑ 0.4%</t>
         </is>
       </c>
       <c r="G14" s="72" t="inlineStr">
         <is>
-          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>███░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9114,23 +9184,23 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D15" s="73" t="n">
-        <v>0.0171</v>
+        <v>0.011</v>
       </c>
       <c r="E15" s="73" t="n">
-        <v>0.0164</v>
-      </c>
-      <c r="F15" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0189</v>
+      </c>
+      <c r="F15" s="74" t="inlineStr">
+        <is>
+          <t>↑ 0.8%</t>
         </is>
       </c>
       <c r="G15" s="75" t="inlineStr">
@@ -9145,28 +9215,28 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Grupo L</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D16" s="70" t="n">
-        <v>0.0155</v>
+        <v>0.0111</v>
       </c>
       <c r="E16" s="70" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="F16" s="76" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0128</v>
+      </c>
+      <c r="F16" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G16" s="72" t="inlineStr">
         <is>
-          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9176,28 +9246,28 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D17" s="73" t="n">
-        <v>0.0178</v>
+        <v>0.0257</v>
       </c>
       <c r="E17" s="73" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="F17" s="79" t="inlineStr">
-        <is>
-          <t>↓ 0.4%</t>
+        <v>0.0109</v>
+      </c>
+      <c r="F17" s="77" t="inlineStr">
+        <is>
+          <t>↓ 1.5%</t>
         </is>
       </c>
       <c r="G17" s="75" t="inlineStr">
         <is>
-          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9216,19 +9286,19 @@
         </is>
       </c>
       <c r="D18" s="70" t="n">
-        <v>0.0138</v>
+        <v>0.0101</v>
       </c>
       <c r="E18" s="70" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="F18" s="76" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0107</v>
+      </c>
+      <c r="F18" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G18" s="72" t="inlineStr">
         <is>
-          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9238,23 +9308,23 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D19" s="73" t="n">
-        <v>0.0244</v>
+        <v>0.0103</v>
       </c>
       <c r="E19" s="73" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F19" s="79" t="inlineStr">
-        <is>
-          <t>↓ 1.4%</t>
+        <v>0.0097</v>
+      </c>
+      <c r="F19" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G19" s="75" t="inlineStr">
@@ -9269,23 +9339,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D20" s="70" t="n">
-        <v>0.0134</v>
+        <v>0.0181</v>
       </c>
       <c r="E20" s="70" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="F20" s="78" t="inlineStr">
-        <is>
-          <t>↓ 0.4%</t>
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F20" s="71" t="inlineStr">
+        <is>
+          <t>↓ 0.9%</t>
         </is>
       </c>
       <c r="G20" s="72" t="inlineStr">
@@ -9300,23 +9370,23 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D21" s="73" t="n">
-        <v>0.015</v>
+        <v>0.0104</v>
       </c>
       <c r="E21" s="73" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="F21" s="79" t="inlineStr">
-        <is>
-          <t>↓ 0.7%</t>
+        <v>0.008</v>
+      </c>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G21" s="75" t="inlineStr">
@@ -9331,23 +9401,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D22" s="70" t="n">
-        <v>0.0044</v>
+        <v>0.0124</v>
       </c>
       <c r="E22" s="70" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0072</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>↑ 0.4%</t>
+          <t>↓ 0.5%</t>
         </is>
       </c>
       <c r="G22" s="72" t="inlineStr">
@@ -9362,28 +9432,28 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D23" s="73" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0035</v>
       </c>
       <c r="E23" s="73" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="F23" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0049</v>
+      </c>
+      <c r="F23" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G23" s="75" t="inlineStr">
         <is>
-          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9463,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -9402,19 +9472,19 @@
         </is>
       </c>
       <c r="D24" s="70" t="n">
-        <v>0.0127</v>
+        <v>0.0032</v>
       </c>
       <c r="E24" s="70" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="F24" s="78" t="inlineStr">
-        <is>
-          <t>↓ 0.6%</t>
+        <v>0.0046</v>
+      </c>
+      <c r="F24" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G24" s="72" t="inlineStr">
         <is>
-          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9424,28 +9494,28 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D25" s="73" t="n">
-        <v>0.0156</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E25" s="73" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="F25" s="79" t="inlineStr">
-        <is>
-          <t>↓ 0.9%</t>
+        <v>0.0046</v>
+      </c>
+      <c r="F25" s="77" t="inlineStr">
+        <is>
+          <t>↓ 0.4%</t>
         </is>
       </c>
       <c r="G25" s="75" t="inlineStr">
         <is>
-          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9455,23 +9525,23 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D26" s="70" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0063</v>
       </c>
       <c r="E26" s="70" t="n">
         <v>0.0037</v>
       </c>
-      <c r="F26" s="76" t="inlineStr">
-        <is>
-          <t>→ 0.2%</t>
+      <c r="F26" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.3%</t>
         </is>
       </c>
       <c r="G26" s="72" t="inlineStr">
@@ -9486,23 +9556,23 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D27" s="73" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="E27" s="73" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="F27" s="79" t="inlineStr">
-        <is>
-          <t>↓ 0.5%</t>
+        <v>0.0032</v>
+      </c>
+      <c r="F27" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.3%</t>
         </is>
       </c>
       <c r="G27" s="75" t="inlineStr">
@@ -9517,23 +9587,23 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D28" s="70" t="n">
-        <v>0.0018</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="E28" s="70" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="F28" s="76" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0031</v>
+      </c>
+      <c r="F28" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.3%</t>
         </is>
       </c>
       <c r="G28" s="72" t="inlineStr">
@@ -9548,23 +9618,23 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D29" s="73" t="n">
-        <v>0.002</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="E29" s="73" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="F29" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0029</v>
+      </c>
+      <c r="F29" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G29" s="75" t="inlineStr">
@@ -9579,21 +9649,21 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D30" s="70" t="n">
-        <v>0.0023</v>
+        <v>0.0021</v>
       </c>
       <c r="E30" s="70" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="F30" s="76" t="inlineStr">
+        <v>0.0029</v>
+      </c>
+      <c r="F30" s="79" t="inlineStr">
         <is>
           <t>→ 0.1%</t>
         </is>
@@ -9610,21 +9680,21 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D31" s="73" t="n">
-        <v>0.001</v>
+        <v>0.0024</v>
       </c>
       <c r="E31" s="73" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F31" s="77" t="inlineStr">
+        <v>0.0022</v>
+      </c>
+      <c r="F31" s="78" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -9650,12 +9720,12 @@
         </is>
       </c>
       <c r="D32" s="70" t="n">
-        <v>0.0018</v>
+        <v>0.0034</v>
       </c>
       <c r="E32" s="70" t="n">
-        <v>0.0007000000000000001</v>
-      </c>
-      <c r="F32" s="76" t="inlineStr">
+        <v>0.0022</v>
+      </c>
+      <c r="F32" s="79" t="inlineStr">
         <is>
           <t>→ 0.1%</t>
         </is>
@@ -9672,23 +9742,23 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D33" s="73" t="n">
-        <v>0.0011</v>
+        <v>0.0063</v>
       </c>
       <c r="E33" s="73" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="F33" s="77" t="inlineStr">
         <is>
-          <t>→ 0.0%</t>
+          <t>↓ 0.5%</t>
         </is>
       </c>
       <c r="G33" s="75" t="inlineStr">
@@ -9703,21 +9773,21 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D34" s="70" t="n">
-        <v>0.0015</v>
+        <v>0.0022</v>
       </c>
       <c r="E34" s="70" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="F34" s="76" t="inlineStr">
+        <v>0.001</v>
+      </c>
+      <c r="F34" s="79" t="inlineStr">
         <is>
           <t>→ 0.1%</t>
         </is>
@@ -9734,21 +9804,21 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D35" s="73" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="E35" s="73" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="F35" s="77" t="inlineStr">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F35" s="78" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -9765,23 +9835,23 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D36" s="70" t="n">
-        <v>0.0027</v>
+        <v>0.001</v>
       </c>
       <c r="E36" s="70" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="F36" s="76" t="inlineStr">
-        <is>
-          <t>→ 0.2%</t>
+        <v>0.0005</v>
+      </c>
+      <c r="F36" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G36" s="72" t="inlineStr">
@@ -9796,23 +9866,23 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D37" s="73" t="n">
-        <v>0.0003</v>
+        <v>0.0011</v>
       </c>
       <c r="E37" s="73" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="F37" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0005</v>
+      </c>
+      <c r="F37" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G37" s="75" t="inlineStr">
@@ -9827,21 +9897,21 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D38" s="70" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="E38" s="70" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="F38" s="76" t="inlineStr">
+        <v>0.0004</v>
+      </c>
+      <c r="F38" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -9858,23 +9928,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D39" s="73" t="n">
-        <v>0.0002</v>
+        <v>0.0016</v>
       </c>
       <c r="E39" s="73" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="F39" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0003</v>
+      </c>
+      <c r="F39" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G39" s="75" t="inlineStr">
@@ -9889,21 +9959,21 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D40" s="70" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="E40" s="70" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="F40" s="76" t="inlineStr">
+        <v>0.0003</v>
+      </c>
+      <c r="F40" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -9920,21 +9990,21 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D41" s="73" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="E41" s="73" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F41" s="77" t="inlineStr">
+      <c r="F41" s="78" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -9951,23 +10021,23 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D42" s="70" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.0002</v>
       </c>
       <c r="E42" s="70" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F42" s="76" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+      <c r="F42" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G42" s="72" t="inlineStr">
@@ -9982,21 +10052,21 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D43" s="73" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="E43" s="73" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F43" s="77" t="inlineStr">
+      <c r="F43" s="78" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10013,21 +10083,21 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D44" s="70" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="E44" s="70" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="F44" s="76" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F44" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10044,21 +10114,21 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D45" s="73" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="E45" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="77" t="inlineStr">
+      <c r="F45" s="78" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10075,21 +10145,21 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D46" s="70" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E46" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="76" t="inlineStr">
+      <c r="F46" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10106,23 +10176,23 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D47" s="73" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E47" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="77" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+      <c r="F47" s="78" t="inlineStr">
+        <is>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G47" s="75" t="inlineStr">
@@ -10137,21 +10207,21 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D48" s="70" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="E48" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="76" t="inlineStr">
+      <c r="F48" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10177,12 +10247,12 @@
         </is>
       </c>
       <c r="D49" s="73" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E49" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="77" t="inlineStr">
+      <c r="F49" s="78" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10199,21 +10269,21 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D50" s="70" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="E50" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="76" t="inlineStr">
+      <c r="F50" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10309,13 +10379,13 @@
         </is>
       </c>
       <c r="D3" s="80" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="E3" s="80" t="n">
         <v>1876</v>
       </c>
       <c r="F3" s="80" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="G3" s="80" t="n">
         <v>2</v>
@@ -10336,13 +10406,13 @@
         </is>
       </c>
       <c r="D4" s="82" t="n">
-        <v>1983</v>
+        <v>1958</v>
       </c>
       <c r="E4" s="82" t="n">
         <v>1875</v>
       </c>
       <c r="F4" s="82" t="n">
-        <v>1940</v>
+        <v>1925</v>
       </c>
       <c r="G4" s="82" t="n">
         <v>3</v>
@@ -10363,13 +10433,13 @@
         </is>
       </c>
       <c r="D5" s="84" t="n">
-        <v>1967</v>
+        <v>1953</v>
       </c>
       <c r="E5" s="84" t="n">
         <v>1877</v>
       </c>
       <c r="F5" s="84" t="n">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="G5" s="84" t="n">
         <v>1</v>
@@ -10390,13 +10460,13 @@
         </is>
       </c>
       <c r="D6" s="86" t="n">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="E6" s="86" t="n">
         <v>1826</v>
       </c>
       <c r="F6" s="86" t="n">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="G6" s="86" t="n">
         <v>4</v>
@@ -10408,7 +10478,7 @@
       </c>
       <c r="B7" s="89" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C7" s="88" t="inlineStr">
@@ -10417,16 +10487,16 @@
         </is>
       </c>
       <c r="D7" s="88" t="n">
-        <v>1889</v>
+        <v>1915</v>
       </c>
       <c r="E7" s="88" t="n">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="F7" s="88" t="n">
-        <v>1838</v>
+        <v>1851</v>
       </c>
       <c r="G7" s="88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -10435,25 +10505,25 @@
       </c>
       <c r="B8" s="87" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C8" s="86" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D8" s="86" t="n">
-        <v>1878</v>
+        <v>1862</v>
       </c>
       <c r="E8" s="86" t="n">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="F8" s="86" t="n">
-        <v>1832</v>
+        <v>1821</v>
       </c>
       <c r="G8" s="86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10471,13 +10541,13 @@
         </is>
       </c>
       <c r="D9" s="88" t="n">
-        <v>1878</v>
+        <v>1862</v>
       </c>
       <c r="E9" s="88" t="n">
         <v>1758</v>
       </c>
       <c r="F9" s="88" t="n">
-        <v>1830</v>
+        <v>1820</v>
       </c>
       <c r="G9" s="88" t="n">
         <v>7</v>
@@ -10489,25 +10559,25 @@
       </c>
       <c r="B10" s="87" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C10" s="86" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D10" s="86" t="n">
-        <v>1876</v>
+        <v>1919</v>
       </c>
       <c r="E10" s="86" t="n">
-        <v>1756</v>
+        <v>1660</v>
       </c>
       <c r="F10" s="86" t="n">
-        <v>1828</v>
+        <v>1815</v>
       </c>
       <c r="G10" s="86" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -10516,25 +10586,25 @@
       </c>
       <c r="B11" s="89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C11" s="88" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D11" s="88" t="n">
-        <v>1879</v>
+        <v>1846</v>
       </c>
       <c r="E11" s="88" t="n">
-        <v>1730</v>
+        <v>1764</v>
       </c>
       <c r="F11" s="88" t="n">
-        <v>1819</v>
+        <v>1813</v>
       </c>
       <c r="G11" s="88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -10543,25 +10613,25 @@
       </c>
       <c r="B12" s="87" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C12" s="86" t="inlineStr">
         <is>
-          <t>Grupo L</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D12" s="86" t="n">
-        <v>1846</v>
+        <v>1856</v>
       </c>
       <c r="E12" s="86" t="n">
-        <v>1717</v>
+        <v>1730</v>
       </c>
       <c r="F12" s="86" t="n">
-        <v>1794</v>
+        <v>1806</v>
       </c>
       <c r="G12" s="86" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -10579,13 +10649,13 @@
         </is>
       </c>
       <c r="D13" s="88" t="n">
-        <v>1861</v>
+        <v>1839</v>
       </c>
       <c r="E13" s="88" t="n">
         <v>1693</v>
       </c>
       <c r="F13" s="88" t="n">
-        <v>1794</v>
+        <v>1781</v>
       </c>
       <c r="G13" s="88" t="n">
         <v>13</v>
@@ -10597,25 +10667,25 @@
       </c>
       <c r="B14" s="87" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C14" s="86" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D14" s="86" t="n">
-        <v>1880</v>
+        <v>1838</v>
       </c>
       <c r="E14" s="86" t="n">
-        <v>1660</v>
+        <v>1689</v>
       </c>
       <c r="F14" s="86" t="n">
-        <v>1792</v>
+        <v>1779</v>
       </c>
       <c r="G14" s="86" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -10624,25 +10694,25 @@
       </c>
       <c r="B15" s="89" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C15" s="88" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo L</t>
         </is>
       </c>
       <c r="D15" s="88" t="n">
-        <v>1829</v>
+        <v>1819</v>
       </c>
       <c r="E15" s="88" t="n">
-        <v>1735</v>
+        <v>1717</v>
       </c>
       <c r="F15" s="88" t="n">
-        <v>1791</v>
+        <v>1778</v>
       </c>
       <c r="G15" s="88" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -10651,25 +10721,25 @@
       </c>
       <c r="B16" s="87" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C16" s="86" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D16" s="86" t="n">
-        <v>1831</v>
+        <v>1804</v>
       </c>
       <c r="E16" s="86" t="n">
-        <v>1681</v>
+        <v>1735</v>
       </c>
       <c r="F16" s="86" t="n">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="G16" s="86" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -10678,25 +10748,25 @@
       </c>
       <c r="B17" s="89" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C17" s="88" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D17" s="88" t="n">
-        <v>1822</v>
+        <v>1816</v>
       </c>
       <c r="E17" s="88" t="n">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="F17" s="88" t="n">
-        <v>1769</v>
+        <v>1762</v>
       </c>
       <c r="G17" s="88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -10705,25 +10775,25 @@
       </c>
       <c r="B18" s="87" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C18" s="86" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D18" s="86" t="n">
-        <v>1830</v>
+        <v>1851</v>
       </c>
       <c r="E18" s="86" t="n">
-        <v>1673</v>
+        <v>1615</v>
       </c>
       <c r="F18" s="86" t="n">
-        <v>1767</v>
+        <v>1756</v>
       </c>
       <c r="G18" s="86" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -10732,25 +10802,25 @@
       </c>
       <c r="B19" s="89" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C19" s="88" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="E19" s="88" t="n">
-        <v>1595</v>
+        <v>1581</v>
       </c>
       <c r="F19" s="88" t="n">
-        <v>1756</v>
+        <v>1747</v>
       </c>
       <c r="G19" s="88" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -10759,25 +10829,25 @@
       </c>
       <c r="B20" s="87" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C20" s="86" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D20" s="86" t="n">
-        <v>1811</v>
+        <v>1793</v>
       </c>
       <c r="E20" s="86" t="n">
-        <v>1649</v>
+        <v>1673</v>
       </c>
       <c r="F20" s="86" t="n">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="G20" s="86" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -10786,25 +10856,25 @@
       </c>
       <c r="B21" s="89" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C21" s="88" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1823</v>
+        <v>1840</v>
       </c>
       <c r="E21" s="88" t="n">
-        <v>1615</v>
+        <v>1589</v>
       </c>
       <c r="F21" s="88" t="n">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="G21" s="88" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -10813,25 +10883,25 @@
       </c>
       <c r="B22" s="87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C22" s="86" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D22" s="86" t="n">
-        <v>1775</v>
+        <v>1792</v>
       </c>
       <c r="E22" s="86" t="n">
-        <v>1673</v>
+        <v>1649</v>
       </c>
       <c r="F22" s="86" t="n">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G22" s="86" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -10840,7 +10910,7 @@
       </c>
       <c r="B23" s="89" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C23" s="88" t="inlineStr">
@@ -10849,16 +10919,16 @@
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1818</v>
+        <v>1774</v>
       </c>
       <c r="E23" s="88" t="n">
-        <v>1599</v>
+        <v>1673</v>
       </c>
       <c r="F23" s="88" t="n">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="G23" s="88" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -10867,25 +10937,25 @@
       </c>
       <c r="B24" s="87" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C24" s="86" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D24" s="86" t="n">
-        <v>1828</v>
+        <v>1819</v>
       </c>
       <c r="E24" s="86" t="n">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="F24" s="86" t="n">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G24" s="86" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -10894,25 +10964,25 @@
       </c>
       <c r="B25" s="89" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C25" s="88" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1815</v>
+        <v>1802</v>
       </c>
       <c r="E25" s="88" t="n">
-        <v>1589</v>
+        <v>1564</v>
       </c>
       <c r="F25" s="88" t="n">
-        <v>1725</v>
+        <v>1707</v>
       </c>
       <c r="G25" s="88" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -10921,25 +10991,25 @@
       </c>
       <c r="B26" s="87" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C26" s="86" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D26" s="86" t="n">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="E26" s="86" t="n">
-        <v>1551</v>
+        <v>1599</v>
       </c>
       <c r="F26" s="86" t="n">
-        <v>1688</v>
+        <v>1706</v>
       </c>
       <c r="G26" s="86" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -10948,25 +11018,25 @@
       </c>
       <c r="B27" s="89" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C27" s="88" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1771</v>
+        <v>1786</v>
       </c>
       <c r="E27" s="88" t="n">
-        <v>1564</v>
+        <v>1551</v>
       </c>
       <c r="F27" s="88" t="n">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="G27" s="88" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -10984,13 +11054,13 @@
         </is>
       </c>
       <c r="D28" s="86" t="n">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="E28" s="86" t="n">
         <v>1556</v>
       </c>
       <c r="F28" s="86" t="n">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="G28" s="86" t="n">
         <v>30</v>
@@ -11002,25 +11072,25 @@
       </c>
       <c r="B29" s="89" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C29" s="88" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1739</v>
+        <v>1750</v>
       </c>
       <c r="E29" s="88" t="n">
-        <v>1593</v>
+        <v>1563</v>
       </c>
       <c r="F29" s="88" t="n">
-        <v>1681</v>
+        <v>1675</v>
       </c>
       <c r="G29" s="88" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -11029,25 +11099,25 @@
       </c>
       <c r="B30" s="87" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C30" s="86" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo L</t>
         </is>
       </c>
       <c r="D30" s="86" t="n">
-        <v>1790</v>
+        <v>1761</v>
       </c>
       <c r="E30" s="86" t="n">
-        <v>1504</v>
+        <v>1541</v>
       </c>
       <c r="F30" s="86" t="n">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="G30" s="86" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -11056,25 +11126,25 @@
       </c>
       <c r="B31" s="89" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C31" s="88" t="inlineStr">
         <is>
-          <t>Grupo L</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1758</v>
+        <v>1808</v>
       </c>
       <c r="E31" s="88" t="n">
-        <v>1541</v>
+        <v>1465</v>
       </c>
       <c r="F31" s="88" t="n">
         <v>1671</v>
       </c>
       <c r="G31" s="88" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -11083,25 +11153,25 @@
       </c>
       <c r="B32" s="87" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C32" s="86" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D32" s="86" t="n">
-        <v>1739</v>
+        <v>1709</v>
       </c>
       <c r="E32" s="86" t="n">
-        <v>1563</v>
+        <v>1593</v>
       </c>
       <c r="F32" s="86" t="n">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="G32" s="86" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -11110,25 +11180,25 @@
       </c>
       <c r="B33" s="89" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C33" s="88" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1777</v>
+        <v>1747</v>
       </c>
       <c r="E33" s="88" t="n">
-        <v>1465</v>
+        <v>1533</v>
       </c>
       <c r="F33" s="88" t="n">
-        <v>1652</v>
+        <v>1662</v>
       </c>
       <c r="G33" s="88" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
@@ -11137,25 +11207,25 @@
       </c>
       <c r="B34" s="87" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C34" s="86" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D34" s="86" t="n">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="E34" s="86" t="n">
-        <v>1533</v>
+        <v>1504</v>
       </c>
       <c r="F34" s="86" t="n">
-        <v>1647</v>
+        <v>1637</v>
       </c>
       <c r="G34" s="86" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -11164,25 +11234,25 @@
       </c>
       <c r="B35" s="89" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C35" s="88" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="E35" s="88" t="n">
-        <v>1498</v>
+        <v>1483</v>
       </c>
       <c r="F35" s="88" t="n">
-        <v>1632</v>
+        <v>1625</v>
       </c>
       <c r="G35" s="88" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -11191,25 +11261,25 @@
       </c>
       <c r="B36" s="87" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="C36" s="86" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D36" s="86" t="n">
-        <v>1681</v>
+        <v>1715</v>
       </c>
       <c r="E36" s="86" t="n">
-        <v>1515</v>
+        <v>1478</v>
       </c>
       <c r="F36" s="86" t="n">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="G36" s="86" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -11227,13 +11297,13 @@
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="E37" s="88" t="n">
         <v>1447</v>
       </c>
       <c r="F37" s="88" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="G37" s="88" t="n">
         <v>57</v>
@@ -11245,25 +11315,25 @@
       </c>
       <c r="B38" s="87" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="C38" s="86" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D38" s="86" t="n">
-        <v>1694</v>
+        <v>1686</v>
       </c>
       <c r="E38" s="86" t="n">
-        <v>1483</v>
+        <v>1498</v>
       </c>
       <c r="F38" s="86" t="n">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="G38" s="86" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
@@ -11272,25 +11342,25 @@
       </c>
       <c r="B39" s="89" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C39" s="88" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1693</v>
+        <v>1751</v>
       </c>
       <c r="E39" s="88" t="n">
-        <v>1478</v>
+        <v>1391</v>
       </c>
       <c r="F39" s="88" t="n">
         <v>1607</v>
       </c>
       <c r="G39" s="88" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -11308,13 +11378,13 @@
         </is>
       </c>
       <c r="D40" s="86" t="n">
-        <v>1675</v>
+        <v>1631</v>
       </c>
       <c r="E40" s="86" t="n">
         <v>1501</v>
       </c>
       <c r="F40" s="86" t="n">
-        <v>1605</v>
+        <v>1579</v>
       </c>
       <c r="G40" s="86" t="n">
         <v>41</v>
@@ -11326,25 +11396,25 @@
       </c>
       <c r="B41" s="89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C41" s="88" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1709</v>
+        <v>1621</v>
       </c>
       <c r="E41" s="88" t="n">
-        <v>1391</v>
+        <v>1515</v>
       </c>
       <c r="F41" s="88" t="n">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G41" s="88" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
@@ -11362,13 +11432,13 @@
         </is>
       </c>
       <c r="D42" s="86" t="n">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="E42" s="86" t="n">
         <v>1421</v>
       </c>
       <c r="F42" s="86" t="n">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="G42" s="86" t="n">
         <v>61</v>
@@ -11380,25 +11450,25 @@
       </c>
       <c r="B43" s="89" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C43" s="88" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="E43" s="88" t="n">
-        <v>1455</v>
+        <v>1430</v>
       </c>
       <c r="F43" s="88" t="n">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="G43" s="88" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44">
@@ -11407,25 +11477,25 @@
       </c>
       <c r="B44" s="87" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C44" s="86" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D44" s="86" t="n">
-        <v>1629</v>
+        <v>1615</v>
       </c>
       <c r="E44" s="86" t="n">
-        <v>1430</v>
+        <v>1455</v>
       </c>
       <c r="F44" s="86" t="n">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="G44" s="86" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45">
@@ -11443,13 +11513,13 @@
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1698</v>
+        <v>1723</v>
       </c>
       <c r="E45" s="88" t="n">
         <v>1282</v>
       </c>
       <c r="F45" s="88" t="n">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="G45" s="88" t="n">
         <v>85</v>
@@ -11470,13 +11540,13 @@
         </is>
       </c>
       <c r="D46" s="86" t="n">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="E46" s="86" t="n">
         <v>1366</v>
       </c>
       <c r="F46" s="86" t="n">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="G46" s="86" t="n">
         <v>69</v>
@@ -11488,25 +11558,25 @@
       </c>
       <c r="B47" s="89" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C47" s="88" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1597</v>
+        <v>1653</v>
       </c>
       <c r="E47" s="88" t="n">
-        <v>1386</v>
+        <v>1292</v>
       </c>
       <c r="F47" s="88" t="n">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="G47" s="88" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
@@ -11524,13 +11594,13 @@
         </is>
       </c>
       <c r="D48" s="86" t="n">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="E48" s="86" t="n">
         <v>1346</v>
       </c>
       <c r="F48" s="86" t="n">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="G48" s="86" t="n">
         <v>74</v>
@@ -11542,25 +11612,25 @@
       </c>
       <c r="B49" s="89" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C49" s="88" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1637</v>
+        <v>1621</v>
       </c>
       <c r="E49" s="88" t="n">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F49" s="88" t="n">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="G49" s="88" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50">
@@ -11569,25 +11639,25 @@
       </c>
       <c r="B50" s="87" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C50" s="86" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D50" s="86" t="n">
-        <v>1572</v>
+        <v>1534</v>
       </c>
       <c r="E50" s="86" t="n">
-        <v>1295</v>
+        <v>1386</v>
       </c>
       <c r="F50" s="86" t="n">
-        <v>1461</v>
+        <v>1475</v>
       </c>
       <c r="G50" s="86" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -11608,4 +11678,357 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📊  VALIDACIÓN DEL MODELO — BACKTESTING MUNDIALES 2018 Y 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="90" t="inlineStr">
+        <is>
+          <t>Resultados de Backtesting (50,000 simulaciones por Mundial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mundial</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Campeón Real</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Prob. Predicha</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ranking Campeón</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Log-Loss</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>vs. Naive (equiprobable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>Rusia 2018</t>
+        </is>
+      </c>
+      <c r="B5" s="92" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C5" s="93" t="inlineStr">
+        <is>
+          <t>7.67%</t>
+        </is>
+      </c>
+      <c r="D5" s="93" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="E5" s="93" t="inlineStr">
+        <is>
+          <t>0.030395</t>
+        </is>
+      </c>
+      <c r="F5" s="93" t="inlineStr">
+        <is>
+          <t>2.5673</t>
+        </is>
+      </c>
+      <c r="G5" s="93" t="inlineStr">
+        <is>
+          <t>BS -0.4% | LL +25.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="94" t="inlineStr">
+        <is>
+          <t>Qatar 2022</t>
+        </is>
+      </c>
+      <c r="B6" s="95" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C6" s="96" t="inlineStr">
+        <is>
+          <t>19.37%</t>
+        </is>
+      </c>
+      <c r="D6" s="96" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="E6" s="96" t="inlineStr">
+        <is>
+          <t>0.024207</t>
+        </is>
+      </c>
+      <c r="F6" s="96" t="inlineStr">
+        <is>
+          <t>1.6413</t>
+        </is>
+      </c>
+      <c r="G6" s="96" t="inlineStr">
+        <is>
+          <t>BS +20.0% | LL +52.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="97" t="inlineStr">
+        <is>
+          <t>Naive (1/32 equiprobable)</t>
+        </is>
+      </c>
+      <c r="B7" s="98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="D7" s="98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="98" t="inlineStr">
+        <is>
+          <t>0.030273</t>
+        </is>
+      </c>
+      <c r="F7" s="98" t="inlineStr">
+        <is>
+          <t>3.4657</t>
+        </is>
+      </c>
+      <c r="G7" s="98" t="inlineStr">
+        <is>
+          <t>Línea base</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>Comparativa de Modelos — Brier Score Promedio (2018 + 2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Brier 2018</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Brier 2022</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Promedio BS</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>LL 2018</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>LL 2022</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mejora vs Naive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>v2 ELO+decay+AD+Forma (completo)</t>
+        </is>
+      </c>
+      <c r="B11" s="100" t="inlineStr">
+        <is>
+          <t>0.030477</t>
+        </is>
+      </c>
+      <c r="C11" s="100" t="inlineStr">
+        <is>
+          <t>0.024116</t>
+        </is>
+      </c>
+      <c r="D11" s="100" t="inlineStr">
+        <is>
+          <t>0.027297</t>
+        </is>
+      </c>
+      <c r="E11" s="100" t="inlineStr">
+        <is>
+          <t>2.5845</t>
+        </is>
+      </c>
+      <c r="F11" s="100" t="inlineStr">
+        <is>
+          <t>1.6384</t>
+        </is>
+      </c>
+      <c r="G11" s="100" t="inlineStr">
+        <is>
+          <t>+9.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="101" t="inlineStr">
+        <is>
+          <t>v1 ELO+decay (sin AD/Forma)</t>
+        </is>
+      </c>
+      <c r="B12" s="102" t="inlineStr">
+        <is>
+          <t>0.029910</t>
+        </is>
+      </c>
+      <c r="C12" s="102" t="inlineStr">
+        <is>
+          <t>0.026015</t>
+        </is>
+      </c>
+      <c r="D12" s="102" t="inlineStr">
+        <is>
+          <t>0.027963</t>
+        </is>
+      </c>
+      <c r="E12" s="102" t="inlineStr">
+        <is>
+          <t>2.6205</t>
+        </is>
+      </c>
+      <c r="F12" s="102" t="inlineStr">
+        <is>
+          <t>1.9590</t>
+        </is>
+      </c>
+      <c r="G12" s="102" t="inlineStr">
+        <is>
+          <t>+7.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="103" t="inlineStr">
+        <is>
+          <t>Naive (1/32 equiprobable)</t>
+        </is>
+      </c>
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>0.030273</t>
+        </is>
+      </c>
+      <c r="C13" s="104" t="inlineStr">
+        <is>
+          <t>0.030273</t>
+        </is>
+      </c>
+      <c r="D13" s="104" t="inlineStr">
+        <is>
+          <t>0.030273</t>
+        </is>
+      </c>
+      <c r="E13" s="104" t="inlineStr">
+        <is>
+          <t>3.4657</t>
+        </is>
+      </c>
+      <c r="F13" s="104" t="inlineStr">
+        <is>
+          <t>3.4657</t>
+        </is>
+      </c>
+      <c r="G13" s="104" t="inlineStr">
+        <is>
+          <t>referencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="105" t="inlineStr">
+        <is>
+          <t>Brier Score: más bajo = mejor (0 = perfecto, 1 = pésimo). Log-Loss: más bajo = mejor. Naive = 1/n igual prob. a todos. El modelo v2 supera al naive en 9.8% en Brier Score y 53% en Log-Loss (Qatar 2022).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/excel/Mundial_2026_Predicciones.xlsx
+++ b/results/excel/Mundial_2026_Predicciones.xlsx
@@ -111,7 +111,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
@@ -128,12 +128,6 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00607D8B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
@@ -159,13 +153,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00B71C1C"/>
+      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B71C1C"/>
+      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
@@ -180,7 +174,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00555555"/>
+      <color rgb="00B71C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B71C1C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -534,58 +534,58 @@
     <xf numFmtId="10" fontId="18" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="21" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5904,16 +5904,16 @@
         <v>1762</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.4552</v>
+        <v>0.4446</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.295</v>
+        <v>0.2972</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1664</v>
+        <v>0.1764</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.08339999999999997</v>
+        <v>0.08179999999999998</v>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
@@ -5932,16 +5932,16 @@
         <v>1735</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.4888</v>
+        <v>0.502</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>0.3072</v>
+        <v>0.2958</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.141</v>
+        <v>0.1416</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>0.06300000000000003</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -5960,16 +5960,16 @@
         <v>1747</v>
       </c>
       <c r="X5" s="19" t="n">
-        <v>0.3258</v>
+        <v>0.3218</v>
       </c>
       <c r="Y5" s="19" t="n">
-        <v>0.2806</v>
+        <v>0.287</v>
       </c>
       <c r="Z5" s="19" t="n">
-        <v>0.2328</v>
+        <v>0.2314</v>
       </c>
       <c r="AA5" s="19" t="n">
-        <v>0.1608</v>
+        <v>0.1598000000000001</v>
       </c>
       <c r="AB5" s="17" t="inlineStr">
         <is>
@@ -5988,16 +5988,16 @@
         <v>1851</v>
       </c>
       <c r="AH5" s="19" t="n">
-        <v>0.5342</v>
+        <v>0.5406</v>
       </c>
       <c r="AI5" s="19" t="n">
-        <v>0.3072</v>
+        <v>0.307</v>
       </c>
       <c r="AJ5" s="19" t="n">
-        <v>0.1276</v>
+        <v>0.1198</v>
       </c>
       <c r="AK5" s="19" t="n">
-        <v>0.03100000000000003</v>
+        <v>0.03260000000000003</v>
       </c>
       <c r="AL5" s="17" t="inlineStr">
         <is>
@@ -6018,16 +6018,16 @@
         <v>1739</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>0.3562</v>
+        <v>0.363</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0.3322</v>
+        <v>0.3352</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0.1938</v>
+        <v>0.1968</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0.1177999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
@@ -6046,16 +6046,16 @@
         <v>1687</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>0.3488</v>
+        <v>0.3304</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>0.3536</v>
+        <v>0.3598</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>0.2006</v>
+        <v>0.2112</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>0.09699999999999998</v>
+        <v>0.09859999999999997</v>
       </c>
       <c r="R6" s="20" t="inlineStr">
         <is>
@@ -6067,23 +6067,23 @@
       </c>
       <c r="V6" s="21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="W6" s="20" t="n">
-        <v>1734</v>
+        <v>1706</v>
       </c>
       <c r="X6" s="22" t="n">
-        <v>0.2832</v>
+        <v>0.2858</v>
       </c>
       <c r="Y6" s="22" t="n">
-        <v>0.272</v>
+        <v>0.2808</v>
       </c>
       <c r="Z6" s="22" t="n">
-        <v>0.2454</v>
+        <v>0.246</v>
       </c>
       <c r="AA6" s="22" t="n">
-        <v>0.1994</v>
+        <v>0.1874</v>
       </c>
       <c r="AB6" s="20" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         <v>1821</v>
       </c>
       <c r="AH6" s="22" t="n">
-        <v>0.3544</v>
+        <v>0.3476</v>
       </c>
       <c r="AI6" s="22" t="n">
-        <v>0.4116</v>
+        <v>0.4026</v>
       </c>
       <c r="AJ6" s="22" t="n">
-        <v>0.171</v>
+        <v>0.1864</v>
       </c>
       <c r="AK6" s="22" t="n">
-        <v>0.06299999999999992</v>
+        <v>0.06339999999999996</v>
       </c>
       <c r="AL6" s="20" t="inlineStr">
         <is>
@@ -6132,16 +6132,16 @@
         <v>1579</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.1086</v>
+        <v>0.1152</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>0.211</v>
+        <v>0.2044</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.3224</v>
+        <v>0.3346</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.358</v>
+        <v>0.3458</v>
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
@@ -6160,16 +6160,16 @@
         <v>1551</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.0958</v>
+        <v>0.0998</v>
       </c>
       <c r="O7" s="25" t="n">
-        <v>0.1948</v>
+        <v>0.198</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>0.348</v>
+        <v>0.34</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>0.3614000000000001</v>
+        <v>0.3621999999999999</v>
       </c>
       <c r="R7" s="26" t="inlineStr">
         <is>
@@ -6181,23 +6181,23 @@
       </c>
       <c r="V7" s="24" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="W7" s="23" t="n">
-        <v>1706</v>
+        <v>1734</v>
       </c>
       <c r="X7" s="25" t="n">
-        <v>0.272</v>
+        <v>0.2828</v>
       </c>
       <c r="Y7" s="25" t="n">
-        <v>0.2744</v>
+        <v>0.2712</v>
       </c>
       <c r="Z7" s="25" t="n">
-        <v>0.2522</v>
+        <v>0.2486</v>
       </c>
       <c r="AA7" s="25" t="n">
-        <v>0.2014</v>
+        <v>0.1974000000000001</v>
       </c>
       <c r="AB7" s="26" t="inlineStr">
         <is>
@@ -6216,16 +6216,16 @@
         <v>1611</v>
       </c>
       <c r="AH7" s="25" t="n">
-        <v>0.079</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="AI7" s="25" t="n">
-        <v>0.1758</v>
+        <v>0.1856</v>
       </c>
       <c r="AJ7" s="25" t="n">
-        <v>0.404</v>
+        <v>0.391</v>
       </c>
       <c r="AK7" s="25" t="n">
-        <v>0.3412000000000001</v>
+        <v>0.3442</v>
       </c>
       <c r="AL7" s="26" t="inlineStr">
         <is>
@@ -6246,16 +6246,16 @@
         <v>1556</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.08</v>
+        <v>0.0772</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.1618</v>
+        <v>0.1632</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.3174</v>
+        <v>0.2922</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.4408</v>
+        <v>0.4673999999999999</v>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
@@ -6274,16 +6274,16 @@
         <v>1475</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0678</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>0.1444</v>
+        <v>0.1464</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.3104</v>
+        <v>0.3072</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>0.4786</v>
+        <v>0.4786000000000001</v>
       </c>
       <c r="R8" s="30" t="inlineStr">
         <is>
@@ -6302,16 +6302,16 @@
         <v>1637</v>
       </c>
       <c r="X8" s="29" t="n">
-        <v>0.119</v>
+        <v>0.1096</v>
       </c>
       <c r="Y8" s="29" t="n">
-        <v>0.173</v>
+        <v>0.161</v>
       </c>
       <c r="Z8" s="29" t="n">
-        <v>0.2696</v>
+        <v>0.274</v>
       </c>
       <c r="AA8" s="29" t="n">
-        <v>0.4384</v>
+        <v>0.4553999999999999</v>
       </c>
       <c r="AB8" s="30" t="inlineStr">
         <is>
@@ -6330,16 +6330,16 @@
         <v>1509</v>
       </c>
       <c r="AH8" s="29" t="n">
-        <v>0.0324</v>
+        <v>0.0326</v>
       </c>
       <c r="AI8" s="29" t="n">
-        <v>0.1054</v>
+        <v>0.1048</v>
       </c>
       <c r="AJ8" s="29" t="n">
-        <v>0.2974</v>
+        <v>0.3028</v>
       </c>
       <c r="AK8" s="29" t="n">
-        <v>0.5648000000000001</v>
+        <v>0.5598000000000001</v>
       </c>
       <c r="AL8" s="30" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         <v>1806</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.5806</v>
+        <v>0.575</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.2548</v>
+        <v>0.2588</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.1232</v>
+        <v>0.1264</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.04139999999999996</v>
+        <v>0.03980000000000006</v>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -6572,16 +6572,16 @@
         <v>1820</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>0.4398</v>
+        <v>0.4424</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>0.3424</v>
+        <v>0.3382</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>0.157</v>
+        <v>0.1542</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>0.06080000000000005</v>
+        <v>0.06519999999999998</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -6600,16 +6600,16 @@
         <v>1776</v>
       </c>
       <c r="X13" s="19" t="n">
-        <v>0.4516</v>
+        <v>0.4438</v>
       </c>
       <c r="Y13" s="19" t="n">
-        <v>0.2904</v>
+        <v>0.2846</v>
       </c>
       <c r="Z13" s="19" t="n">
-        <v>0.187</v>
+        <v>0.1882</v>
       </c>
       <c r="AA13" s="19" t="n">
-        <v>0.07100000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="AB13" s="17" t="inlineStr">
         <is>
@@ -6628,16 +6628,16 @@
         <v>1959</v>
       </c>
       <c r="AH13" s="19" t="n">
-        <v>0.7786</v>
+        <v>0.7678</v>
       </c>
       <c r="AI13" s="19" t="n">
-        <v>0.1714</v>
+        <v>0.187</v>
       </c>
       <c r="AJ13" s="19" t="n">
         <v>0.0392</v>
       </c>
       <c r="AK13" s="19" t="n">
-        <v>0.01080000000000005</v>
+        <v>0.005999999999999964</v>
       </c>
       <c r="AL13" s="17" t="inlineStr">
         <is>
@@ -6658,16 +6658,16 @@
         <v>1730</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0.212</v>
+        <v>0.2056</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0.3334</v>
+        <v>0.3456</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.313</v>
+        <v>0.3088</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.1416000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
@@ -6686,16 +6686,16 @@
         <v>1815</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.4358</v>
+        <v>0.4352</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>0.3562</v>
+        <v>0.3508</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.1498</v>
+        <v>0.1542</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>0.05820000000000003</v>
+        <v>0.05979999999999996</v>
       </c>
       <c r="R14" s="20" t="inlineStr">
         <is>
@@ -6714,16 +6714,16 @@
         <v>1756</v>
       </c>
       <c r="X14" s="22" t="n">
-        <v>0.3182</v>
+        <v>0.3344</v>
       </c>
       <c r="Y14" s="22" t="n">
-        <v>0.3302</v>
+        <v>0.3274</v>
       </c>
       <c r="Z14" s="22" t="n">
-        <v>0.2362</v>
+        <v>0.2264</v>
       </c>
       <c r="AA14" s="22" t="n">
-        <v>0.1154</v>
+        <v>0.1118</v>
       </c>
       <c r="AB14" s="20" t="inlineStr">
         <is>
@@ -6742,16 +6742,16 @@
         <v>1745</v>
       </c>
       <c r="AH14" s="22" t="n">
-        <v>0.1622</v>
+        <v>0.1648</v>
       </c>
       <c r="AI14" s="22" t="n">
-        <v>0.4998</v>
+        <v>0.4884</v>
       </c>
       <c r="AJ14" s="22" t="n">
-        <v>0.2414</v>
+        <v>0.2494</v>
       </c>
       <c r="AK14" s="22" t="n">
-        <v>0.09659999999999996</v>
+        <v>0.09739999999999993</v>
       </c>
       <c r="AL14" s="20" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>1662</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.178</v>
+        <v>0.1882</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.324</v>
+        <v>0.3066</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.3428</v>
+        <v>0.3452</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>0.1552000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -6800,16 +6800,16 @@
         <v>1625</v>
       </c>
       <c r="N15" s="25" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0708</v>
       </c>
       <c r="O15" s="25" t="n">
-        <v>0.1726</v>
+        <v>0.1818</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>0.3948</v>
+        <v>0.3908</v>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>0.3568000000000001</v>
+        <v>0.3566000000000001</v>
       </c>
       <c r="R15" s="26" t="inlineStr">
         <is>
@@ -6828,16 +6828,16 @@
         <v>1675</v>
       </c>
       <c r="X15" s="25" t="n">
-        <v>0.1874</v>
+        <v>0.1782</v>
       </c>
       <c r="Y15" s="25" t="n">
-        <v>0.2598</v>
+        <v>0.28</v>
       </c>
       <c r="Z15" s="25" t="n">
-        <v>0.3316</v>
+        <v>0.3392</v>
       </c>
       <c r="AA15" s="25" t="n">
-        <v>0.2212</v>
+        <v>0.2025999999999999</v>
       </c>
       <c r="AB15" s="26" t="inlineStr">
         <is>
@@ -6856,16 +6856,16 @@
         <v>1578</v>
       </c>
       <c r="AH15" s="25" t="n">
-        <v>0.0364</v>
+        <v>0.042</v>
       </c>
       <c r="AI15" s="25" t="n">
-        <v>0.193</v>
+        <v>0.1934</v>
       </c>
       <c r="AJ15" s="25" t="n">
-        <v>0.3892</v>
+        <v>0.3898</v>
       </c>
       <c r="AK15" s="25" t="n">
-        <v>0.3814</v>
+        <v>0.3748</v>
       </c>
       <c r="AL15" s="26" t="inlineStr">
         <is>
@@ -6886,16 +6886,16 @@
         <v>1491</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.0294</v>
+        <v>0.0312</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>0.0878</v>
+        <v>0.089</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>0.221</v>
+        <v>0.2196</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
@@ -6914,16 +6914,16 @@
         <v>1579</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.0486</v>
+        <v>0.0516</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>0.2984</v>
+        <v>0.3008</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>0.5242</v>
+        <v>0.5184</v>
       </c>
       <c r="R16" s="30" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         <v>1547</v>
       </c>
       <c r="X16" s="29" t="n">
-        <v>0.0428</v>
+        <v>0.0436</v>
       </c>
       <c r="Y16" s="29" t="n">
-        <v>0.1196</v>
+        <v>0.108</v>
       </c>
       <c r="Z16" s="29" t="n">
-        <v>0.2452</v>
+        <v>0.2462</v>
       </c>
       <c r="AA16" s="29" t="n">
-        <v>0.5924</v>
+        <v>0.6022000000000001</v>
       </c>
       <c r="AB16" s="30" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         <v>1512</v>
       </c>
       <c r="AH16" s="29" t="n">
-        <v>0.0228</v>
+        <v>0.0254</v>
       </c>
       <c r="AI16" s="29" t="n">
-        <v>0.1358</v>
+        <v>0.1312</v>
       </c>
       <c r="AJ16" s="29" t="n">
-        <v>0.3302</v>
+        <v>0.3216</v>
       </c>
       <c r="AK16" s="29" t="n">
-        <v>0.5111999999999999</v>
+        <v>0.5218</v>
       </c>
       <c r="AL16" s="30" t="inlineStr">
         <is>
@@ -7184,16 +7184,16 @@
         <v>1923</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.588</v>
+        <v>0.609</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.2676</v>
+        <v>0.2536</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.1088</v>
+        <v>0.1048</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.03560000000000003</v>
+        <v>0.03260000000000002</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -7212,16 +7212,16 @@
         <v>1925</v>
       </c>
       <c r="N21" s="19" t="n">
-        <v>0.681</v>
+        <v>0.6818</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>0.2132</v>
+        <v>0.215</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>0.081</v>
+        <v>0.0772</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>0.02479999999999995</v>
+        <v>0.02600000000000004</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -7240,16 +7240,16 @@
         <v>1813</v>
       </c>
       <c r="X21" s="19" t="n">
-        <v>0.4714</v>
+        <v>0.4366</v>
       </c>
       <c r="Y21" s="19" t="n">
-        <v>0.2778</v>
+        <v>0.2856</v>
       </c>
       <c r="Z21" s="19" t="n">
-        <v>0.158</v>
+        <v>0.179</v>
       </c>
       <c r="AA21" s="19" t="n">
-        <v>0.09279999999999997</v>
+        <v>0.0988</v>
       </c>
       <c r="AB21" s="17" t="inlineStr">
         <is>
@@ -7268,16 +7268,16 @@
         <v>1890</v>
       </c>
       <c r="AH21" s="19" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5594</v>
       </c>
       <c r="AI21" s="19" t="n">
-        <v>0.2884</v>
+        <v>0.2938</v>
       </c>
       <c r="AJ21" s="19" t="n">
-        <v>0.1264</v>
+        <v>0.1208</v>
       </c>
       <c r="AK21" s="19" t="n">
-        <v>0.02819999999999995</v>
+        <v>0.02599999999999998</v>
       </c>
       <c r="AL21" s="17" t="inlineStr">
         <is>
@@ -7298,16 +7298,16 @@
         <v>1779</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0.256</v>
+        <v>0.2428</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0.3654</v>
+        <v>0.3776</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>0.2492</v>
+        <v>0.2468</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0.1294</v>
+        <v>0.1328</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -7326,16 +7326,16 @@
         <v>1707</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>0.1536</v>
+        <v>0.1458</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>0.3404</v>
+        <v>0.3264</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.2988</v>
+        <v>0.317</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0.2072</v>
+        <v>0.2107999999999999</v>
       </c>
       <c r="R22" s="20" t="inlineStr">
         <is>
@@ -7354,16 +7354,16 @@
         <v>1781</v>
       </c>
       <c r="X22" s="22" t="n">
-        <v>0.3</v>
+        <v>0.3268</v>
       </c>
       <c r="Y22" s="22" t="n">
-        <v>0.3236</v>
+        <v>0.3194</v>
       </c>
       <c r="Z22" s="22" t="n">
-        <v>0.224</v>
+        <v>0.2062</v>
       </c>
       <c r="AA22" s="22" t="n">
-        <v>0.1524</v>
+        <v>0.1476</v>
       </c>
       <c r="AB22" s="20" t="inlineStr">
         <is>
@@ -7382,16 +7382,16 @@
         <v>1778</v>
       </c>
       <c r="AH22" s="22" t="n">
-        <v>0.298</v>
+        <v>0.2976</v>
       </c>
       <c r="AI22" s="22" t="n">
-        <v>0.3812</v>
+        <v>0.3986</v>
       </c>
       <c r="AJ22" s="22" t="n">
-        <v>0.2392</v>
+        <v>0.2274</v>
       </c>
       <c r="AK22" s="22" t="n">
-        <v>0.08159999999999998</v>
+        <v>0.07640000000000002</v>
       </c>
       <c r="AL22" s="20" t="inlineStr">
         <is>
@@ -7412,16 +7412,16 @@
         <v>1692</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.1062</v>
+        <v>0.1042</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0.2262</v>
+        <v>0.2366</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>0.3658</v>
+        <v>0.3616</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>0.3018</v>
+        <v>0.2976</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -7440,16 +7440,16 @@
         <v>1663</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>0.1122</v>
+        <v>0.1138</v>
       </c>
       <c r="O23" s="25" t="n">
-        <v>0.2822</v>
+        <v>0.2858</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.3406</v>
+        <v>0.3272</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>0.265</v>
+        <v>0.2732000000000001</v>
       </c>
       <c r="R23" s="26" t="inlineStr">
         <is>
@@ -7468,16 +7468,16 @@
         <v>1671</v>
       </c>
       <c r="X23" s="25" t="n">
-        <v>0.132</v>
+        <v>0.1432</v>
       </c>
       <c r="Y23" s="25" t="n">
-        <v>0.2282</v>
+        <v>0.218</v>
       </c>
       <c r="Z23" s="25" t="n">
-        <v>0.3198</v>
+        <v>0.3088</v>
       </c>
       <c r="AA23" s="25" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="AB23" s="26" t="inlineStr">
         <is>
@@ -7496,16 +7496,16 @@
         <v>1673</v>
       </c>
       <c r="AH23" s="25" t="n">
-        <v>0.1244</v>
+        <v>0.1236</v>
       </c>
       <c r="AI23" s="25" t="n">
-        <v>0.2574</v>
+        <v>0.237</v>
       </c>
       <c r="AJ23" s="25" t="n">
-        <v>0.412</v>
+        <v>0.43</v>
       </c>
       <c r="AK23" s="25" t="n">
-        <v>0.2062000000000001</v>
+        <v>0.2094</v>
       </c>
       <c r="AL23" s="26" t="inlineStr">
         <is>
@@ -7526,16 +7526,16 @@
         <v>1615</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>0.0498</v>
+        <v>0.044</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>0.1408</v>
+        <v>0.1322</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0.2762</v>
+        <v>0.2868</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>0.5332</v>
+        <v>0.5369999999999999</v>
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
@@ -7554,16 +7554,16 @@
         <v>1607</v>
       </c>
       <c r="N24" s="29" t="n">
-        <v>0.0532</v>
+        <v>0.0586</v>
       </c>
       <c r="O24" s="29" t="n">
-        <v>0.1642</v>
+        <v>0.1728</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.2796</v>
+        <v>0.2786</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>0.5029999999999999</v>
+        <v>0.4899999999999999</v>
       </c>
       <c r="R24" s="30" t="inlineStr">
         <is>
@@ -7582,16 +7582,16 @@
         <v>1620</v>
       </c>
       <c r="X24" s="29" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0934</v>
       </c>
       <c r="Y24" s="29" t="n">
-        <v>0.1704</v>
+        <v>0.177</v>
       </c>
       <c r="Z24" s="29" t="n">
-        <v>0.2982</v>
+        <v>0.306</v>
       </c>
       <c r="AA24" s="29" t="n">
-        <v>0.4348</v>
+        <v>0.4236</v>
       </c>
       <c r="AB24" s="30" t="inlineStr">
         <is>
@@ -7610,16 +7610,16 @@
         <v>1508</v>
       </c>
       <c r="AH24" s="29" t="n">
-        <v>0.0206</v>
+        <v>0.0194</v>
       </c>
       <c r="AI24" s="29" t="n">
-        <v>0.073</v>
+        <v>0.0706</v>
       </c>
       <c r="AJ24" s="29" t="n">
-        <v>0.2224</v>
+        <v>0.2218</v>
       </c>
       <c r="AK24" s="29" t="n">
-        <v>0.6840000000000002</v>
+        <v>0.6882</v>
       </c>
       <c r="AL24" s="30" t="inlineStr">
         <is>
@@ -7825,15 +7825,15 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.551</v>
+        <v>0.518</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.239</v>
+        <v>0.263</v>
       </c>
       <c r="G6" s="36" t="inlineStr">
         <is>
@@ -7858,19 +7858,19 @@
         </is>
       </c>
       <c r="D7" s="34" t="n">
-        <v>0.382</v>
+        <v>0.389</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F7" s="35" t="n">
-        <v>0.362</v>
+        <v>0.358</v>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>→ Japan</t>
+          <t>→ Netherlands</t>
         </is>
       </c>
     </row>
@@ -7887,11 +7887,11 @@
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D8" s="34" t="n">
-        <v>0.485</v>
+        <v>0.479</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
@@ -7899,11 +7899,11 @@
         </is>
       </c>
       <c r="F8" s="35" t="n">
-        <v>0.288</v>
+        <v>0.292</v>
       </c>
       <c r="G8" s="36" t="inlineStr">
         <is>
-          <t>→ Netherlands</t>
+          <t>→ Japan</t>
         </is>
       </c>
     </row>
@@ -8122,15 +8122,15 @@
         </is>
       </c>
       <c r="D15" s="34" t="n">
-        <v>0.423</v>
+        <v>0.441</v>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F15" s="35" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="G15" s="36" t="inlineStr">
         <is>
@@ -8155,15 +8155,15 @@
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F16" s="35" t="n">
-        <v>0.227</v>
+        <v>0.213</v>
       </c>
       <c r="G16" s="36" t="inlineStr">
         <is>
@@ -8188,15 +8188,15 @@
         </is>
       </c>
       <c r="D17" s="34" t="n">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="F17" s="35" t="n">
-        <v>0.278</v>
+        <v>0.276</v>
       </c>
       <c r="G17" s="36" t="inlineStr">
         <is>
@@ -8221,15 +8221,15 @@
         </is>
       </c>
       <c r="D18" s="34" t="n">
-        <v>0.6940000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F18" s="35" t="n">
-        <v>0.134</v>
+        <v>0.132</v>
       </c>
       <c r="G18" s="36" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D22" s="34" t="n">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="E22" s="39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F22" s="35" t="n">
@@ -8821,19 +8821,19 @@
         </is>
       </c>
       <c r="D3" s="55" t="n">
-        <v>0.2269</v>
+        <v>0.2285</v>
       </c>
       <c r="E3" s="55" t="n">
-        <v>0.2261</v>
+        <v>0.2316</v>
       </c>
       <c r="F3" s="56" t="inlineStr">
         <is>
-          <t>→ 0.1%</t>
+          <t>↑ 0.3%</t>
         </is>
       </c>
       <c r="G3" s="57" t="inlineStr">
         <is>
-          <t>█████████████████████████████████░░░░░░░░░░░░</t>
+          <t>██████████████████████████████████░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8852,19 +8852,19 @@
         </is>
       </c>
       <c r="D4" s="61" t="n">
-        <v>0.1176</v>
+        <v>0.1168</v>
       </c>
       <c r="E4" s="61" t="n">
-        <v>0.1388</v>
+        <v>0.1469</v>
       </c>
       <c r="F4" s="62" t="inlineStr">
         <is>
-          <t>↑ 2.1%</t>
+          <t>↑ 3.0%</t>
         </is>
       </c>
       <c r="G4" s="63" t="inlineStr">
         <is>
-          <t>████████████████████░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██████████████████████░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8883,19 +8883,19 @@
         </is>
       </c>
       <c r="D5" s="67" t="n">
-        <v>0.1129</v>
+        <v>0.11</v>
       </c>
       <c r="E5" s="67" t="n">
-        <v>0.1352</v>
+        <v>0.1415</v>
       </c>
       <c r="F5" s="68" t="inlineStr">
         <is>
-          <t>↑ 2.2%</t>
+          <t>↑ 3.2%</t>
         </is>
       </c>
       <c r="G5" s="69" t="inlineStr">
         <is>
-          <t>████████████████████░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█████████████████████░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8914,14 +8914,14 @@
         </is>
       </c>
       <c r="D6" s="70" t="n">
-        <v>0.0863</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E6" s="70" t="n">
-        <v>0.0805</v>
+        <v>0.0852</v>
       </c>
       <c r="F6" s="71" t="inlineStr">
         <is>
-          <t>↓ 0.6%</t>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G6" s="72" t="inlineStr">
@@ -8945,14 +8945,14 @@
         </is>
       </c>
       <c r="D7" s="73" t="n">
-        <v>0.0699</v>
+        <v>0.0702</v>
       </c>
       <c r="E7" s="73" t="n">
-        <v>0.0775</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F7" s="74" t="inlineStr">
         <is>
-          <t>↑ 0.8%</t>
+          <t>↑ 0.4%</t>
         </is>
       </c>
       <c r="G7" s="75" t="inlineStr">
@@ -8976,14 +8976,14 @@
         </is>
       </c>
       <c r="D8" s="70" t="n">
-        <v>0.031</v>
+        <v>0.0313</v>
       </c>
       <c r="E8" s="70" t="n">
-        <v>0.0406</v>
+        <v>0.0428</v>
       </c>
       <c r="F8" s="76" t="inlineStr">
         <is>
-          <t>↑ 1.0%</t>
+          <t>↑ 1.2%</t>
         </is>
       </c>
       <c r="G8" s="72" t="inlineStr">
@@ -9007,19 +9007,19 @@
         </is>
       </c>
       <c r="D9" s="73" t="n">
-        <v>0.0741</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E9" s="73" t="n">
-        <v>0.0396</v>
+        <v>0.0428</v>
       </c>
       <c r="F9" s="77" t="inlineStr">
         <is>
-          <t>↓ 3.5%</t>
+          <t>↓ 3.2%</t>
         </is>
       </c>
       <c r="G9" s="75" t="inlineStr">
         <is>
-          <t>█████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="D10" s="70" t="n">
-        <v>0.0329</v>
+        <v>0.0334</v>
       </c>
       <c r="E10" s="70" t="n">
-        <v>0.0377</v>
-      </c>
-      <c r="F10" s="76" t="inlineStr">
-        <is>
-          <t>↑ 0.5%</t>
+        <v>0.0314</v>
+      </c>
+      <c r="F10" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G10" s="72" t="inlineStr">
         <is>
-          <t>█████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9069,14 +9069,14 @@
         </is>
       </c>
       <c r="D11" s="73" t="n">
-        <v>0.0203</v>
+        <v>0.0199</v>
       </c>
       <c r="E11" s="73" t="n">
-        <v>0.0288</v>
+        <v>0.0302</v>
       </c>
       <c r="F11" s="74" t="inlineStr">
         <is>
-          <t>↑ 0.9%</t>
+          <t>↑ 1.0%</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
@@ -9100,14 +9100,14 @@
         </is>
       </c>
       <c r="D12" s="70" t="n">
-        <v>0.0188</v>
+        <v>0.0193</v>
       </c>
       <c r="E12" s="70" t="n">
-        <v>0.0257</v>
+        <v>0.024</v>
       </c>
       <c r="F12" s="76" t="inlineStr">
         <is>
-          <t>↑ 0.7%</t>
+          <t>↑ 0.5%</t>
         </is>
       </c>
       <c r="G12" s="72" t="inlineStr">
@@ -9131,19 +9131,19 @@
         </is>
       </c>
       <c r="D13" s="73" t="n">
-        <v>0.023</v>
+        <v>0.0229</v>
       </c>
       <c r="E13" s="73" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="F13" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0192</v>
+      </c>
+      <c r="F13" s="77" t="inlineStr">
+        <is>
+          <t>↓ 0.4%</t>
         </is>
       </c>
       <c r="G13" s="75" t="inlineStr">
         <is>
-          <t>███░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9162,19 +9162,19 @@
         </is>
       </c>
       <c r="D14" s="70" t="n">
-        <v>0.0167</v>
+        <v>0.018</v>
       </c>
       <c r="E14" s="70" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F14" s="76" t="inlineStr">
-        <is>
-          <t>↑ 0.4%</t>
+        <v>0.017</v>
+      </c>
+      <c r="F14" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G14" s="72" t="inlineStr">
         <is>
-          <t>███░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9193,14 +9193,14 @@
         </is>
       </c>
       <c r="D15" s="73" t="n">
-        <v>0.011</v>
+        <v>0.0108</v>
       </c>
       <c r="E15" s="73" t="n">
-        <v>0.0189</v>
+        <v>0.0169</v>
       </c>
       <c r="F15" s="74" t="inlineStr">
         <is>
-          <t>↑ 0.8%</t>
+          <t>↑ 0.6%</t>
         </is>
       </c>
       <c r="G15" s="75" t="inlineStr">
@@ -9224,19 +9224,19 @@
         </is>
       </c>
       <c r="D16" s="70" t="n">
-        <v>0.0111</v>
+        <v>0.011</v>
       </c>
       <c r="E16" s="70" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="F16" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.2%</t>
+        <v>0.0147</v>
+      </c>
+      <c r="F16" s="76" t="inlineStr">
+        <is>
+          <t>↑ 0.4%</t>
         </is>
       </c>
       <c r="G16" s="72" t="inlineStr">
         <is>
-          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="D17" s="73" t="n">
-        <v>0.0257</v>
+        <v>0.0259</v>
       </c>
       <c r="E17" s="73" t="n">
-        <v>0.0109</v>
+        <v>0.0111</v>
       </c>
       <c r="F17" s="77" t="inlineStr">
         <is>
@@ -9277,23 +9277,23 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D18" s="70" t="n">
-        <v>0.0101</v>
+        <v>0.018</v>
       </c>
       <c r="E18" s="70" t="n">
-        <v>0.0107</v>
-      </c>
-      <c r="F18" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0098</v>
+      </c>
+      <c r="F18" s="78" t="inlineStr">
+        <is>
+          <t>↓ 0.8%</t>
         </is>
       </c>
       <c r="G18" s="72" t="inlineStr">
@@ -9308,23 +9308,23 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Grupo K</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D19" s="73" t="n">
-        <v>0.0103</v>
+        <v>0.0092</v>
       </c>
       <c r="E19" s="73" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="F19" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F19" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G19" s="75" t="inlineStr">
@@ -9339,23 +9339,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo K</t>
         </is>
       </c>
       <c r="D20" s="70" t="n">
-        <v>0.0181</v>
+        <v>0.0098</v>
       </c>
       <c r="E20" s="70" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>↓ 0.9%</t>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G20" s="72" t="inlineStr">
@@ -9379,19 +9379,19 @@
         </is>
       </c>
       <c r="D21" s="73" t="n">
-        <v>0.0104</v>
+        <v>0.0102</v>
       </c>
       <c r="E21" s="73" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F21" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.2%</t>
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F21" s="77" t="inlineStr">
+        <is>
+          <t>↓ 0.5%</t>
         </is>
       </c>
       <c r="G21" s="75" t="inlineStr">
         <is>
-          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9413,16 +9413,16 @@
         <v>0.0124</v>
       </c>
       <c r="E22" s="70" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="F22" s="71" t="inlineStr">
-        <is>
-          <t>↓ 0.5%</t>
+        <v>0.0054</v>
+      </c>
+      <c r="F22" s="78" t="inlineStr">
+        <is>
+          <t>↓ 0.7%</t>
         </is>
       </c>
       <c r="G22" s="72" t="inlineStr">
         <is>
-          <t>█░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -9441,12 +9441,12 @@
         </is>
       </c>
       <c r="D23" s="73" t="n">
-        <v>0.0035</v>
+        <v>0.0039</v>
       </c>
       <c r="E23" s="73" t="n">
-        <v>0.0049</v>
-      </c>
-      <c r="F23" s="78" t="inlineStr">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="F23" s="79" t="inlineStr">
         <is>
           <t>→ 0.1%</t>
         </is>
@@ -9472,14 +9472,14 @@
         </is>
       </c>
       <c r="D24" s="70" t="n">
-        <v>0.0032</v>
+        <v>0.0028</v>
       </c>
       <c r="E24" s="70" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="F24" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0044</v>
+      </c>
+      <c r="F24" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G24" s="72" t="inlineStr">
@@ -9503,14 +9503,14 @@
         </is>
       </c>
       <c r="D25" s="73" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="E25" s="73" t="n">
-        <v>0.0046</v>
+        <v>0.0035</v>
       </c>
       <c r="F25" s="77" t="inlineStr">
         <is>
-          <t>↓ 0.4%</t>
+          <t>↓ 0.5%</t>
         </is>
       </c>
       <c r="G25" s="75" t="inlineStr">
@@ -9537,9 +9537,9 @@
         <v>0.0063</v>
       </c>
       <c r="E26" s="70" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="F26" s="79" t="inlineStr">
+        <v>0.0033</v>
+      </c>
+      <c r="F26" s="71" t="inlineStr">
         <is>
           <t>→ 0.3%</t>
         </is>
@@ -9556,12 +9556,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D27" s="73" t="n">
@@ -9570,7 +9570,7 @@
       <c r="E27" s="73" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F27" s="78" t="inlineStr">
+      <c r="F27" s="79" t="inlineStr">
         <is>
           <t>→ 0.3%</t>
         </is>
@@ -9587,23 +9587,23 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D28" s="70" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="E28" s="70" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="F28" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.3%</t>
+        <v>0.0024</v>
+      </c>
+      <c r="F28" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G28" s="72" t="inlineStr">
@@ -9618,23 +9618,23 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D29" s="73" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="E29" s="73" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="F29" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.2%</t>
+        <v>0.0024</v>
+      </c>
+      <c r="F29" s="77" t="inlineStr">
+        <is>
+          <t>↓ 0.3%</t>
         </is>
       </c>
       <c r="G29" s="75" t="inlineStr">
@@ -9658,14 +9658,14 @@
         </is>
       </c>
       <c r="D30" s="70" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="E30" s="70" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="F30" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0022</v>
+      </c>
+      <c r="F30" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G30" s="72" t="inlineStr">
@@ -9689,14 +9689,14 @@
         </is>
       </c>
       <c r="D31" s="73" t="n">
-        <v>0.0024</v>
+        <v>0.0029</v>
       </c>
       <c r="E31" s="73" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="F31" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0016</v>
+      </c>
+      <c r="F31" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G31" s="75" t="inlineStr">
@@ -9720,14 +9720,14 @@
         </is>
       </c>
       <c r="D32" s="70" t="n">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="E32" s="70" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="F32" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0014</v>
+      </c>
+      <c r="F32" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G32" s="72" t="inlineStr">
@@ -9751,14 +9751,14 @@
         </is>
       </c>
       <c r="D33" s="73" t="n">
-        <v>0.0063</v>
+        <v>0.0066</v>
       </c>
       <c r="E33" s="73" t="n">
-        <v>0.0014</v>
+        <v>0.001</v>
       </c>
       <c r="F33" s="77" t="inlineStr">
         <is>
-          <t>↓ 0.5%</t>
+          <t>↓ 0.6%</t>
         </is>
       </c>
       <c r="G33" s="75" t="inlineStr">
@@ -9782,12 +9782,12 @@
         </is>
       </c>
       <c r="D34" s="70" t="n">
-        <v>0.0022</v>
+        <v>0.002</v>
       </c>
       <c r="E34" s="70" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F34" s="79" t="inlineStr">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F34" s="71" t="inlineStr">
         <is>
           <t>→ 0.1%</t>
         </is>
@@ -9813,14 +9813,14 @@
         </is>
       </c>
       <c r="D35" s="73" t="n">
-        <v>0.0009</v>
+        <v>0.0011</v>
       </c>
       <c r="E35" s="73" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="F35" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0004</v>
+      </c>
+      <c r="F35" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G35" s="75" t="inlineStr">
@@ -9844,14 +9844,14 @@
         </is>
       </c>
       <c r="D36" s="70" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="E36" s="70" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="F36" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0004</v>
+      </c>
+      <c r="F36" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G36" s="72" t="inlineStr">
@@ -9866,23 +9866,23 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D37" s="73" t="n">
-        <v>0.0011</v>
+        <v>0.0002</v>
       </c>
       <c r="E37" s="73" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="F37" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0003</v>
+      </c>
+      <c r="F37" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G37" s="75" t="inlineStr">
@@ -9897,23 +9897,23 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D38" s="70" t="n">
-        <v>0.0002</v>
+        <v>0.0014</v>
       </c>
       <c r="E38" s="70" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="F38" s="79" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
+        <v>0.0003</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G38" s="72" t="inlineStr">
@@ -9937,14 +9937,14 @@
         </is>
       </c>
       <c r="D39" s="73" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="E39" s="73" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="F39" s="78" t="inlineStr">
-        <is>
-          <t>→ 0.1%</t>
+        <v>0.0002</v>
+      </c>
+      <c r="F39" s="79" t="inlineStr">
+        <is>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G39" s="75" t="inlineStr">
@@ -9971,9 +9971,9 @@
         <v>0.0005</v>
       </c>
       <c r="E40" s="70" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="F40" s="79" t="inlineStr">
+        <v>0.0002</v>
+      </c>
+      <c r="F40" s="71" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -9990,21 +9990,21 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo F</t>
         </is>
       </c>
       <c r="D41" s="73" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="E41" s="73" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F41" s="78" t="inlineStr">
+      <c r="F41" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10021,21 +10021,21 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D42" s="70" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="E42" s="70" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F42" s="79" t="inlineStr">
+      <c r="F42" s="71" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10052,21 +10052,21 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Grupo F</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D43" s="73" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="E43" s="73" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F43" s="78" t="inlineStr">
+      <c r="F43" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -10095,9 +10095,9 @@
         <v>0</v>
       </c>
       <c r="E44" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="79" t="inlineStr">
+        <v>0.0001</v>
+      </c>
+      <c r="F44" s="71" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10114,21 +10114,21 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D45" s="73" t="n">
         <v>0.0002</v>
       </c>
       <c r="E45" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="78" t="inlineStr">
+        <v>0.0001</v>
+      </c>
+      <c r="F45" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10145,12 +10145,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D46" s="70" t="n">
@@ -10159,7 +10159,7 @@
       <c r="E46" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="79" t="inlineStr">
+      <c r="F46" s="71" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10176,21 +10176,21 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D47" s="73" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E47" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="78" t="inlineStr">
+      <c r="F47" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10207,21 +10207,21 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D48" s="70" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="E48" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="79" t="inlineStr">
+      <c r="F48" s="71" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10238,21 +10238,21 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Grupo L</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D49" s="73" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E49" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="78" t="inlineStr">
+      <c r="F49" s="79" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>
@@ -10269,21 +10269,21 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo L</t>
         </is>
       </c>
       <c r="D50" s="70" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="E50" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="79" t="inlineStr">
+      <c r="F50" s="71" t="inlineStr">
         <is>
           <t>→ 0.0%</t>
         </is>

--- a/results/excel/Mundial_2026_Predicciones.xlsx
+++ b/results/excel/Mundial_2026_Predicciones.xlsx
@@ -5904,16 +5904,16 @@
         <v>1762</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.4446</v>
+        <v>0.443</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2972</v>
+        <v>0.3066</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1764</v>
+        <v>0.1676</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.08179999999999998</v>
+        <v>0.08279999999999996</v>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
@@ -5932,16 +5932,16 @@
         <v>1735</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>0.2958</v>
+        <v>0.288</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.1416</v>
+        <v>0.1492</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.05880000000000002</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -5960,16 +5960,16 @@
         <v>1747</v>
       </c>
       <c r="X5" s="19" t="n">
-        <v>0.3218</v>
+        <v>0.3346</v>
       </c>
       <c r="Y5" s="19" t="n">
-        <v>0.287</v>
+        <v>0.277</v>
       </c>
       <c r="Z5" s="19" t="n">
-        <v>0.2314</v>
+        <v>0.2346</v>
       </c>
       <c r="AA5" s="19" t="n">
-        <v>0.1598000000000001</v>
+        <v>0.1538</v>
       </c>
       <c r="AB5" s="17" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         <v>0.5406</v>
       </c>
       <c r="AI5" s="19" t="n">
-        <v>0.307</v>
+        <v>0.3104</v>
       </c>
       <c r="AJ5" s="19" t="n">
-        <v>0.1198</v>
+        <v>0.1168</v>
       </c>
       <c r="AK5" s="19" t="n">
-        <v>0.03260000000000003</v>
+        <v>0.03220000000000002</v>
       </c>
       <c r="AL5" s="17" t="inlineStr">
         <is>
@@ -6018,16 +6018,16 @@
         <v>1739</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>0.363</v>
+        <v>0.3592</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0.3352</v>
+        <v>0.3336</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0.1968</v>
+        <v>0.1902</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0.105</v>
+        <v>0.117</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
@@ -6046,16 +6046,16 @@
         <v>1687</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>0.3304</v>
+        <v>0.33</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>0.3598</v>
+        <v>0.3552</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>0.2112</v>
+        <v>0.2122</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>0.09859999999999997</v>
+        <v>0.1025999999999999</v>
       </c>
       <c r="R6" s="20" t="inlineStr">
         <is>
@@ -6067,23 +6067,23 @@
       </c>
       <c r="V6" s="21" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="W6" s="20" t="n">
-        <v>1706</v>
+        <v>1734</v>
       </c>
       <c r="X6" s="22" t="n">
-        <v>0.2858</v>
+        <v>0.2862</v>
       </c>
       <c r="Y6" s="22" t="n">
-        <v>0.2808</v>
+        <v>0.269</v>
       </c>
       <c r="Z6" s="22" t="n">
-        <v>0.246</v>
+        <v>0.2456</v>
       </c>
       <c r="AA6" s="22" t="n">
-        <v>0.1874</v>
+        <v>0.1992</v>
       </c>
       <c r="AB6" s="20" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         <v>1821</v>
       </c>
       <c r="AH6" s="22" t="n">
-        <v>0.3476</v>
+        <v>0.3534</v>
       </c>
       <c r="AI6" s="22" t="n">
-        <v>0.4026</v>
+        <v>0.404</v>
       </c>
       <c r="AJ6" s="22" t="n">
-        <v>0.1864</v>
+        <v>0.1758</v>
       </c>
       <c r="AK6" s="22" t="n">
-        <v>0.06339999999999996</v>
+        <v>0.06680000000000003</v>
       </c>
       <c r="AL6" s="20" t="inlineStr">
         <is>
@@ -6132,16 +6132,16 @@
         <v>1579</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.1152</v>
+        <v>0.114</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>0.2044</v>
+        <v>0.202</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.3346</v>
+        <v>0.3382</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.3458</v>
+        <v>0.3457999999999999</v>
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
@@ -6160,16 +6160,16 @@
         <v>1551</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.0998</v>
+        <v>0.1026</v>
       </c>
       <c r="O7" s="25" t="n">
-        <v>0.198</v>
+        <v>0.205</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>0.34</v>
+        <v>0.3502</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>0.3621999999999999</v>
+        <v>0.3422</v>
       </c>
       <c r="R7" s="26" t="inlineStr">
         <is>
@@ -6181,23 +6181,23 @@
       </c>
       <c r="V7" s="24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="W7" s="23" t="n">
-        <v>1734</v>
+        <v>1706</v>
       </c>
       <c r="X7" s="25" t="n">
-        <v>0.2828</v>
+        <v>0.2698</v>
       </c>
       <c r="Y7" s="25" t="n">
-        <v>0.2712</v>
+        <v>0.2806</v>
       </c>
       <c r="Z7" s="25" t="n">
-        <v>0.2486</v>
+        <v>0.259</v>
       </c>
       <c r="AA7" s="25" t="n">
-        <v>0.1974000000000001</v>
+        <v>0.1905999999999999</v>
       </c>
       <c r="AB7" s="26" t="inlineStr">
         <is>
@@ -6216,16 +6216,16 @@
         <v>1611</v>
       </c>
       <c r="AH7" s="25" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="AI7" s="25" t="n">
-        <v>0.1856</v>
+        <v>0.1814</v>
       </c>
       <c r="AJ7" s="25" t="n">
-        <v>0.391</v>
+        <v>0.4084</v>
       </c>
       <c r="AK7" s="25" t="n">
-        <v>0.3442</v>
+        <v>0.3368</v>
       </c>
       <c r="AL7" s="26" t="inlineStr">
         <is>
@@ -6246,16 +6246,16 @@
         <v>1556</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.0772</v>
+        <v>0.0838</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.1632</v>
+        <v>0.1578</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.2922</v>
+        <v>0.304</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.4673999999999999</v>
+        <v>0.4544</v>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
@@ -6274,16 +6274,16 @@
         <v>1475</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>0.0678</v>
+        <v>0.0634</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>0.1464</v>
+        <v>0.1518</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.3072</v>
+        <v>0.2884</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>0.4786000000000001</v>
+        <v>0.4964</v>
       </c>
       <c r="R8" s="30" t="inlineStr">
         <is>
@@ -6302,16 +6302,16 @@
         <v>1637</v>
       </c>
       <c r="X8" s="29" t="n">
-        <v>0.1096</v>
+        <v>0.1094</v>
       </c>
       <c r="Y8" s="29" t="n">
-        <v>0.161</v>
+        <v>0.1734</v>
       </c>
       <c r="Z8" s="29" t="n">
-        <v>0.274</v>
+        <v>0.2608</v>
       </c>
       <c r="AA8" s="29" t="n">
-        <v>0.4553999999999999</v>
+        <v>0.4564000000000001</v>
       </c>
       <c r="AB8" s="30" t="inlineStr">
         <is>
@@ -6333,13 +6333,13 @@
         <v>0.0326</v>
       </c>
       <c r="AI8" s="29" t="n">
-        <v>0.1048</v>
+        <v>0.1042</v>
       </c>
       <c r="AJ8" s="29" t="n">
-        <v>0.3028</v>
+        <v>0.299</v>
       </c>
       <c r="AK8" s="29" t="n">
-        <v>0.5598000000000001</v>
+        <v>0.5642</v>
       </c>
       <c r="AL8" s="30" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         <v>1806</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.575</v>
+        <v>0.5738</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.2588</v>
+        <v>0.2678</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.1264</v>
+        <v>0.1228</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.03980000000000006</v>
+        <v>0.03560000000000003</v>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -6565,23 +6565,23 @@
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="M13" s="17" t="n">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>0.4424</v>
+        <v>0.4496</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>0.3382</v>
+        <v>0.3458</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>0.1542</v>
+        <v>0.1478</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>0.06519999999999998</v>
+        <v>0.05680000000000002</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -6600,16 +6600,16 @@
         <v>1776</v>
       </c>
       <c r="X13" s="19" t="n">
-        <v>0.4438</v>
+        <v>0.445</v>
       </c>
       <c r="Y13" s="19" t="n">
-        <v>0.2846</v>
+        <v>0.2894</v>
       </c>
       <c r="Z13" s="19" t="n">
-        <v>0.1882</v>
+        <v>0.188</v>
       </c>
       <c r="AA13" s="19" t="n">
-        <v>0.0834</v>
+        <v>0.07759999999999995</v>
       </c>
       <c r="AB13" s="17" t="inlineStr">
         <is>
@@ -6628,16 +6628,16 @@
         <v>1959</v>
       </c>
       <c r="AH13" s="19" t="n">
-        <v>0.7678</v>
+        <v>0.781</v>
       </c>
       <c r="AI13" s="19" t="n">
-        <v>0.187</v>
+        <v>0.176</v>
       </c>
       <c r="AJ13" s="19" t="n">
-        <v>0.0392</v>
+        <v>0.0358</v>
       </c>
       <c r="AK13" s="19" t="n">
-        <v>0.005999999999999964</v>
+        <v>0.007199999999999984</v>
       </c>
       <c r="AL13" s="17" t="inlineStr">
         <is>
@@ -6658,16 +6658,16 @@
         <v>1730</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0.2056</v>
+        <v>0.2084</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0.3456</v>
+        <v>0.339</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.3088</v>
+        <v>0.313</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.14</v>
+        <v>0.1395999999999999</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
@@ -6679,23 +6679,23 @@
       </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.4352</v>
+        <v>0.4262</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>0.3508</v>
+        <v>0.3486</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.1542</v>
+        <v>0.1592</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>0.05979999999999996</v>
+        <v>0.06599999999999995</v>
       </c>
       <c r="R14" s="20" t="inlineStr">
         <is>
@@ -6714,16 +6714,16 @@
         <v>1756</v>
       </c>
       <c r="X14" s="22" t="n">
-        <v>0.3344</v>
+        <v>0.3214</v>
       </c>
       <c r="Y14" s="22" t="n">
-        <v>0.3274</v>
+        <v>0.323</v>
       </c>
       <c r="Z14" s="22" t="n">
-        <v>0.2264</v>
+        <v>0.2382</v>
       </c>
       <c r="AA14" s="22" t="n">
-        <v>0.1118</v>
+        <v>0.1174</v>
       </c>
       <c r="AB14" s="20" t="inlineStr">
         <is>
@@ -6742,16 +6742,16 @@
         <v>1745</v>
       </c>
       <c r="AH14" s="22" t="n">
-        <v>0.1648</v>
+        <v>0.1584</v>
       </c>
       <c r="AI14" s="22" t="n">
-        <v>0.4884</v>
+        <v>0.499</v>
       </c>
       <c r="AJ14" s="22" t="n">
-        <v>0.2494</v>
+        <v>0.2406</v>
       </c>
       <c r="AK14" s="22" t="n">
-        <v>0.09739999999999993</v>
+        <v>0.102</v>
       </c>
       <c r="AL14" s="20" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>1662</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.1882</v>
+        <v>0.1914</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.3066</v>
+        <v>0.3006</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.3452</v>
+        <v>0.3406</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>0.16</v>
+        <v>0.1674</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -6800,16 +6800,16 @@
         <v>1625</v>
       </c>
       <c r="N15" s="25" t="n">
-        <v>0.0708</v>
+        <v>0.074</v>
       </c>
       <c r="O15" s="25" t="n">
-        <v>0.1818</v>
+        <v>0.1778</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>0.3908</v>
+        <v>0.4084</v>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>0.3566000000000001</v>
+        <v>0.3398</v>
       </c>
       <c r="R15" s="26" t="inlineStr">
         <is>
@@ -6828,16 +6828,16 @@
         <v>1675</v>
       </c>
       <c r="X15" s="25" t="n">
-        <v>0.1782</v>
+        <v>0.1806</v>
       </c>
       <c r="Y15" s="25" t="n">
-        <v>0.28</v>
+        <v>0.2822</v>
       </c>
       <c r="Z15" s="25" t="n">
-        <v>0.3392</v>
+        <v>0.3304</v>
       </c>
       <c r="AA15" s="25" t="n">
-        <v>0.2025999999999999</v>
+        <v>0.2068</v>
       </c>
       <c r="AB15" s="26" t="inlineStr">
         <is>
@@ -6856,16 +6856,16 @@
         <v>1578</v>
       </c>
       <c r="AH15" s="25" t="n">
-        <v>0.042</v>
+        <v>0.0412</v>
       </c>
       <c r="AI15" s="25" t="n">
-        <v>0.1934</v>
+        <v>0.197</v>
       </c>
       <c r="AJ15" s="25" t="n">
-        <v>0.3898</v>
+        <v>0.3856</v>
       </c>
       <c r="AK15" s="25" t="n">
-        <v>0.3748</v>
+        <v>0.3762</v>
       </c>
       <c r="AL15" s="26" t="inlineStr">
         <is>
@@ -6886,16 +6886,16 @@
         <v>1491</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.0312</v>
+        <v>0.0264</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>0.089</v>
+        <v>0.0926</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>0.2196</v>
+        <v>0.2236</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.6602</v>
+        <v>0.6574</v>
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
@@ -6914,16 +6914,16 @@
         <v>1579</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.0516</v>
+        <v>0.0502</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.1292</v>
+        <v>0.1278</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>0.3008</v>
+        <v>0.2846</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>0.5184</v>
+        <v>0.5373999999999999</v>
       </c>
       <c r="R16" s="30" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         <v>1547</v>
       </c>
       <c r="X16" s="29" t="n">
-        <v>0.0436</v>
+        <v>0.053</v>
       </c>
       <c r="Y16" s="29" t="n">
-        <v>0.108</v>
+        <v>0.1054</v>
       </c>
       <c r="Z16" s="29" t="n">
-        <v>0.2462</v>
+        <v>0.2434</v>
       </c>
       <c r="AA16" s="29" t="n">
-        <v>0.6022000000000001</v>
+        <v>0.5981999999999998</v>
       </c>
       <c r="AB16" s="30" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         <v>1512</v>
       </c>
       <c r="AH16" s="29" t="n">
-        <v>0.0254</v>
+        <v>0.0194</v>
       </c>
       <c r="AI16" s="29" t="n">
-        <v>0.1312</v>
+        <v>0.128</v>
       </c>
       <c r="AJ16" s="29" t="n">
-        <v>0.3216</v>
+        <v>0.338</v>
       </c>
       <c r="AK16" s="29" t="n">
-        <v>0.5218</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="AL16" s="30" t="inlineStr">
         <is>
@@ -7184,16 +7184,16 @@
         <v>1923</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.609</v>
+        <v>0.6088</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.2536</v>
+        <v>0.248</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.1048</v>
+        <v>0.1076</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.03260000000000002</v>
+        <v>0.03559999999999999</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -7212,16 +7212,16 @@
         <v>1925</v>
       </c>
       <c r="N21" s="19" t="n">
-        <v>0.6818</v>
+        <v>0.6844</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>0.215</v>
+        <v>0.214</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>0.0772</v>
+        <v>0.0752</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>0.02600000000000004</v>
+        <v>0.02639999999999999</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -7240,16 +7240,16 @@
         <v>1813</v>
       </c>
       <c r="X21" s="19" t="n">
-        <v>0.4366</v>
+        <v>0.4466</v>
       </c>
       <c r="Y21" s="19" t="n">
-        <v>0.2856</v>
+        <v>0.289</v>
       </c>
       <c r="Z21" s="19" t="n">
-        <v>0.179</v>
+        <v>0.168</v>
       </c>
       <c r="AA21" s="19" t="n">
-        <v>0.0988</v>
+        <v>0.09640000000000001</v>
       </c>
       <c r="AB21" s="17" t="inlineStr">
         <is>
@@ -7268,16 +7268,16 @@
         <v>1890</v>
       </c>
       <c r="AH21" s="19" t="n">
-        <v>0.5594</v>
+        <v>0.5648</v>
       </c>
       <c r="AI21" s="19" t="n">
-        <v>0.2938</v>
+        <v>0.2808</v>
       </c>
       <c r="AJ21" s="19" t="n">
-        <v>0.1208</v>
+        <v>0.1272</v>
       </c>
       <c r="AK21" s="19" t="n">
-        <v>0.02599999999999998</v>
+        <v>0.02720000000000003</v>
       </c>
       <c r="AL21" s="17" t="inlineStr">
         <is>
@@ -7298,16 +7298,16 @@
         <v>1779</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0.2428</v>
+        <v>0.2364</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0.3776</v>
+        <v>0.3638</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>0.2468</v>
+        <v>0.264</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0.1328</v>
+        <v>0.1358</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -7326,16 +7326,16 @@
         <v>1707</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>0.1458</v>
+        <v>0.1496</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>0.3264</v>
+        <v>0.3412</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.317</v>
+        <v>0.304</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0.2107999999999999</v>
+        <v>0.2052000000000001</v>
       </c>
       <c r="R22" s="20" t="inlineStr">
         <is>
@@ -7354,16 +7354,16 @@
         <v>1781</v>
       </c>
       <c r="X22" s="22" t="n">
-        <v>0.3268</v>
+        <v>0.3138</v>
       </c>
       <c r="Y22" s="22" t="n">
-        <v>0.3194</v>
+        <v>0.3082</v>
       </c>
       <c r="Z22" s="22" t="n">
-        <v>0.2062</v>
+        <v>0.233</v>
       </c>
       <c r="AA22" s="22" t="n">
-        <v>0.1476</v>
+        <v>0.1449999999999999</v>
       </c>
       <c r="AB22" s="20" t="inlineStr">
         <is>
@@ -7382,16 +7382,16 @@
         <v>1778</v>
       </c>
       <c r="AH22" s="22" t="n">
-        <v>0.2976</v>
+        <v>0.2998</v>
       </c>
       <c r="AI22" s="22" t="n">
-        <v>0.3986</v>
+        <v>0.3852</v>
       </c>
       <c r="AJ22" s="22" t="n">
-        <v>0.2274</v>
+        <v>0.2352</v>
       </c>
       <c r="AK22" s="22" t="n">
-        <v>0.07640000000000002</v>
+        <v>0.07979999999999995</v>
       </c>
       <c r="AL22" s="20" t="inlineStr">
         <is>
@@ -7412,16 +7412,16 @@
         <v>1692</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.1042</v>
+        <v>0.1032</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0.2366</v>
+        <v>0.2478</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>0.3616</v>
+        <v>0.3522</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>0.2976</v>
+        <v>0.2968</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -7440,16 +7440,16 @@
         <v>1663</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>0.1138</v>
+        <v>0.1104</v>
       </c>
       <c r="O23" s="25" t="n">
-        <v>0.2858</v>
+        <v>0.281</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.3272</v>
+        <v>0.337</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>0.2732000000000001</v>
+        <v>0.2715999999999999</v>
       </c>
       <c r="R23" s="26" t="inlineStr">
         <is>
@@ -7468,16 +7468,16 @@
         <v>1671</v>
       </c>
       <c r="X23" s="25" t="n">
-        <v>0.1432</v>
+        <v>0.1396</v>
       </c>
       <c r="Y23" s="25" t="n">
-        <v>0.218</v>
+        <v>0.2202</v>
       </c>
       <c r="Z23" s="25" t="n">
-        <v>0.3088</v>
+        <v>0.3144</v>
       </c>
       <c r="AA23" s="25" t="n">
-        <v>0.33</v>
+        <v>0.3258000000000001</v>
       </c>
       <c r="AB23" s="26" t="inlineStr">
         <is>
@@ -7496,16 +7496,16 @@
         <v>1673</v>
       </c>
       <c r="AH23" s="25" t="n">
-        <v>0.1236</v>
+        <v>0.1148</v>
       </c>
       <c r="AI23" s="25" t="n">
-        <v>0.237</v>
+        <v>0.2612</v>
       </c>
       <c r="AJ23" s="25" t="n">
-        <v>0.43</v>
+        <v>0.4204</v>
       </c>
       <c r="AK23" s="25" t="n">
-        <v>0.2094</v>
+        <v>0.2036</v>
       </c>
       <c r="AL23" s="26" t="inlineStr">
         <is>
@@ -7526,16 +7526,16 @@
         <v>1615</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>0.044</v>
+        <v>0.0516</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>0.1322</v>
+        <v>0.1404</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0.2868</v>
+        <v>0.2762</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>0.5369999999999999</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
@@ -7554,16 +7554,16 @@
         <v>1607</v>
       </c>
       <c r="N24" s="29" t="n">
-        <v>0.0586</v>
+        <v>0.0556</v>
       </c>
       <c r="O24" s="29" t="n">
-        <v>0.1728</v>
+        <v>0.1638</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.2786</v>
+        <v>0.2838</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>0.4899999999999999</v>
+        <v>0.4968</v>
       </c>
       <c r="R24" s="30" t="inlineStr">
         <is>
@@ -7582,16 +7582,16 @@
         <v>1620</v>
       </c>
       <c r="X24" s="29" t="n">
-        <v>0.0934</v>
+        <v>0.1</v>
       </c>
       <c r="Y24" s="29" t="n">
-        <v>0.177</v>
+        <v>0.1826</v>
       </c>
       <c r="Z24" s="29" t="n">
-        <v>0.306</v>
+        <v>0.2846</v>
       </c>
       <c r="AA24" s="29" t="n">
-        <v>0.4236</v>
+        <v>0.4328</v>
       </c>
       <c r="AB24" s="30" t="inlineStr">
         <is>
@@ -7610,16 +7610,16 @@
         <v>1508</v>
       </c>
       <c r="AH24" s="29" t="n">
-        <v>0.0194</v>
+        <v>0.0206</v>
       </c>
       <c r="AI24" s="29" t="n">
-        <v>0.0706</v>
+        <v>0.0728</v>
       </c>
       <c r="AJ24" s="29" t="n">
-        <v>0.2218</v>
+        <v>0.2172</v>
       </c>
       <c r="AK24" s="29" t="n">
-        <v>0.6882</v>
+        <v>0.6894</v>
       </c>
       <c r="AL24" s="30" t="inlineStr">
         <is>
@@ -7825,15 +7825,15 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.518</v>
+        <v>0.551</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.263</v>
+        <v>0.239</v>
       </c>
       <c r="G6" s="36" t="inlineStr">
         <is>
@@ -7858,19 +7858,19 @@
         </is>
       </c>
       <c r="D7" s="34" t="n">
-        <v>0.389</v>
+        <v>0.382</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F7" s="35" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>→ Netherlands</t>
+          <t>→ Japan</t>
         </is>
       </c>
     </row>
@@ -8089,15 +8089,15 @@
         </is>
       </c>
       <c r="D14" s="34" t="n">
-        <v>0.508</v>
+        <v>0.468</v>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F14" s="35" t="n">
-        <v>0.271</v>
+        <v>0.301</v>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
@@ -8317,23 +8317,23 @@
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D22" s="34" t="n">
-        <v>0.377</v>
+        <v>0.371</v>
       </c>
       <c r="E22" s="39" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F22" s="35" t="n">
-        <v>0.366</v>
+      <c r="F22" s="34" t="n">
+        <v>0.371</v>
       </c>
       <c r="G22" s="40" t="inlineStr">
         <is>
-          <t>→ Netherlands</t>
+          <t>→ Japan</t>
         </is>
       </c>
     </row>
@@ -8549,11 +8549,11 @@
       </c>
       <c r="C30" s="43" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D30" s="34" t="n">
-        <v>0.544</v>
+        <v>0.55</v>
       </c>
       <c r="E30" s="43" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="F30" s="35" t="n">
-        <v>0.244</v>
+        <v>0.24</v>
       </c>
       <c r="G30" s="44" t="inlineStr">
         <is>

--- a/results/excel/Mundial_2026_Predicciones.xlsx
+++ b/results/excel/Mundial_2026_Predicciones.xlsx
@@ -576,13 +576,13 @@
     <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5904,16 +5904,16 @@
         <v>1762</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.443</v>
+        <v>0.4424</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.3066</v>
+        <v>0.3118</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1676</v>
+        <v>0.1604</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.08279999999999996</v>
+        <v>0.08539999999999998</v>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
@@ -5932,16 +5932,16 @@
         <v>1735</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>0.504</v>
+        <v>0.493</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>0.288</v>
+        <v>0.2984</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.1492</v>
+        <v>0.1396</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>0.05880000000000002</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -5960,16 +5960,16 @@
         <v>1747</v>
       </c>
       <c r="X5" s="19" t="n">
-        <v>0.3346</v>
+        <v>0.3432</v>
       </c>
       <c r="Y5" s="19" t="n">
-        <v>0.277</v>
+        <v>0.2562</v>
       </c>
       <c r="Z5" s="19" t="n">
-        <v>0.2346</v>
+        <v>0.2434</v>
       </c>
       <c r="AA5" s="19" t="n">
-        <v>0.1538</v>
+        <v>0.1572000000000001</v>
       </c>
       <c r="AB5" s="17" t="inlineStr">
         <is>
@@ -5988,16 +5988,16 @@
         <v>1851</v>
       </c>
       <c r="AH5" s="19" t="n">
-        <v>0.5406</v>
+        <v>0.527</v>
       </c>
       <c r="AI5" s="19" t="n">
-        <v>0.3104</v>
+        <v>0.3218</v>
       </c>
       <c r="AJ5" s="19" t="n">
-        <v>0.1168</v>
+        <v>0.1202</v>
       </c>
       <c r="AK5" s="19" t="n">
-        <v>0.03220000000000002</v>
+        <v>0.031</v>
       </c>
       <c r="AL5" s="17" t="inlineStr">
         <is>
@@ -6018,16 +6018,16 @@
         <v>1739</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>0.3592</v>
+        <v>0.3598</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0.3336</v>
+        <v>0.3226</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0.1902</v>
+        <v>0.2088</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0.117</v>
+        <v>0.1088</v>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
@@ -6046,16 +6046,16 @@
         <v>1687</v>
       </c>
       <c r="N6" s="22" t="n">
-        <v>0.33</v>
+        <v>0.339</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>0.3552</v>
+        <v>0.3432</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>0.2122</v>
+        <v>0.217</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>0.1025999999999999</v>
+        <v>0.1008</v>
       </c>
       <c r="R6" s="20" t="inlineStr">
         <is>
@@ -6074,16 +6074,16 @@
         <v>1734</v>
       </c>
       <c r="X6" s="22" t="n">
-        <v>0.2862</v>
+        <v>0.2812</v>
       </c>
       <c r="Y6" s="22" t="n">
-        <v>0.269</v>
+        <v>0.2804</v>
       </c>
       <c r="Z6" s="22" t="n">
-        <v>0.2456</v>
+        <v>0.2406</v>
       </c>
       <c r="AA6" s="22" t="n">
-        <v>0.1992</v>
+        <v>0.1978</v>
       </c>
       <c r="AB6" s="20" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         <v>1821</v>
       </c>
       <c r="AH6" s="22" t="n">
-        <v>0.3534</v>
+        <v>0.3636</v>
       </c>
       <c r="AI6" s="22" t="n">
-        <v>0.404</v>
+        <v>0.3928</v>
       </c>
       <c r="AJ6" s="22" t="n">
-        <v>0.1758</v>
+        <v>0.1806</v>
       </c>
       <c r="AK6" s="22" t="n">
-        <v>0.06680000000000003</v>
+        <v>0.06300000000000008</v>
       </c>
       <c r="AL6" s="20" t="inlineStr">
         <is>
@@ -6132,16 +6132,16 @@
         <v>1579</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.114</v>
+        <v>0.1188</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>0.202</v>
+        <v>0.2122</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.3382</v>
+        <v>0.3232</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.3457999999999999</v>
+        <v>0.3458000000000001</v>
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
@@ -6160,16 +6160,16 @@
         <v>1551</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.1026</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="O7" s="25" t="n">
-        <v>0.205</v>
+        <v>0.2056</v>
       </c>
       <c r="P7" s="25" t="n">
-        <v>0.3502</v>
+        <v>0.3418</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <v>0.3422</v>
+        <v>0.353</v>
       </c>
       <c r="R7" s="26" t="inlineStr">
         <is>
@@ -6188,16 +6188,16 @@
         <v>1706</v>
       </c>
       <c r="X7" s="25" t="n">
-        <v>0.2698</v>
+        <v>0.2764</v>
       </c>
       <c r="Y7" s="25" t="n">
-        <v>0.2806</v>
+        <v>0.292</v>
       </c>
       <c r="Z7" s="25" t="n">
-        <v>0.259</v>
+        <v>0.2432</v>
       </c>
       <c r="AA7" s="25" t="n">
-        <v>0.1905999999999999</v>
+        <v>0.1884</v>
       </c>
       <c r="AB7" s="26" t="inlineStr">
         <is>
@@ -6216,16 +6216,16 @@
         <v>1611</v>
       </c>
       <c r="AH7" s="25" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0774</v>
       </c>
       <c r="AI7" s="25" t="n">
-        <v>0.1814</v>
+        <v>0.1824</v>
       </c>
       <c r="AJ7" s="25" t="n">
-        <v>0.4084</v>
+        <v>0.4054</v>
       </c>
       <c r="AK7" s="25" t="n">
-        <v>0.3368</v>
+        <v>0.3348</v>
       </c>
       <c r="AL7" s="26" t="inlineStr">
         <is>
@@ -6246,16 +6246,16 @@
         <v>1556</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.0838</v>
+        <v>0.079</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.1578</v>
+        <v>0.1534</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>0.304</v>
+        <v>0.3076</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.4544</v>
+        <v>0.4600000000000001</v>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
@@ -6274,16 +6274,16 @@
         <v>1475</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>0.0634</v>
+        <v>0.0684</v>
       </c>
       <c r="O8" s="29" t="n">
-        <v>0.1518</v>
+        <v>0.1528</v>
       </c>
       <c r="P8" s="29" t="n">
-        <v>0.2884</v>
+        <v>0.3016</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>0.4964</v>
+        <v>0.4772</v>
       </c>
       <c r="R8" s="30" t="inlineStr">
         <is>
@@ -6302,16 +6302,16 @@
         <v>1637</v>
       </c>
       <c r="X8" s="29" t="n">
-        <v>0.1094</v>
+        <v>0.0992</v>
       </c>
       <c r="Y8" s="29" t="n">
-        <v>0.1734</v>
+        <v>0.1714</v>
       </c>
       <c r="Z8" s="29" t="n">
-        <v>0.2608</v>
+        <v>0.2728</v>
       </c>
       <c r="AA8" s="29" t="n">
-        <v>0.4564000000000001</v>
+        <v>0.4566000000000001</v>
       </c>
       <c r="AB8" s="30" t="inlineStr">
         <is>
@@ -6330,16 +6330,16 @@
         <v>1509</v>
       </c>
       <c r="AH8" s="29" t="n">
-        <v>0.0326</v>
+        <v>0.032</v>
       </c>
       <c r="AI8" s="29" t="n">
-        <v>0.1042</v>
+        <v>0.103</v>
       </c>
       <c r="AJ8" s="29" t="n">
-        <v>0.299</v>
+        <v>0.2938</v>
       </c>
       <c r="AK8" s="29" t="n">
-        <v>0.5642</v>
+        <v>0.5711999999999999</v>
       </c>
       <c r="AL8" s="30" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         <v>1806</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>0.5738</v>
+        <v>0.577</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.2678</v>
+        <v>0.2642</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.1228</v>
+        <v>0.1186</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.03560000000000003</v>
+        <v>0.04020000000000006</v>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
@@ -6572,16 +6572,16 @@
         <v>1815</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>0.4496</v>
+        <v>0.4396</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>0.3458</v>
+        <v>0.3476</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>0.1478</v>
+        <v>0.1592</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>0.05680000000000002</v>
+        <v>0.05359999999999998</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -6600,16 +6600,16 @@
         <v>1776</v>
       </c>
       <c r="X13" s="19" t="n">
-        <v>0.445</v>
+        <v>0.4542</v>
       </c>
       <c r="Y13" s="19" t="n">
-        <v>0.2894</v>
+        <v>0.2944</v>
       </c>
       <c r="Z13" s="19" t="n">
-        <v>0.188</v>
+        <v>0.177</v>
       </c>
       <c r="AA13" s="19" t="n">
-        <v>0.07759999999999995</v>
+        <v>0.07440000000000008</v>
       </c>
       <c r="AB13" s="17" t="inlineStr">
         <is>
@@ -6628,16 +6628,16 @@
         <v>1959</v>
       </c>
       <c r="AH13" s="19" t="n">
-        <v>0.781</v>
+        <v>0.7824</v>
       </c>
       <c r="AI13" s="19" t="n">
-        <v>0.176</v>
+        <v>0.169</v>
       </c>
       <c r="AJ13" s="19" t="n">
-        <v>0.0358</v>
+        <v>0.0414</v>
       </c>
       <c r="AK13" s="19" t="n">
-        <v>0.007199999999999984</v>
+        <v>0.007200000000000005</v>
       </c>
       <c r="AL13" s="17" t="inlineStr">
         <is>
@@ -6658,16 +6658,16 @@
         <v>1730</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0.2084</v>
+        <v>0.2086</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0.339</v>
+        <v>0.3348</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.313</v>
+        <v>0.318</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.1395999999999999</v>
+        <v>0.1386</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
@@ -6686,16 +6686,16 @@
         <v>1820</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>0.4262</v>
+        <v>0.4376</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>0.3486</v>
+        <v>0.3474</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>0.1592</v>
+        <v>0.1546</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>0.06599999999999995</v>
+        <v>0.06040000000000004</v>
       </c>
       <c r="R14" s="20" t="inlineStr">
         <is>
@@ -6714,16 +6714,16 @@
         <v>1756</v>
       </c>
       <c r="X14" s="22" t="n">
-        <v>0.3214</v>
+        <v>0.328</v>
       </c>
       <c r="Y14" s="22" t="n">
-        <v>0.323</v>
+        <v>0.3312</v>
       </c>
       <c r="Z14" s="22" t="n">
-        <v>0.2382</v>
+        <v>0.2314</v>
       </c>
       <c r="AA14" s="22" t="n">
-        <v>0.1174</v>
+        <v>0.1093999999999999</v>
       </c>
       <c r="AB14" s="20" t="inlineStr">
         <is>
@@ -6742,16 +6742,16 @@
         <v>1745</v>
       </c>
       <c r="AH14" s="22" t="n">
-        <v>0.1584</v>
+        <v>0.157</v>
       </c>
       <c r="AI14" s="22" t="n">
-        <v>0.499</v>
+        <v>0.5104</v>
       </c>
       <c r="AJ14" s="22" t="n">
-        <v>0.2406</v>
+        <v>0.236</v>
       </c>
       <c r="AK14" s="22" t="n">
-        <v>0.102</v>
+        <v>0.09660000000000002</v>
       </c>
       <c r="AL14" s="20" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>1662</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.1914</v>
+        <v>0.181</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.3006</v>
+        <v>0.314</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>0.3406</v>
+        <v>0.3452</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>0.1674</v>
+        <v>0.1597999999999999</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -6800,16 +6800,16 @@
         <v>1625</v>
       </c>
       <c r="N15" s="25" t="n">
-        <v>0.074</v>
+        <v>0.0746</v>
       </c>
       <c r="O15" s="25" t="n">
-        <v>0.1778</v>
+        <v>0.18</v>
       </c>
       <c r="P15" s="25" t="n">
-        <v>0.4084</v>
+        <v>0.39</v>
       </c>
       <c r="Q15" s="25" t="n">
-        <v>0.3398</v>
+        <v>0.3554</v>
       </c>
       <c r="R15" s="26" t="inlineStr">
         <is>
@@ -6828,16 +6828,16 @@
         <v>1675</v>
       </c>
       <c r="X15" s="25" t="n">
-        <v>0.1806</v>
+        <v>0.17</v>
       </c>
       <c r="Y15" s="25" t="n">
-        <v>0.2822</v>
+        <v>0.262</v>
       </c>
       <c r="Z15" s="25" t="n">
-        <v>0.3304</v>
+        <v>0.3562</v>
       </c>
       <c r="AA15" s="25" t="n">
-        <v>0.2068</v>
+        <v>0.2117999999999999</v>
       </c>
       <c r="AB15" s="26" t="inlineStr">
         <is>
@@ -6856,13 +6856,13 @@
         <v>1578</v>
       </c>
       <c r="AH15" s="25" t="n">
-        <v>0.0412</v>
+        <v>0.0386</v>
       </c>
       <c r="AI15" s="25" t="n">
-        <v>0.197</v>
+        <v>0.1856</v>
       </c>
       <c r="AJ15" s="25" t="n">
-        <v>0.3856</v>
+        <v>0.3996</v>
       </c>
       <c r="AK15" s="25" t="n">
         <v>0.3762</v>
@@ -6886,16 +6886,16 @@
         <v>1491</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>0.0264</v>
+        <v>0.0334</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>0.0926</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>0.2236</v>
+        <v>0.2182</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.6574</v>
+        <v>0.6614</v>
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
@@ -6914,16 +6914,16 @@
         <v>1579</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>0.0502</v>
+        <v>0.0482</v>
       </c>
       <c r="O16" s="29" t="n">
-        <v>0.1278</v>
+        <v>0.125</v>
       </c>
       <c r="P16" s="29" t="n">
-        <v>0.2846</v>
+        <v>0.2962</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>0.5373999999999999</v>
+        <v>0.5306</v>
       </c>
       <c r="R16" s="30" t="inlineStr">
         <is>
@@ -6942,16 +6942,16 @@
         <v>1547</v>
       </c>
       <c r="X16" s="29" t="n">
-        <v>0.053</v>
+        <v>0.0478</v>
       </c>
       <c r="Y16" s="29" t="n">
-        <v>0.1054</v>
+        <v>0.1124</v>
       </c>
       <c r="Z16" s="29" t="n">
-        <v>0.2434</v>
+        <v>0.2354</v>
       </c>
       <c r="AA16" s="29" t="n">
-        <v>0.5981999999999998</v>
+        <v>0.6044</v>
       </c>
       <c r="AB16" s="30" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         <v>1512</v>
       </c>
       <c r="AH16" s="29" t="n">
-        <v>0.0194</v>
+        <v>0.022</v>
       </c>
       <c r="AI16" s="29" t="n">
-        <v>0.128</v>
+        <v>0.135</v>
       </c>
       <c r="AJ16" s="29" t="n">
-        <v>0.338</v>
+        <v>0.323</v>
       </c>
       <c r="AK16" s="29" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="AL16" s="30" t="inlineStr">
         <is>
@@ -7184,16 +7184,16 @@
         <v>1923</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.6088</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.248</v>
+        <v>0.259</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.1076</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.03559999999999999</v>
+        <v>0.03539999999999995</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -7212,16 +7212,16 @@
         <v>1925</v>
       </c>
       <c r="N21" s="19" t="n">
-        <v>0.6844</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>0.214</v>
+        <v>0.2066</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>0.0752</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>0.02639999999999999</v>
+        <v>0.02700000000000004</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -7240,16 +7240,16 @@
         <v>1813</v>
       </c>
       <c r="X21" s="19" t="n">
-        <v>0.4466</v>
+        <v>0.4526</v>
       </c>
       <c r="Y21" s="19" t="n">
-        <v>0.289</v>
+        <v>0.2916</v>
       </c>
       <c r="Z21" s="19" t="n">
-        <v>0.168</v>
+        <v>0.1632</v>
       </c>
       <c r="AA21" s="19" t="n">
-        <v>0.09640000000000001</v>
+        <v>0.09259999999999996</v>
       </c>
       <c r="AB21" s="17" t="inlineStr">
         <is>
@@ -7268,16 +7268,16 @@
         <v>1890</v>
       </c>
       <c r="AH21" s="19" t="n">
-        <v>0.5648</v>
+        <v>0.5698</v>
       </c>
       <c r="AI21" s="19" t="n">
-        <v>0.2808</v>
+        <v>0.28</v>
       </c>
       <c r="AJ21" s="19" t="n">
-        <v>0.1272</v>
+        <v>0.1238</v>
       </c>
       <c r="AK21" s="19" t="n">
-        <v>0.02720000000000003</v>
+        <v>0.02640000000000001</v>
       </c>
       <c r="AL21" s="17" t="inlineStr">
         <is>
@@ -7298,16 +7298,16 @@
         <v>1779</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0.2364</v>
+        <v>0.2434</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0.3638</v>
+        <v>0.378</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>0.264</v>
+        <v>0.2528</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0.1358</v>
+        <v>0.1257999999999999</v>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
@@ -7326,16 +7326,16 @@
         <v>1707</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>0.1496</v>
+        <v>0.1504</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>0.3412</v>
+        <v>0.3416</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>0.304</v>
+        <v>0.3038</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0.2052000000000001</v>
+        <v>0.2042</v>
       </c>
       <c r="R22" s="20" t="inlineStr">
         <is>
@@ -7357,13 +7357,13 @@
         <v>0.3138</v>
       </c>
       <c r="Y22" s="22" t="n">
-        <v>0.3082</v>
+        <v>0.3132</v>
       </c>
       <c r="Z22" s="22" t="n">
-        <v>0.233</v>
+        <v>0.221</v>
       </c>
       <c r="AA22" s="22" t="n">
-        <v>0.1449999999999999</v>
+        <v>0.1519999999999999</v>
       </c>
       <c r="AB22" s="20" t="inlineStr">
         <is>
@@ -7382,16 +7382,16 @@
         <v>1778</v>
       </c>
       <c r="AH22" s="22" t="n">
-        <v>0.2998</v>
+        <v>0.2874</v>
       </c>
       <c r="AI22" s="22" t="n">
-        <v>0.3852</v>
+        <v>0.3922</v>
       </c>
       <c r="AJ22" s="22" t="n">
-        <v>0.2352</v>
+        <v>0.2428</v>
       </c>
       <c r="AK22" s="22" t="n">
-        <v>0.07979999999999995</v>
+        <v>0.07760000000000003</v>
       </c>
       <c r="AL22" s="20" t="inlineStr">
         <is>
@@ -7412,16 +7412,16 @@
         <v>1692</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.1032</v>
+        <v>0.1044</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0.2478</v>
+        <v>0.2328</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>0.3522</v>
+        <v>0.374</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>0.2968</v>
+        <v>0.2887999999999999</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -7440,16 +7440,16 @@
         <v>1663</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>0.1104</v>
+        <v>0.1024</v>
       </c>
       <c r="O23" s="25" t="n">
-        <v>0.281</v>
+        <v>0.2776</v>
       </c>
       <c r="P23" s="25" t="n">
-        <v>0.337</v>
+        <v>0.345</v>
       </c>
       <c r="Q23" s="25" t="n">
-        <v>0.2715999999999999</v>
+        <v>0.2749999999999999</v>
       </c>
       <c r="R23" s="26" t="inlineStr">
         <is>
@@ -7468,16 +7468,16 @@
         <v>1671</v>
       </c>
       <c r="X23" s="25" t="n">
-        <v>0.1396</v>
+        <v>0.1364</v>
       </c>
       <c r="Y23" s="25" t="n">
-        <v>0.2202</v>
+        <v>0.217</v>
       </c>
       <c r="Z23" s="25" t="n">
-        <v>0.3144</v>
+        <v>0.3214</v>
       </c>
       <c r="AA23" s="25" t="n">
-        <v>0.3258000000000001</v>
+        <v>0.3252</v>
       </c>
       <c r="AB23" s="26" t="inlineStr">
         <is>
@@ -7496,16 +7496,16 @@
         <v>1673</v>
       </c>
       <c r="AH23" s="25" t="n">
-        <v>0.1148</v>
+        <v>0.1224</v>
       </c>
       <c r="AI23" s="25" t="n">
-        <v>0.2612</v>
+        <v>0.2556</v>
       </c>
       <c r="AJ23" s="25" t="n">
-        <v>0.4204</v>
+        <v>0.4186</v>
       </c>
       <c r="AK23" s="25" t="n">
-        <v>0.2036</v>
+        <v>0.2034000000000001</v>
       </c>
       <c r="AL23" s="26" t="inlineStr">
         <is>
@@ -7526,16 +7526,16 @@
         <v>1615</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>0.0516</v>
+        <v>0.0428</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>0.1404</v>
+        <v>0.1302</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0.2762</v>
+        <v>0.277</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H24" s="30" t="inlineStr">
         <is>
@@ -7554,16 +7554,16 @@
         <v>1607</v>
       </c>
       <c r="N24" s="29" t="n">
-        <v>0.0556</v>
+        <v>0.0542</v>
       </c>
       <c r="O24" s="29" t="n">
-        <v>0.1638</v>
+        <v>0.1742</v>
       </c>
       <c r="P24" s="29" t="n">
-        <v>0.2838</v>
+        <v>0.2778</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>0.4968</v>
+        <v>0.4938</v>
       </c>
       <c r="R24" s="30" t="inlineStr">
         <is>
@@ -7582,16 +7582,16 @@
         <v>1620</v>
       </c>
       <c r="X24" s="29" t="n">
-        <v>0.1</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="Y24" s="29" t="n">
-        <v>0.1826</v>
+        <v>0.1782</v>
       </c>
       <c r="Z24" s="29" t="n">
-        <v>0.2846</v>
+        <v>0.2944</v>
       </c>
       <c r="AA24" s="29" t="n">
-        <v>0.4328</v>
+        <v>0.4302</v>
       </c>
       <c r="AB24" s="30" t="inlineStr">
         <is>
@@ -7610,16 +7610,16 @@
         <v>1508</v>
       </c>
       <c r="AH24" s="29" t="n">
-        <v>0.0206</v>
+        <v>0.0204</v>
       </c>
       <c r="AI24" s="29" t="n">
-        <v>0.0728</v>
+        <v>0.0722</v>
       </c>
       <c r="AJ24" s="29" t="n">
-        <v>0.2172</v>
+        <v>0.2148</v>
       </c>
       <c r="AK24" s="29" t="n">
-        <v>0.6894</v>
+        <v>0.6926</v>
       </c>
       <c r="AL24" s="30" t="inlineStr">
         <is>
@@ -7758,16 +7758,16 @@
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D4" s="35" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="n">
         <v>0.376</v>
-      </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="F4" s="35" t="n">
-        <v>0.366</v>
       </c>
       <c r="G4" s="36" t="inlineStr">
         <is>
@@ -7791,16 +7791,16 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="35" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="n">
         <v>0.464</v>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>0.303</v>
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
@@ -7825,15 +7825,15 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.551</v>
+        <v>0.518</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.239</v>
+        <v>0.263</v>
       </c>
       <c r="G6" s="36" t="inlineStr">
         <is>
@@ -7857,20 +7857,20 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D7" s="34" t="n">
-        <v>0.382</v>
+      <c r="D7" s="35" t="n">
+        <v>0.358</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0.362</v>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0.389</v>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>→ Japan</t>
+          <t>→ Netherlands</t>
         </is>
       </c>
     </row>
@@ -8089,15 +8089,15 @@
         </is>
       </c>
       <c r="D14" s="34" t="n">
-        <v>0.468</v>
+        <v>0.508</v>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F14" s="35" t="n">
-        <v>0.301</v>
+        <v>0.271</v>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
@@ -8287,16 +8287,16 @@
           <t>Brazil</t>
         </is>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="35" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="n">
         <v>0.408</v>
-      </c>
-      <c r="E21" s="39" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>0.344</v>
       </c>
       <c r="G21" s="40" t="inlineStr">
         <is>
@@ -8317,23 +8317,23 @@
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="D22" s="34" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="E22" s="39" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F22" s="34" t="n">
-        <v>0.371</v>
+      <c r="F22" s="35" t="n">
+        <v>0.366</v>
       </c>
       <c r="G22" s="40" t="inlineStr">
         <is>
-          <t>→ Japan</t>
+          <t>→ Netherlands</t>
         </is>
       </c>
     </row>
@@ -8353,16 +8353,16 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="D23" s="34" t="n">
+      <c r="D23" s="35" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="E23" s="39" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="n">
         <v>0.594</v>
-      </c>
-      <c r="E23" s="39" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>0.207</v>
       </c>
       <c r="G23" s="40" t="inlineStr">
         <is>
@@ -8386,16 +8386,16 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="35" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="E24" s="39" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F24" s="34" t="n">
         <v>0.373</v>
-      </c>
-      <c r="E24" s="39" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="n">
-        <v>0.369</v>
       </c>
       <c r="G24" s="40" t="inlineStr">
         <is>
@@ -8419,16 +8419,16 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="35" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="E25" s="39" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F25" s="34" t="n">
         <v>0.468</v>
-      </c>
-      <c r="E25" s="39" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>0.301</v>
       </c>
       <c r="G25" s="40" t="inlineStr">
         <is>
@@ -8452,16 +8452,16 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="35" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="E26" s="39" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F26" s="34" t="n">
         <v>0.501</v>
-      </c>
-      <c r="E26" s="39" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="n">
-        <v>0.276</v>
       </c>
       <c r="G26" s="40" t="inlineStr">
         <is>
@@ -8485,16 +8485,16 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="D27" s="34" t="n">
+      <c r="D27" s="35" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="E27" s="39" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="n">
         <v>0.594</v>
-      </c>
-      <c r="E27" s="39" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="n">
-        <v>0.207</v>
       </c>
       <c r="G27" s="40" t="inlineStr">
         <is>
@@ -8519,16 +8519,16 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="35" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="E29" s="43" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="n">
         <v>0.483</v>
-      </c>
-      <c r="E29" s="43" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="n">
-        <v>0.289</v>
       </c>
       <c r="G29" s="44" t="inlineStr">
         <is>
@@ -8549,19 +8549,19 @@
       </c>
       <c r="C30" s="43" t="inlineStr">
         <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="n">
-        <v>0.55</v>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="n">
+        <v>0.244</v>
       </c>
       <c r="E30" s="43" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="F30" s="35" t="n">
-        <v>0.24</v>
+      <c r="F30" s="34" t="n">
+        <v>0.544</v>
       </c>
       <c r="G30" s="44" t="inlineStr">
         <is>
@@ -8618,16 +8618,16 @@
           <t>Morocco</t>
         </is>
       </c>
-      <c r="D32" s="34" t="n">
+      <c r="D32" s="35" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="E32" s="43" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F32" s="34" t="n">
         <v>0.507</v>
-      </c>
-      <c r="E32" s="43" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F32" s="35" t="n">
-        <v>0.272</v>
       </c>
       <c r="G32" s="44" t="inlineStr">
         <is>
@@ -8652,16 +8652,16 @@
           <t>Morocco</t>
         </is>
       </c>
-      <c r="D34" s="34" t="n">
+      <c r="D34" s="35" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="E34" s="47" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F34" s="34" t="n">
         <v>0.507</v>
-      </c>
-      <c r="E34" s="47" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F34" s="35" t="n">
-        <v>0.272</v>
       </c>
       <c r="G34" s="48" t="inlineStr">
         <is>
@@ -8685,16 +8685,16 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="D35" s="34" t="n">
+      <c r="D35" s="35" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E35" s="47" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F35" s="34" t="n">
         <v>0.414</v>
-      </c>
-      <c r="E35" s="47" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F35" s="35" t="n">
-        <v>0.34</v>
       </c>
       <c r="G35" s="48" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8824,11 +8824,11 @@
         <v>0.2285</v>
       </c>
       <c r="E3" s="55" t="n">
-        <v>0.2316</v>
+        <v>0.2321</v>
       </c>
       <c r="F3" s="56" t="inlineStr">
         <is>
-          <t>↑ 0.3%</t>
+          <t>↑ 0.4%</t>
         </is>
       </c>
       <c r="G3" s="57" t="inlineStr">
@@ -8855,16 +8855,16 @@
         <v>0.1168</v>
       </c>
       <c r="E4" s="61" t="n">
-        <v>0.1469</v>
+        <v>0.1443</v>
       </c>
       <c r="F4" s="62" t="inlineStr">
         <is>
-          <t>↑ 3.0%</t>
+          <t>↑ 2.8%</t>
         </is>
       </c>
       <c r="G4" s="63" t="inlineStr">
         <is>
-          <t>██████████████████████░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█████████████████████░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -8886,11 +8886,11 @@
         <v>0.11</v>
       </c>
       <c r="E5" s="67" t="n">
-        <v>0.1415</v>
+        <v>0.1413</v>
       </c>
       <c r="F5" s="68" t="inlineStr">
         <is>
-          <t>↑ 3.2%</t>
+          <t>↑ 3.1%</t>
         </is>
       </c>
       <c r="G5" s="69" t="inlineStr">
@@ -8917,11 +8917,11 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="E6" s="70" t="n">
-        <v>0.0852</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="F6" s="71" t="inlineStr">
         <is>
-          <t>→ 0.0%</t>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G6" s="72" t="inlineStr">
@@ -8948,11 +8948,11 @@
         <v>0.0702</v>
       </c>
       <c r="E7" s="73" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F7" s="74" t="inlineStr">
         <is>
-          <t>↑ 0.4%</t>
+          <t>↑ 0.5%</t>
         </is>
       </c>
       <c r="G7" s="75" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -8976,14 +8976,14 @@
         </is>
       </c>
       <c r="D8" s="70" t="n">
-        <v>0.0313</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E8" s="70" t="n">
-        <v>0.0428</v>
+        <v>0.043</v>
       </c>
       <c r="F8" s="76" t="inlineStr">
         <is>
-          <t>↑ 1.2%</t>
+          <t>↓ 3.2%</t>
         </is>
       </c>
       <c r="G8" s="72" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -9007,14 +9007,14 @@
         </is>
       </c>
       <c r="D9" s="73" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0313</v>
       </c>
       <c r="E9" s="73" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="F9" s="77" t="inlineStr">
-        <is>
-          <t>↓ 3.2%</t>
+        <v>0.0416</v>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>↑ 1.0%</t>
         </is>
       </c>
       <c r="G9" s="75" t="inlineStr">
@@ -9041,7 +9041,7 @@
         <v>0.0334</v>
       </c>
       <c r="E10" s="70" t="n">
-        <v>0.0314</v>
+        <v>0.0318</v>
       </c>
       <c r="F10" s="71" t="inlineStr">
         <is>
@@ -9072,11 +9072,11 @@
         <v>0.0199</v>
       </c>
       <c r="E11" s="73" t="n">
-        <v>0.0302</v>
+        <v>0.0307</v>
       </c>
       <c r="F11" s="74" t="inlineStr">
         <is>
-          <t>↑ 1.0%</t>
+          <t>↑ 1.1%</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
@@ -9103,9 +9103,9 @@
         <v>0.0193</v>
       </c>
       <c r="E12" s="70" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="F12" s="76" t="inlineStr">
+        <v>0.0243</v>
+      </c>
+      <c r="F12" s="77" t="inlineStr">
         <is>
           <t>↑ 0.5%</t>
         </is>
@@ -9134,9 +9134,9 @@
         <v>0.0229</v>
       </c>
       <c r="E13" s="73" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="F13" s="77" t="inlineStr">
+        <v>0.0187</v>
+      </c>
+      <c r="F13" s="78" t="inlineStr">
         <is>
           <t>↓ 0.4%</t>
         </is>
@@ -9165,11 +9165,11 @@
         <v>0.018</v>
       </c>
       <c r="E14" s="70" t="n">
-        <v>0.017</v>
+        <v>0.0182</v>
       </c>
       <c r="F14" s="71" t="inlineStr">
         <is>
-          <t>→ 0.1%</t>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G14" s="72" t="inlineStr">
@@ -9196,11 +9196,11 @@
         <v>0.0108</v>
       </c>
       <c r="E15" s="73" t="n">
-        <v>0.0169</v>
+        <v>0.0175</v>
       </c>
       <c r="F15" s="74" t="inlineStr">
         <is>
-          <t>↑ 0.6%</t>
+          <t>↑ 0.7%</t>
         </is>
       </c>
       <c r="G15" s="75" t="inlineStr">
@@ -9227,11 +9227,11 @@
         <v>0.011</v>
       </c>
       <c r="E16" s="70" t="n">
-        <v>0.0147</v>
-      </c>
-      <c r="F16" s="76" t="inlineStr">
-        <is>
-          <t>↑ 0.4%</t>
+        <v>0.0144</v>
+      </c>
+      <c r="F16" s="77" t="inlineStr">
+        <is>
+          <t>↑ 0.3%</t>
         </is>
       </c>
       <c r="G16" s="72" t="inlineStr">
@@ -9258,9 +9258,9 @@
         <v>0.0259</v>
       </c>
       <c r="E17" s="73" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="F17" s="77" t="inlineStr">
+        <v>0.0109</v>
+      </c>
+      <c r="F17" s="78" t="inlineStr">
         <is>
           <t>↓ 1.5%</t>
         </is>
@@ -9289,11 +9289,11 @@
         <v>0.018</v>
       </c>
       <c r="E18" s="70" t="n">
-        <v>0.0098</v>
-      </c>
-      <c r="F18" s="78" t="inlineStr">
-        <is>
-          <t>↓ 0.8%</t>
+        <v>0.0095</v>
+      </c>
+      <c r="F18" s="76" t="inlineStr">
+        <is>
+          <t>↓ 0.9%</t>
         </is>
       </c>
       <c r="G18" s="72" t="inlineStr">
@@ -9320,7 +9320,7 @@
         <v>0.0092</v>
       </c>
       <c r="E19" s="73" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F19" s="79" t="inlineStr">
         <is>
@@ -9351,11 +9351,11 @@
         <v>0.0098</v>
       </c>
       <c r="E20" s="70" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>→ 0.1%</t>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G20" s="72" t="inlineStr">
@@ -9370,23 +9370,23 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo G</t>
         </is>
       </c>
       <c r="D21" s="73" t="n">
-        <v>0.0102</v>
+        <v>0.0124</v>
       </c>
       <c r="E21" s="73" t="n">
-        <v>0.005600000000000001</v>
-      </c>
-      <c r="F21" s="77" t="inlineStr">
-        <is>
-          <t>↓ 0.5%</t>
+        <v>0.0061</v>
+      </c>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>↓ 0.6%</t>
         </is>
       </c>
       <c r="G21" s="75" t="inlineStr">
@@ -9401,23 +9401,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Grupo G</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D22" s="70" t="n">
-        <v>0.0124</v>
+        <v>0.0102</v>
       </c>
       <c r="E22" s="70" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="F22" s="78" t="inlineStr">
-        <is>
-          <t>↓ 0.7%</t>
+        <v>0.0058</v>
+      </c>
+      <c r="F22" s="76" t="inlineStr">
+        <is>
+          <t>↓ 0.4%</t>
         </is>
       </c>
       <c r="G22" s="72" t="inlineStr">
@@ -9432,19 +9432,19 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo C</t>
         </is>
       </c>
       <c r="D23" s="73" t="n">
-        <v>0.0039</v>
+        <v>0.0028</v>
       </c>
       <c r="E23" s="73" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F23" s="79" t="inlineStr">
         <is>
@@ -9463,23 +9463,23 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Grupo C</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D24" s="70" t="n">
-        <v>0.0028</v>
+        <v>0.0039</v>
       </c>
       <c r="E24" s="70" t="n">
-        <v>0.0044</v>
+        <v>0.004</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>→ 0.2%</t>
+          <t>→ 0.0%</t>
         </is>
       </c>
       <c r="G24" s="72" t="inlineStr">
@@ -9506,9 +9506,9 @@
         <v>0.0086</v>
       </c>
       <c r="E25" s="73" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="F25" s="77" t="inlineStr">
+        <v>0.0036</v>
+      </c>
+      <c r="F25" s="78" t="inlineStr">
         <is>
           <t>↓ 0.5%</t>
         </is>
@@ -9537,7 +9537,7 @@
         <v>0.0063</v>
       </c>
       <c r="E26" s="70" t="n">
-        <v>0.0033</v>
+        <v>0.0035</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
@@ -9568,11 +9568,11 @@
         <v>0.0059</v>
       </c>
       <c r="E27" s="73" t="n">
-        <v>0.0032</v>
+        <v>0.0034</v>
       </c>
       <c r="F27" s="79" t="inlineStr">
         <is>
-          <t>→ 0.3%</t>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G27" s="75" t="inlineStr">
@@ -9599,7 +9599,7 @@
         <v>0.0049</v>
       </c>
       <c r="E28" s="70" t="n">
-        <v>0.0024</v>
+        <v>0.0026</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
@@ -9630,9 +9630,9 @@
         <v>0.0058</v>
       </c>
       <c r="E29" s="73" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="F29" s="77" t="inlineStr">
+        <v>0.0025</v>
+      </c>
+      <c r="F29" s="78" t="inlineStr">
         <is>
           <t>↓ 0.3%</t>
         </is>
@@ -9723,11 +9723,11 @@
         <v>0.0036</v>
       </c>
       <c r="E32" s="70" t="n">
-        <v>0.0014</v>
+        <v>0.001</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>→ 0.2%</t>
+          <t>→ 0.3%</t>
         </is>
       </c>
       <c r="G32" s="72" t="inlineStr">
@@ -9756,7 +9756,7 @@
       <c r="E33" s="73" t="n">
         <v>0.001</v>
       </c>
-      <c r="F33" s="77" t="inlineStr">
+      <c r="F33" s="78" t="inlineStr">
         <is>
           <t>↓ 0.6%</t>
         </is>
@@ -9785,7 +9785,7 @@
         <v>0.002</v>
       </c>
       <c r="E34" s="70" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
@@ -9897,23 +9897,23 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Grupo I</t>
+          <t>Grupo J</t>
         </is>
       </c>
       <c r="D38" s="70" t="n">
-        <v>0.0014</v>
+        <v>0.0017</v>
       </c>
       <c r="E38" s="70" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>→ 0.1%</t>
+          <t>→ 0.2%</t>
         </is>
       </c>
       <c r="G38" s="72" t="inlineStr">
@@ -9928,23 +9928,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Grupo J</t>
+          <t>Grupo I</t>
         </is>
       </c>
       <c r="D39" s="73" t="n">
-        <v>0.0017</v>
+        <v>0.0014</v>
       </c>
       <c r="E39" s="73" t="n">
         <v>0.0002</v>
       </c>
       <c r="F39" s="79" t="inlineStr">
         <is>
-          <t>→ 0.2%</t>
+          <t>→ 0.1%</t>
         </is>
       </c>
       <c r="G39" s="75" t="inlineStr">
@@ -10033,7 +10033,7 @@
         <v>0.0003</v>
       </c>
       <c r="E42" s="70" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="F42" s="71" t="inlineStr">
         <is>
@@ -10052,19 +10052,19 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Grupo A</t>
+          <t>Grupo B</t>
         </is>
       </c>
       <c r="D43" s="73" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="E43" s="73" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="F43" s="79" t="inlineStr">
         <is>
@@ -10083,19 +10083,19 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D44" s="70" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="E44" s="70" t="n">
         <v>0</v>
-      </c>
-      <c r="E44" s="70" t="n">
-        <v>0.0001</v>
       </c>
       <c r="F44" s="71" t="inlineStr">
         <is>
@@ -10114,19 +10114,19 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo L</t>
         </is>
       </c>
       <c r="D45" s="73" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="E45" s="73" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="F45" s="79" t="inlineStr">
         <is>
@@ -10145,16 +10145,16 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Grupo E</t>
+          <t>Grupo A</t>
         </is>
       </c>
       <c r="D46" s="70" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="E46" s="70" t="n">
         <v>0</v>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Grupo H</t>
+          <t>Grupo E</t>
         </is>
       </c>
       <c r="D47" s="73" t="n">
@@ -10207,16 +10207,16 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Grupo D</t>
+          <t>Grupo H</t>
         </is>
       </c>
       <c r="D48" s="70" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="E48" s="70" t="n">
         <v>0</v>
@@ -10238,16 +10238,16 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Grupo B</t>
+          <t>Grupo D</t>
         </is>
       </c>
       <c r="D49" s="73" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="E49" s="73" t="n">
         <v>0</v>
@@ -10258,37 +10258,6 @@
         </is>
       </c>
       <c r="G49" s="75" t="inlineStr">
-        <is>
-          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Grupo L</t>
-        </is>
-      </c>
-      <c r="D50" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="71" t="inlineStr">
-        <is>
-          <t>→ 0.0%</t>
-        </is>
-      </c>
-      <c r="G50" s="72" t="inlineStr">
         <is>
           <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
@@ -12018,7 +11987,7 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="105" t="inlineStr">
         <is>
-          <t>Brier Score: más bajo = mejor (0 = perfecto, 1 = pésimo). Log-Loss: más bajo = mejor. Naive = 1/n igual prob. a todos. El modelo v2 supera al naive en 9.8% en Brier Score y 53% en Log-Loss (Qatar 2022).</t>
+          <t>Brier Score: más bajo = mejor (0 = perfecto, 1 = pésimo). Log-Loss: más bajo = mejor. Naive = 1/n igual prob. a todos. El modelo v3 supera al naive en 9.8% en Brier Score y 53% en Log-Loss (Qatar 2022).</t>
         </is>
       </c>
     </row>
